--- a/Excel/DialogDatas.xlsx
+++ b/Excel/DialogDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15060"/>
+    <workbookView windowHeight="14880"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="162">
   <si>
     <t>int</t>
   </si>
@@ -364,6 +364,9 @@
     <t>这太奇怪了，我居然又做了这种梦</t>
   </si>
   <si>
+    <t>对梦里的事情感到后怕，San值减少10</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="24"/>
@@ -426,7 +429,13 @@
     <t>要不给小猫喝一下？</t>
   </si>
   <si>
+    <t>感觉到很奇怪，san值减少5，去拿给小猫喝一口吧</t>
+  </si>
+  <si>
     <t>猫喝了牛奶很快呼呼大睡了，你心里觉得更奇怪了</t>
+  </si>
+  <si>
+    <t>对小猫的行为感到很奇怪，san值减5</t>
   </si>
   <si>
     <t>小猫真是吃饱了就睡觉了。我们把它的铃铛取下来吧</t>
@@ -1786,7 +1795,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T103"/>
+  <dimension ref="A1:T106"/>
   <sheetFormatPr defaultColWidth="9.22115384615385" defaultRowHeight="34.4"/>
   <cols>
     <col min="1" max="1" width="21" style="2" customWidth="1"/>
@@ -2480,7 +2489,7 @@
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
     </row>
-    <row r="15" ht="172" spans="1:20">
+    <row r="15" ht="138" spans="1:20">
       <c r="A15" s="5">
         <v>10204</v>
       </c>
@@ -3858,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="C46" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D46" s="5">
         <v>0</v>
@@ -3873,7 +3882,7 @@
         <v>-1</v>
       </c>
       <c r="H46" s="5">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>105</v>
@@ -3894,7 +3903,7 @@
       <c r="S46" s="5"/>
       <c r="T46" s="5"/>
     </row>
-    <row r="47" ht="69" spans="1:20">
+    <row r="47" ht="138" spans="1:20">
       <c r="A47" s="5">
         <v>10802</v>
       </c>
@@ -3902,10 +3911,10 @@
         <v>0</v>
       </c>
       <c r="C47" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D47" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>42</v>
@@ -3917,18 +3926,18 @@
         <v>-1</v>
       </c>
       <c r="H47" s="5">
-        <v>0</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>106</v>
-      </c>
+        <v>-10</v>
+      </c>
+      <c r="I47" s="4"/>
       <c r="J47" s="5">
         <v>0</v>
       </c>
       <c r="K47" s="5">
         <v>10803</v>
       </c>
-      <c r="L47" s="4"/>
+      <c r="L47" s="4" t="s">
+        <v>106</v>
+      </c>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
@@ -3964,13 +3973,13 @@
         <v>0</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="J48" s="5">
         <v>0</v>
       </c>
       <c r="K48" s="5">
-        <v>0</v>
+        <v>10804</v>
       </c>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
@@ -3982,18 +3991,18 @@
       <c r="S48" s="5"/>
       <c r="T48" s="5"/>
     </row>
-    <row r="49" ht="104" spans="1:20">
+    <row r="49" ht="69" spans="1:20">
       <c r="A49" s="5">
-        <v>10901</v>
+        <v>10804</v>
       </c>
       <c r="B49" s="5">
         <v>0</v>
       </c>
       <c r="C49" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>42</v>
@@ -4008,13 +4017,13 @@
         <v>0</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="J49" s="5">
         <v>0</v>
       </c>
       <c r="K49" s="5">
-        <v>10902</v>
+        <v>0</v>
       </c>
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
@@ -4028,7 +4037,7 @@
     </row>
     <row r="50" ht="104" spans="1:20">
       <c r="A50" s="5">
-        <v>10902</v>
+        <v>10901</v>
       </c>
       <c r="B50" s="5">
         <v>0</v>
@@ -4037,7 +4046,7 @@
         <v>1</v>
       </c>
       <c r="D50" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>42</v>
@@ -4058,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="K50" s="5">
-        <v>10903</v>
+        <v>10902</v>
       </c>
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
@@ -4072,7 +4081,7 @@
     </row>
     <row r="51" ht="104" spans="1:20">
       <c r="A51" s="5">
-        <v>10903</v>
+        <v>10902</v>
       </c>
       <c r="B51" s="5">
         <v>0</v>
@@ -4102,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="K51" s="5">
-        <v>10904</v>
+        <v>10903</v>
       </c>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
@@ -4114,9 +4123,9 @@
       <c r="S51" s="5"/>
       <c r="T51" s="5"/>
     </row>
-    <row r="52" ht="69" spans="1:20">
+    <row r="52" ht="104" spans="1:20">
       <c r="A52" s="5">
-        <v>10904</v>
+        <v>10903</v>
       </c>
       <c r="B52" s="5">
         <v>0</v>
@@ -4146,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="K52" s="5">
-        <v>10905</v>
+        <v>10904</v>
       </c>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
@@ -4158,12 +4167,12 @@
       <c r="S52" s="5"/>
       <c r="T52" s="5"/>
     </row>
-    <row r="53" ht="138" spans="1:20">
+    <row r="53" ht="69" spans="1:20">
       <c r="A53" s="5">
-        <v>10905</v>
+        <v>10904</v>
       </c>
       <c r="B53" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C53" s="5">
         <v>1</v>
@@ -4171,11 +4180,11 @@
       <c r="D53" s="5">
         <v>1</v>
       </c>
-      <c r="E53" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>57</v>
+      <c r="E53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G53" s="5">
         <v>-1</v>
@@ -4190,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="K53" s="5">
-        <v>10906</v>
+        <v>10905</v>
       </c>
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
@@ -4204,10 +4213,10 @@
     </row>
     <row r="54" ht="138" spans="1:20">
       <c r="A54" s="5">
-        <v>10906</v>
+        <v>10905</v>
       </c>
       <c r="B54" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C54" s="5">
         <v>1</v>
@@ -4215,11 +4224,11 @@
       <c r="D54" s="5">
         <v>1</v>
       </c>
-      <c r="E54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>43</v>
+      <c r="E54" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="G54" s="5">
         <v>-1</v>
@@ -4234,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="K54" s="5">
-        <v>10907</v>
+        <v>10906</v>
       </c>
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
@@ -4246,12 +4255,12 @@
       <c r="S54" s="5"/>
       <c r="T54" s="5"/>
     </row>
-    <row r="55" ht="69" spans="1:20">
+    <row r="55" ht="138" spans="1:20">
       <c r="A55" s="5">
-        <v>10907</v>
+        <v>10906</v>
       </c>
       <c r="B55" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C55" s="5">
         <v>1</v>
@@ -4259,11 +4268,11 @@
       <c r="D55" s="5">
         <v>1</v>
       </c>
-      <c r="E55" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>57</v>
+      <c r="E55" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G55" s="5">
         <v>-1</v>
@@ -4278,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="K55" s="5">
-        <v>10908</v>
+        <v>10907</v>
       </c>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
@@ -4292,10 +4301,10 @@
     </row>
     <row r="56" ht="69" spans="1:20">
       <c r="A56" s="5">
-        <v>10908</v>
+        <v>10907</v>
       </c>
       <c r="B56" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C56" s="5">
         <v>1</v>
@@ -4303,11 +4312,11 @@
       <c r="D56" s="5">
         <v>1</v>
       </c>
-      <c r="E56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>43</v>
+      <c r="E56" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="G56" s="5">
         <v>-1</v>
@@ -4322,7 +4331,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="5">
-        <v>10909</v>
+        <v>10908</v>
       </c>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
@@ -4334,9 +4343,9 @@
       <c r="S56" s="5"/>
       <c r="T56" s="5"/>
     </row>
-    <row r="57" ht="104" spans="1:20">
+    <row r="57" ht="69" spans="1:20">
       <c r="A57" s="5">
-        <v>10909</v>
+        <v>10908</v>
       </c>
       <c r="B57" s="5">
         <v>0</v>
@@ -4366,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="K57" s="5">
-        <v>10910</v>
+        <v>10909</v>
       </c>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
@@ -4380,10 +4389,10 @@
     </row>
     <row r="58" ht="104" spans="1:20">
       <c r="A58" s="5">
-        <v>10910</v>
+        <v>10909</v>
       </c>
       <c r="B58" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C58" s="5">
         <v>1</v>
@@ -4391,11 +4400,11 @@
       <c r="D58" s="5">
         <v>1</v>
       </c>
-      <c r="E58" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>57</v>
+      <c r="E58" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G58" s="5">
         <v>-1</v>
@@ -4410,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="5">
-        <v>10911</v>
+        <v>10910</v>
       </c>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
@@ -4422,12 +4431,12 @@
       <c r="S58" s="5"/>
       <c r="T58" s="5"/>
     </row>
-    <row r="59" ht="69" spans="1:20">
+    <row r="59" ht="104" spans="1:20">
       <c r="A59" s="5">
-        <v>10911</v>
+        <v>10910</v>
       </c>
       <c r="B59" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C59" s="5">
         <v>1</v>
@@ -4435,11 +4444,11 @@
       <c r="D59" s="5">
         <v>1</v>
       </c>
-      <c r="E59" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>43</v>
+      <c r="E59" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="G59" s="5">
         <v>-1</v>
@@ -4454,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="5">
-        <v>0</v>
+        <v>10911</v>
       </c>
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
@@ -4466,24 +4475,24 @@
       <c r="S59" s="5"/>
       <c r="T59" s="5"/>
     </row>
-    <row r="60" ht="104" spans="1:20">
+    <row r="60" ht="69" spans="1:20">
       <c r="A60" s="5">
-        <v>11001</v>
+        <v>10911</v>
       </c>
       <c r="B60" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" s="5">
         <v>1</v>
       </c>
       <c r="D60" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="G60" s="5">
         <v>-1</v>
@@ -4498,7 +4507,7 @@
         <v>0</v>
       </c>
       <c r="K60" s="5">
-        <v>10102</v>
+        <v>0</v>
       </c>
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
@@ -4510,39 +4519,39 @@
       <c r="S60" s="5"/>
       <c r="T60" s="5"/>
     </row>
-    <row r="61" ht="35" spans="1:20">
+    <row r="61" ht="104" spans="1:20">
       <c r="A61" s="5">
+        <v>11001</v>
+      </c>
+      <c r="B61" s="5">
+        <v>1</v>
+      </c>
+      <c r="C61" s="5">
+        <v>1</v>
+      </c>
+      <c r="D61" s="5">
+        <v>0</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G61" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H61" s="5">
+        <v>0</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J61" s="5">
+        <v>0</v>
+      </c>
+      <c r="K61" s="5">
         <v>11002</v>
-      </c>
-      <c r="B61" s="5">
-        <v>0</v>
-      </c>
-      <c r="C61" s="5">
-        <v>1</v>
-      </c>
-      <c r="D61" s="5">
-        <v>1</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G61" s="5">
-        <v>-1</v>
-      </c>
-      <c r="H61" s="5">
-        <v>0</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J61" s="5">
-        <v>0</v>
-      </c>
-      <c r="K61" s="5">
-        <v>0</v>
       </c>
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
@@ -4554,9 +4563,9 @@
       <c r="S61" s="5"/>
       <c r="T61" s="5"/>
     </row>
-    <row r="62" ht="104" spans="1:20">
+    <row r="62" ht="35" spans="1:20">
       <c r="A62" s="5">
-        <v>11101</v>
+        <v>11002</v>
       </c>
       <c r="B62" s="5">
         <v>0</v>
@@ -4565,7 +4574,7 @@
         <v>1</v>
       </c>
       <c r="D62" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" s="5" t="s">
         <v>42</v>
@@ -4580,13 +4589,13 @@
         <v>0</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="J62" s="5">
         <v>0</v>
       </c>
       <c r="K62" s="5">
-        <v>11102</v>
+        <v>0</v>
       </c>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
@@ -4598,27 +4607,27 @@
       <c r="S62" s="5"/>
       <c r="T62" s="5"/>
     </row>
-    <row r="63" ht="69" spans="1:20">
+    <row r="63" ht="104" spans="1:20">
       <c r="A63" s="5">
-        <v>11102</v>
+        <v>11101</v>
       </c>
       <c r="B63" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C63" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" s="5">
-        <v>1</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G63" s="5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H63" s="5">
         <v>0</v>
@@ -4630,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="K63" s="5">
-        <v>0</v>
+        <v>11102</v>
       </c>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
@@ -4642,30 +4651,30 @@
       <c r="S63" s="5"/>
       <c r="T63" s="5"/>
     </row>
-    <row r="64" ht="104" spans="1:20">
+    <row r="64" ht="69" spans="1:20">
       <c r="A64" s="5">
-        <v>1901</v>
+        <v>11102</v>
       </c>
       <c r="B64" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C64" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D64" s="5">
-        <v>0</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>47</v>
+        <v>1</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="G64" s="5">
         <v>-1</v>
       </c>
       <c r="H64" s="5">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>121</v>
@@ -4674,7 +4683,7 @@
         <v>0</v>
       </c>
       <c r="K64" s="5">
-        <v>0</v>
+        <v>11103</v>
       </c>
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
@@ -4686,41 +4695,41 @@
       <c r="S64" s="5"/>
       <c r="T64" s="5"/>
     </row>
-    <row r="65" ht="104" spans="1:20">
+    <row r="65" ht="172" spans="1:20">
       <c r="A65" s="5">
-        <v>11201</v>
+        <v>11103</v>
       </c>
       <c r="B65" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C65" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D65" s="5">
-        <v>0</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>57</v>
+        <v>1</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G65" s="5">
         <v>-1</v>
       </c>
       <c r="H65" s="5">
-        <v>0</v>
-      </c>
-      <c r="I65" s="4" t="s">
+        <v>-5</v>
+      </c>
+      <c r="I65" s="4"/>
+      <c r="J65" s="5">
+        <v>0</v>
+      </c>
+      <c r="K65" s="5">
+        <v>0</v>
+      </c>
+      <c r="L65" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="J65" s="5">
-        <v>0</v>
-      </c>
-      <c r="K65" s="5">
-        <v>11202</v>
-      </c>
-      <c r="L65" s="4"/>
       <c r="M65" s="4"/>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
@@ -4730,27 +4739,27 @@
       <c r="S65" s="5"/>
       <c r="T65" s="5"/>
     </row>
-    <row r="66" ht="69" spans="1:20">
+    <row r="66" ht="104" spans="1:20">
       <c r="A66" s="5">
-        <v>11202</v>
+        <v>1901</v>
       </c>
       <c r="B66" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C66" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D66" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G66" s="5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H66" s="5">
         <v>0</v>
@@ -4762,7 +4771,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="5">
-        <v>11203</v>
+        <v>1902</v>
       </c>
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
@@ -4774,41 +4783,41 @@
       <c r="S66" s="5"/>
       <c r="T66" s="5"/>
     </row>
-    <row r="67" ht="104" spans="1:20">
+    <row r="67" ht="138" spans="1:20">
       <c r="A67" s="5">
-        <v>11203</v>
+        <v>1902</v>
       </c>
       <c r="B67" s="5">
         <v>0</v>
       </c>
       <c r="C67" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D67" s="5">
         <v>1</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G67" s="5">
         <v>-1</v>
       </c>
       <c r="H67" s="5">
-        <v>0</v>
-      </c>
-      <c r="I67" s="4" t="s">
+        <v>-5</v>
+      </c>
+      <c r="I67" s="4"/>
+      <c r="J67" s="5">
+        <v>0</v>
+      </c>
+      <c r="K67" s="5">
+        <v>0</v>
+      </c>
+      <c r="L67" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="J67" s="5">
-        <v>0</v>
-      </c>
-      <c r="K67" s="5">
-        <v>0</v>
-      </c>
-      <c r="L67" s="4"/>
       <c r="M67" s="4"/>
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
@@ -4818,24 +4827,24 @@
       <c r="S67" s="5"/>
       <c r="T67" s="5"/>
     </row>
-    <row r="68" ht="69" spans="1:20">
+    <row r="68" ht="104" spans="1:20">
       <c r="A68" s="5">
-        <v>11301</v>
+        <v>11201</v>
       </c>
       <c r="B68" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C68" s="5">
         <v>1</v>
       </c>
       <c r="D68" s="5">
-        <v>1</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>43</v>
+        <v>0</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="G68" s="5">
         <v>-1</v>
@@ -4850,7 +4859,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="5">
-        <v>11302</v>
+        <v>11202</v>
       </c>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
@@ -4862,27 +4871,27 @@
       <c r="S68" s="5"/>
       <c r="T68" s="5"/>
     </row>
-    <row r="69" ht="104" spans="1:20">
+    <row r="69" ht="69" spans="1:20">
       <c r="A69" s="5">
-        <v>11302</v>
+        <v>11202</v>
       </c>
       <c r="B69" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C69" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" s="5">
         <v>1</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G69" s="5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H69" s="5">
         <v>0</v>
@@ -4894,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="5">
-        <v>11303</v>
+        <v>11203</v>
       </c>
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
@@ -4906,15 +4915,15 @@
       <c r="S69" s="5"/>
       <c r="T69" s="5"/>
     </row>
-    <row r="70" ht="35" spans="1:20">
+    <row r="70" ht="104" spans="1:20">
       <c r="A70" s="5">
-        <v>11303</v>
+        <v>11203</v>
       </c>
       <c r="B70" s="5">
         <v>0</v>
       </c>
       <c r="C70" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D70" s="5">
         <v>1</v>
@@ -4929,7 +4938,7 @@
         <v>-1</v>
       </c>
       <c r="H70" s="5">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>127</v>
@@ -4938,7 +4947,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="5">
-        <v>11304</v>
+        <v>0</v>
       </c>
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
@@ -4950,12 +4959,12 @@
       <c r="S70" s="5"/>
       <c r="T70" s="5"/>
     </row>
-    <row r="71" ht="207" spans="1:20">
+    <row r="71" ht="69" spans="1:20">
       <c r="A71" s="5">
-        <v>11304</v>
+        <v>11301</v>
       </c>
       <c r="B71" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C71" s="5">
         <v>1</v>
@@ -4964,10 +4973,10 @@
         <v>1</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G71" s="5">
         <v>-1</v>
@@ -4982,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="5">
-        <v>11305</v>
+        <v>11302</v>
       </c>
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
@@ -4994,9 +5003,9 @@
       <c r="S71" s="5"/>
       <c r="T71" s="5"/>
     </row>
-    <row r="72" ht="138" spans="1:20">
+    <row r="72" ht="104" spans="1:20">
       <c r="A72" s="5">
-        <v>11305</v>
+        <v>11302</v>
       </c>
       <c r="B72" s="5">
         <v>12</v>
@@ -5026,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="K72" s="5">
-        <v>11306</v>
+        <v>11303</v>
       </c>
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
@@ -5038,30 +5047,30 @@
       <c r="S72" s="5"/>
       <c r="T72" s="5"/>
     </row>
-    <row r="73" ht="138" spans="1:20">
+    <row r="73" ht="69" spans="1:20">
       <c r="A73" s="5">
-        <v>11306</v>
+        <v>11303</v>
       </c>
       <c r="B73" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C73" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D73" s="5">
         <v>1</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G73" s="5">
         <v>-1</v>
       </c>
       <c r="H73" s="5">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>130</v>
@@ -5070,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="5">
-        <v>0</v>
+        <v>11304</v>
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
@@ -5082,21 +5091,21 @@
       <c r="S73" s="5"/>
       <c r="T73" s="5"/>
     </row>
-    <row r="74" ht="69" spans="1:20">
+    <row r="74" ht="207" spans="1:20">
       <c r="A74" s="5">
-        <v>2001</v>
+        <v>11304</v>
       </c>
       <c r="B74" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C74" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>47</v>
@@ -5114,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="K74" s="5">
-        <v>0</v>
+        <v>11305</v>
       </c>
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
@@ -5126,21 +5135,21 @@
       <c r="S74" s="5"/>
       <c r="T74" s="5"/>
     </row>
-    <row r="75" ht="69" spans="1:20">
+    <row r="75" ht="138" spans="1:20">
       <c r="A75" s="5">
-        <v>2101</v>
+        <v>11305</v>
       </c>
       <c r="B75" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C75" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="F75" s="7" t="s">
         <v>47</v>
@@ -5152,13 +5161,13 @@
         <v>0</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J75" s="5">
         <v>0</v>
       </c>
       <c r="K75" s="5">
-        <v>0</v>
+        <v>11306</v>
       </c>
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
@@ -5170,21 +5179,21 @@
       <c r="S75" s="5"/>
       <c r="T75" s="5"/>
     </row>
-    <row r="76" ht="35" spans="1:20">
+    <row r="76" ht="138" spans="1:20">
       <c r="A76" s="5">
-        <v>2201</v>
+        <v>11306</v>
       </c>
       <c r="B76" s="5">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C76" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D76" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="F76" s="7" t="s">
         <v>47</v>
@@ -5196,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J76" s="5">
         <v>0</v>
@@ -5214,12 +5223,12 @@
       <c r="S76" s="5"/>
       <c r="T76" s="5"/>
     </row>
-    <row r="77" ht="104" spans="1:20">
+    <row r="77" ht="69" spans="1:20">
       <c r="A77" s="5">
-        <v>2301</v>
+        <v>2001</v>
       </c>
       <c r="B77" s="5">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C77" s="5">
         <v>0</v>
@@ -5228,9 +5237,9 @@
         <v>0</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F77" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F77" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G77" s="5">
@@ -5240,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="J77" s="5">
         <v>0</v>
@@ -5260,10 +5269,10 @@
     </row>
     <row r="78" ht="69" spans="1:20">
       <c r="A78" s="5">
-        <v>11401</v>
+        <v>2101</v>
       </c>
       <c r="B78" s="5">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C78" s="5">
         <v>0</v>
@@ -5272,10 +5281,10 @@
         <v>0</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>96</v>
+        <v>135</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="G78" s="5">
         <v>-1</v>
@@ -5290,7 +5299,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="5">
-        <v>11402</v>
+        <v>0</v>
       </c>
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
@@ -5302,24 +5311,24 @@
       <c r="S78" s="5"/>
       <c r="T78" s="5"/>
     </row>
-    <row r="79" ht="104" spans="1:20">
+    <row r="79" ht="35" spans="1:20">
       <c r="A79" s="5">
-        <v>11402</v>
+        <v>2201</v>
       </c>
       <c r="B79" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C79" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D79" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>43</v>
+        <v>137</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="G79" s="5">
         <v>-1</v>
@@ -5328,7 +5337,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J79" s="5">
         <v>0</v>
@@ -5346,23 +5355,23 @@
       <c r="S79" s="5"/>
       <c r="T79" s="5"/>
     </row>
-    <row r="80" ht="138" spans="1:20">
+    <row r="80" ht="104" spans="1:20">
       <c r="A80" s="5">
-        <v>11501</v>
+        <v>2301</v>
       </c>
       <c r="B80" s="5">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C80" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80" s="5">
         <v>0</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="F80" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F80" s="5" t="s">
         <v>47</v>
       </c>
       <c r="G80" s="5">
@@ -5372,13 +5381,13 @@
         <v>0</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="J80" s="5">
         <v>0</v>
       </c>
       <c r="K80" s="5">
-        <v>11502</v>
+        <v>0</v>
       </c>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
@@ -5390,24 +5399,24 @@
       <c r="S80" s="5"/>
       <c r="T80" s="5"/>
     </row>
-    <row r="81" ht="138" spans="1:20">
+    <row r="81" ht="69" spans="1:20">
       <c r="A81" s="5">
-        <v>11502</v>
+        <v>11401</v>
       </c>
       <c r="B81" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81" s="5">
-        <v>1</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="G81" s="5">
         <v>-1</v>
@@ -5416,13 +5425,13 @@
         <v>0</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J81" s="5">
         <v>0</v>
       </c>
       <c r="K81" s="5">
-        <v>11503</v>
+        <v>11402</v>
       </c>
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
@@ -5434,24 +5443,24 @@
       <c r="S81" s="5"/>
       <c r="T81" s="5"/>
     </row>
-    <row r="82" ht="138" spans="1:20">
+    <row r="82" ht="104" spans="1:20">
       <c r="A82" s="5">
-        <v>11503</v>
+        <v>11402</v>
       </c>
       <c r="B82" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C82" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D82" s="5">
         <v>1</v>
       </c>
-      <c r="E82" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>57</v>
+      <c r="E82" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G82" s="5">
         <v>-1</v>
@@ -5460,13 +5469,13 @@
         <v>0</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J82" s="5">
         <v>0</v>
       </c>
       <c r="K82" s="5">
-        <v>11504</v>
+        <v>0</v>
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
@@ -5478,24 +5487,24 @@
       <c r="S82" s="5"/>
       <c r="T82" s="5"/>
     </row>
-    <row r="83" ht="35" spans="1:20">
+    <row r="83" ht="104" spans="1:20">
       <c r="A83" s="5">
-        <v>11504</v>
+        <v>11501</v>
       </c>
       <c r="B83" s="5">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C83" s="5">
         <v>1</v>
       </c>
       <c r="D83" s="5">
-        <v>1</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F83" s="8" t="s">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="G83" s="5">
         <v>-1</v>
@@ -5504,13 +5513,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>65</v>
+        <v>142</v>
       </c>
       <c r="J83" s="5">
         <v>0</v>
       </c>
       <c r="K83" s="5">
-        <v>11505</v>
+        <v>11502</v>
       </c>
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
@@ -5522,9 +5531,9 @@
       <c r="S83" s="5"/>
       <c r="T83" s="5"/>
     </row>
-    <row r="84" ht="69" spans="1:20">
+    <row r="84" ht="138" spans="1:20">
       <c r="A84" s="5">
-        <v>11505</v>
+        <v>11502</v>
       </c>
       <c r="B84" s="5">
         <v>2</v>
@@ -5548,13 +5557,13 @@
         <v>0</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J84" s="5">
         <v>0</v>
       </c>
       <c r="K84" s="5">
-        <v>11506</v>
+        <v>11503</v>
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
@@ -5566,9 +5575,9 @@
       <c r="S84" s="5"/>
       <c r="T84" s="5"/>
     </row>
-    <row r="85" ht="35" spans="1:20">
+    <row r="85" ht="138" spans="1:20">
       <c r="A85" s="5">
-        <v>11506</v>
+        <v>11503</v>
       </c>
       <c r="B85" s="5">
         <v>2</v>
@@ -5592,13 +5601,13 @@
         <v>0</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J85" s="5">
         <v>0</v>
       </c>
       <c r="K85" s="5">
-        <v>11507</v>
+        <v>11504</v>
       </c>
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
@@ -5610,9 +5619,9 @@
       <c r="S85" s="5"/>
       <c r="T85" s="5"/>
     </row>
-    <row r="86" ht="69" spans="1:20">
+    <row r="86" ht="35" spans="1:20">
       <c r="A86" s="5">
-        <v>11507</v>
+        <v>11504</v>
       </c>
       <c r="B86" s="5">
         <v>2</v>
@@ -5636,13 +5645,13 @@
         <v>0</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>144</v>
+        <v>65</v>
       </c>
       <c r="J86" s="5">
         <v>0</v>
       </c>
       <c r="K86" s="5">
-        <v>0</v>
+        <v>11505</v>
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
@@ -5654,9 +5663,9 @@
       <c r="S86" s="5"/>
       <c r="T86" s="5"/>
     </row>
-    <row r="87" ht="172" spans="1:20">
+    <row r="87" ht="69" spans="1:20">
       <c r="A87" s="5">
-        <v>11601</v>
+        <v>11505</v>
       </c>
       <c r="B87" s="5">
         <v>2</v>
@@ -5665,7 +5674,7 @@
         <v>1</v>
       </c>
       <c r="D87" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" s="8" t="s">
         <v>56</v>
@@ -5686,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="5">
-        <v>11602</v>
+        <v>11506</v>
       </c>
       <c r="L87" s="4"/>
       <c r="M87" s="4"/>
@@ -5698,9 +5707,9 @@
       <c r="S87" s="5"/>
       <c r="T87" s="5"/>
     </row>
-    <row r="88" ht="104" spans="1:20">
+    <row r="88" ht="35" spans="1:20">
       <c r="A88" s="5">
-        <v>11602</v>
+        <v>11506</v>
       </c>
       <c r="B88" s="5">
         <v>2</v>
@@ -5730,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="5">
-        <v>11603</v>
+        <v>11507</v>
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
@@ -5742,9 +5751,9 @@
       <c r="S88" s="5"/>
       <c r="T88" s="5"/>
     </row>
-    <row r="89" ht="35" spans="1:20">
+    <row r="89" ht="69" spans="1:20">
       <c r="A89" s="5">
-        <v>11603</v>
+        <v>11507</v>
       </c>
       <c r="B89" s="5">
         <v>2</v>
@@ -5768,13 +5777,13 @@
         <v>0</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="J89" s="5">
         <v>0</v>
       </c>
       <c r="K89" s="5">
-        <v>11604</v>
+        <v>0</v>
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
@@ -5786,9 +5795,9 @@
       <c r="S89" s="5"/>
       <c r="T89" s="5"/>
     </row>
-    <row r="90" ht="104" spans="1:20">
+    <row r="90" ht="172" spans="1:20">
       <c r="A90" s="5">
-        <v>11604</v>
+        <v>11601</v>
       </c>
       <c r="B90" s="5">
         <v>2</v>
@@ -5797,7 +5806,7 @@
         <v>1</v>
       </c>
       <c r="D90" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>56</v>
@@ -5812,13 +5821,13 @@
         <v>0</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J90" s="5">
         <v>0</v>
       </c>
       <c r="K90" s="5">
-        <v>11605</v>
+        <v>11602</v>
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
@@ -5830,9 +5839,9 @@
       <c r="S90" s="5"/>
       <c r="T90" s="5"/>
     </row>
-    <row r="91" ht="35" spans="1:20">
+    <row r="91" ht="104" spans="1:20">
       <c r="A91" s="5">
-        <v>11605</v>
+        <v>11602</v>
       </c>
       <c r="B91" s="5">
         <v>2</v>
@@ -5856,13 +5865,13 @@
         <v>0</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>65</v>
+        <v>149</v>
       </c>
       <c r="J91" s="5">
         <v>0</v>
       </c>
       <c r="K91" s="5">
-        <v>11606</v>
+        <v>11603</v>
       </c>
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
@@ -5874,9 +5883,9 @@
       <c r="S91" s="5"/>
       <c r="T91" s="5"/>
     </row>
-    <row r="92" ht="104" spans="1:20">
+    <row r="92" ht="35" spans="1:20">
       <c r="A92" s="5">
-        <v>11606</v>
+        <v>11603</v>
       </c>
       <c r="B92" s="5">
         <v>2</v>
@@ -5900,13 +5909,13 @@
         <v>0</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="J92" s="5">
         <v>0</v>
       </c>
       <c r="K92" s="5">
-        <v>0</v>
+        <v>11604</v>
       </c>
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
@@ -5920,22 +5929,22 @@
     </row>
     <row r="93" ht="104" spans="1:20">
       <c r="A93" s="5">
-        <v>2401</v>
+        <v>11604</v>
       </c>
       <c r="B93" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C93" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93" s="5">
-        <v>0</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="G93" s="5">
         <v>-1</v>
@@ -5944,13 +5953,13 @@
         <v>0</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J93" s="5">
         <v>0</v>
       </c>
       <c r="K93" s="5">
-        <v>0</v>
+        <v>11605</v>
       </c>
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
@@ -5962,39 +5971,39 @@
       <c r="S93" s="5"/>
       <c r="T93" s="5"/>
     </row>
-    <row r="94" ht="104" spans="1:20">
+    <row r="94" ht="35" spans="1:20">
       <c r="A94" s="5">
-        <v>11701</v>
+        <v>11605</v>
       </c>
       <c r="B94" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C94" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D94" s="5">
-        <v>0</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="G94" s="5">
         <v>-1</v>
       </c>
       <c r="H94" s="5">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="J94" s="5">
         <v>0</v>
       </c>
       <c r="K94" s="5">
-        <v>11702</v>
+        <v>11606</v>
       </c>
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
@@ -6006,24 +6015,24 @@
       <c r="S94" s="5"/>
       <c r="T94" s="5"/>
     </row>
-    <row r="95" ht="35" spans="1:20">
+    <row r="95" ht="104" spans="1:20">
       <c r="A95" s="5">
-        <v>11702</v>
+        <v>11606</v>
       </c>
       <c r="B95" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C95" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95" s="5">
         <v>1</v>
       </c>
-      <c r="E95" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>43</v>
+      <c r="E95" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="G95" s="5">
         <v>-1</v>
@@ -6038,7 +6047,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="5">
-        <v>11703</v>
+        <v>0</v>
       </c>
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
@@ -6050,9 +6059,9 @@
       <c r="S95" s="5"/>
       <c r="T95" s="5"/>
     </row>
-    <row r="96" ht="69" spans="1:20">
+    <row r="96" ht="104" spans="1:20">
       <c r="A96" s="5">
-        <v>11703</v>
+        <v>2401</v>
       </c>
       <c r="B96" s="5">
         <v>0</v>
@@ -6061,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="D96" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" s="5" t="s">
         <v>42</v>
@@ -6094,15 +6103,15 @@
       <c r="S96" s="5"/>
       <c r="T96" s="5"/>
     </row>
-    <row r="97" ht="69" spans="1:20">
+    <row r="97" ht="104" spans="1:20">
       <c r="A97" s="5">
-        <v>2501</v>
+        <v>11701</v>
       </c>
       <c r="B97" s="5">
         <v>0</v>
       </c>
       <c r="C97" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D97" s="5">
         <v>0</v>
@@ -6117,7 +6126,7 @@
         <v>-1</v>
       </c>
       <c r="H97" s="5">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>153</v>
@@ -6126,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="5">
-        <v>0</v>
+        <v>11702</v>
       </c>
       <c r="L97" s="4"/>
       <c r="M97" s="4"/>
@@ -6138,24 +6147,24 @@
       <c r="S97" s="5"/>
       <c r="T97" s="5"/>
     </row>
-    <row r="98" ht="69" spans="1:20">
+    <row r="98" ht="35" spans="1:20">
       <c r="A98" s="5">
-        <v>2601</v>
+        <v>11702</v>
       </c>
       <c r="B98" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C98" s="5">
         <v>0</v>
       </c>
       <c r="D98" s="5">
-        <v>0</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F98" s="8" t="s">
-        <v>57</v>
+        <v>1</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G98" s="5">
         <v>-1</v>
@@ -6170,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="5">
-        <v>2602</v>
+        <v>11703</v>
       </c>
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
@@ -6182,12 +6191,12 @@
       <c r="S98" s="5"/>
       <c r="T98" s="5"/>
     </row>
-    <row r="99" ht="104" spans="1:20">
+    <row r="99" ht="69" spans="1:20">
       <c r="A99" s="5">
-        <v>2602</v>
+        <v>11703</v>
       </c>
       <c r="B99" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C99" s="5">
         <v>0</v>
@@ -6195,11 +6204,11 @@
       <c r="D99" s="5">
         <v>1</v>
       </c>
-      <c r="E99" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>57</v>
+      <c r="E99" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F99" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G99" s="5">
         <v>-1</v>
@@ -6228,13 +6237,13 @@
     </row>
     <row r="100" ht="69" spans="1:20">
       <c r="A100" s="5">
-        <v>11801</v>
+        <v>2501</v>
       </c>
       <c r="B100" s="5">
         <v>0</v>
       </c>
       <c r="C100" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D100" s="5">
         <v>0</v>
@@ -6249,7 +6258,7 @@
         <v>-1</v>
       </c>
       <c r="H100" s="5">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>156</v>
@@ -6258,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="5">
-        <v>11802</v>
+        <v>0</v>
       </c>
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
@@ -6270,30 +6279,30 @@
       <c r="S100" s="5"/>
       <c r="T100" s="5"/>
     </row>
-    <row r="101" ht="138" spans="1:20">
+    <row r="101" ht="69" spans="1:20">
       <c r="A101" s="5">
-        <v>11802</v>
+        <v>2601</v>
       </c>
       <c r="B101" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C101" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D101" s="5">
-        <v>1</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>43</v>
+        <v>0</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="G101" s="5">
         <v>-1</v>
       </c>
       <c r="H101" s="5">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>157</v>
@@ -6302,7 +6311,7 @@
         <v>0</v>
       </c>
       <c r="K101" s="5">
-        <v>11803</v>
+        <v>2602</v>
       </c>
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
@@ -6314,30 +6323,30 @@
       <c r="S101" s="5"/>
       <c r="T101" s="5"/>
     </row>
-    <row r="102" ht="69" spans="1:20">
+    <row r="102" ht="104" spans="1:20">
       <c r="A102" s="5">
-        <v>11803</v>
+        <v>2602</v>
       </c>
       <c r="B102" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C102" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D102" s="5">
         <v>1</v>
       </c>
-      <c r="E102" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>43</v>
+      <c r="E102" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="G102" s="5">
         <v>-1</v>
       </c>
       <c r="H102" s="5">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>158</v>
@@ -6358,10 +6367,142 @@
       <c r="S102" s="5"/>
       <c r="T102" s="5"/>
     </row>
-    <row r="103" spans="1:3">
-      <c r="A103" s="5"/>
-      <c r="B103" s="5"/>
-      <c r="C103" s="5"/>
+    <row r="103" ht="69" spans="1:20">
+      <c r="A103" s="5">
+        <v>11801</v>
+      </c>
+      <c r="B103" s="5">
+        <v>0</v>
+      </c>
+      <c r="C103" s="5">
+        <v>4</v>
+      </c>
+      <c r="D103" s="5">
+        <v>0</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G103" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H103" s="5">
+        <v>-10</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="J103" s="5">
+        <v>0</v>
+      </c>
+      <c r="K103" s="5">
+        <v>11802</v>
+      </c>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4"/>
+      <c r="N103" s="4"/>
+      <c r="O103" s="4"/>
+      <c r="P103" s="4"/>
+      <c r="Q103" s="5"/>
+      <c r="R103" s="5"/>
+      <c r="S103" s="5"/>
+      <c r="T103" s="5"/>
+    </row>
+    <row r="104" ht="138" spans="1:20">
+      <c r="A104" s="5">
+        <v>11802</v>
+      </c>
+      <c r="B104" s="5">
+        <v>0</v>
+      </c>
+      <c r="C104" s="5">
+        <v>4</v>
+      </c>
+      <c r="D104" s="5">
+        <v>1</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G104" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H104" s="5">
+        <v>-10</v>
+      </c>
+      <c r="I104" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="J104" s="5">
+        <v>0</v>
+      </c>
+      <c r="K104" s="5">
+        <v>11803</v>
+      </c>
+      <c r="L104" s="4"/>
+      <c r="M104" s="4"/>
+      <c r="N104" s="4"/>
+      <c r="O104" s="4"/>
+      <c r="P104" s="4"/>
+      <c r="Q104" s="5"/>
+      <c r="R104" s="5"/>
+      <c r="S104" s="5"/>
+      <c r="T104" s="5"/>
+    </row>
+    <row r="105" ht="69" spans="1:20">
+      <c r="A105" s="5">
+        <v>11803</v>
+      </c>
+      <c r="B105" s="5">
+        <v>0</v>
+      </c>
+      <c r="C105" s="5">
+        <v>4</v>
+      </c>
+      <c r="D105" s="5">
+        <v>1</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G105" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H105" s="5">
+        <v>-10</v>
+      </c>
+      <c r="I105" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="J105" s="5">
+        <v>0</v>
+      </c>
+      <c r="K105" s="5">
+        <v>0</v>
+      </c>
+      <c r="L105" s="4"/>
+      <c r="M105" s="4"/>
+      <c r="N105" s="4"/>
+      <c r="O105" s="4"/>
+      <c r="P105" s="4"/>
+      <c r="Q105" s="5"/>
+      <c r="R105" s="5"/>
+      <c r="S105" s="5"/>
+      <c r="T105" s="5"/>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="5"/>
+      <c r="B106" s="5"/>
+      <c r="C106" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Excel/DialogDatas.xlsx
+++ b/Excel/DialogDatas.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="173">
   <si>
     <t>int</t>
   </si>
@@ -41,7 +41,7 @@
     <t>对话主体的类型：0代表主角，1代表Mom，2代表Bob，3代表God，4代表TV，5代表相框，6代表桌子，7代表猫，8代表狗，9代表炸鸡店，10代表糖果店，11代表花店，12代表路人甲，13代表路人乙，14代表路人丙，15代表路人丁，16代表David‘Mom</t>
   </si>
   <si>
-    <t>对话的类型：0代表Normal，1代表Task，2代表Item，3代表Choose，4代表Effect</t>
+    <t>对话的类型：0代表Normal，1代表Task，2代表Item，3代表Choose，4代表Effect，5代表Info</t>
   </si>
   <si>
     <t>对话的触发时机，0代表isStart,1代表isSpeaking，2代表isEnd，isEnd暂时没用</t>
@@ -194,6 +194,12 @@
     <t>感觉收到惊吓，San值减少了20</t>
   </si>
   <si>
+    <t>上帝</t>
+  </si>
+  <si>
+    <t>家里好像还有事情没有处理，四处逛逛吧</t>
+  </si>
+  <si>
     <t>bob来了，我去开门吧</t>
   </si>
   <si>
@@ -294,6 +300,12 @@
   </si>
   <si>
     <t>我总觉得有些不对，bob你明天再来我家吧</t>
+  </si>
+  <si>
+    <t>尽快回家吧，在外面玩的太晚不是什么好事</t>
+  </si>
+  <si>
+    <t>家里已经没有事情可以处理了，在院子四处逛逛吧</t>
   </si>
   <si>
     <t>想想今天所看到的。奇怪的梦，遇害的隔壁老王，带血的牙齿，异常的毛发......</t>
@@ -420,6 +432,9 @@
     <t>没办法，我妈让我喝，说长得高</t>
   </si>
   <si>
+    <t>去客厅的桌子上喝牛奶吧</t>
+  </si>
+  <si>
     <t>你们不可以白天喝牛奶噢。乖，去外边玩吧</t>
   </si>
   <si>
@@ -432,6 +447,9 @@
     <t>感觉到很奇怪，san值减少5，去拿给小猫喝一口吧</t>
   </si>
   <si>
+    <t>妈妈不允许喝牛奶，这是为什么呢？去院子探索一番吧</t>
+  </si>
+  <si>
     <t>猫喝了牛奶很快呼呼大睡了，你心里觉得更奇怪了</t>
   </si>
   <si>
@@ -441,12 +459,18 @@
     <t>小猫真是吃饱了就睡觉了。我们把它的铃铛取下来吧</t>
   </si>
   <si>
-    <t>看起来有些旧，收着可能有用吧</t>
+    <t>你上前取下了小猫戴着的铃铛</t>
+  </si>
+  <si>
+    <t>获得一个铃铛，虽然看起来有些旧，但是收着吧，可能后面会有用</t>
   </si>
   <si>
     <t>不应该是这样的，我们得去问问其他人</t>
   </si>
   <si>
+    <t>四处走走，打听一下消息吧</t>
+  </si>
+  <si>
     <t>叔叔，想问你会在白天喝牛奶吗</t>
   </si>
   <si>
@@ -456,6 +480,9 @@
     <t>......为什么这么说</t>
   </si>
   <si>
+    <t>对他说的话感到奇怪，san值减少5点</t>
+  </si>
+  <si>
     <t>是你家大人不让你们喝吗？我只能告诉你，我的父母从小也是这么告诉我的，父母的父母那辈也是如此。</t>
   </si>
   <si>
@@ -465,6 +492,9 @@
     <t>你长大就知道了。有些事情就是这样传承下来的。不需要知道为什么。</t>
   </si>
   <si>
+    <t>对他的话感到很疑惑，四处逛逛收集更多信息吧</t>
+  </si>
+  <si>
     <t>我爱睡觉皮肤好好，啦啦啦</t>
   </si>
   <si>
@@ -484,6 +514,9 @@
   </si>
   <si>
     <t>你感到牛奶也很奇怪，但心底有股冲动还是想喝下去</t>
+  </si>
+  <si>
+    <t>你最终选择喝下了牛奶</t>
   </si>
   <si>
     <t>鲍勃的妈妈</t>
@@ -768,7 +801,7 @@
     </font>
     <font>
       <sz val="24"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -780,7 +813,7 @@
     </font>
     <font>
       <sz val="24"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1795,7 +1828,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T106"/>
+  <dimension ref="A1:T116"/>
   <sheetFormatPr defaultColWidth="9.22115384615385" defaultRowHeight="34.4"/>
   <cols>
     <col min="1" max="1" width="21" style="2" customWidth="1"/>
@@ -2311,24 +2344,24 @@
       <c r="S10" s="5"/>
       <c r="T10" s="5"/>
     </row>
-    <row r="11" ht="69" spans="1:20">
+    <row r="11" ht="138" spans="1:20">
       <c r="A11" s="5">
-        <v>10101</v>
+        <v>10050</v>
       </c>
       <c r="B11" s="5">
         <v>0</v>
       </c>
       <c r="C11" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D11" s="5">
         <v>0</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G11" s="5">
         <v>-1</v>
@@ -2337,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J11" s="5">
         <v>0</v>
@@ -2345,7 +2378,9 @@
       <c r="K11" s="5">
         <v>0</v>
       </c>
-      <c r="L11" s="4"/>
+      <c r="L11" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
@@ -2355,105 +2390,103 @@
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
     </row>
-    <row r="12" s="1" customFormat="1" ht="104" spans="1:20">
-      <c r="A12" s="6">
+    <row r="12" ht="69" spans="1:20">
+      <c r="A12" s="5">
+        <v>10101</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="104" spans="1:20">
+      <c r="A13" s="6">
         <v>10201</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B13" s="6">
         <v>2</v>
       </c>
-      <c r="C12" s="6">
-        <v>0</v>
-      </c>
-      <c r="D12" s="6">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H12" s="6">
-        <v>0</v>
-      </c>
-      <c r="I12" s="9" t="s">
+      <c r="C13" s="6">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="6">
-        <v>0</v>
-      </c>
-      <c r="K12" s="6">
+      <c r="F13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="6">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="6">
+        <v>0</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" s="6">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6">
         <v>10202</v>
       </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
-    </row>
-    <row r="13" ht="104" spans="1:20">
-      <c r="A13" s="5">
+      <c r="L13" s="4"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+    </row>
+    <row r="14" ht="104" spans="1:20">
+      <c r="A14" s="5">
         <v>10202</v>
       </c>
-      <c r="B13" s="5">
-        <v>0</v>
-      </c>
-      <c r="C13" s="5">
+      <c r="B14" s="5">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5">
         <v>2</v>
-      </c>
-      <c r="D13" s="5">
-        <v>1</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13" s="5">
-        <v>1</v>
-      </c>
-      <c r="H13" s="5">
-        <v>0</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="J13" s="5">
-        <v>0</v>
-      </c>
-      <c r="K13" s="5">
-        <v>10203</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-    </row>
-    <row r="14" ht="69" spans="1:20">
-      <c r="A14" s="5">
-        <v>10203</v>
-      </c>
-      <c r="B14" s="5">
-        <v>0</v>
-      </c>
-      <c r="C14" s="5">
-        <v>0</v>
       </c>
       <c r="D14" s="5">
         <v>1</v>
@@ -2465,7 +2498,7 @@
         <v>43</v>
       </c>
       <c r="G14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="5">
         <v>0</v>
@@ -2477,9 +2510,11 @@
         <v>0</v>
       </c>
       <c r="K14" s="5">
-        <v>10204</v>
-      </c>
-      <c r="L14" s="4"/>
+        <v>10203</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
@@ -2489,15 +2524,15 @@
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
     </row>
-    <row r="15" ht="138" spans="1:20">
+    <row r="15" ht="69" spans="1:20">
       <c r="A15" s="5">
-        <v>10204</v>
+        <v>10203</v>
       </c>
       <c r="B15" s="5">
         <v>0</v>
       </c>
       <c r="C15" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D15" s="5">
         <v>1</v>
@@ -2512,18 +2547,18 @@
         <v>0</v>
       </c>
       <c r="H15" s="5">
-        <v>5</v>
-      </c>
-      <c r="I15" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="J15" s="5">
         <v>0</v>
       </c>
       <c r="K15" s="5">
-        <v>10205</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>62</v>
-      </c>
+        <v>10204</v>
+      </c>
+      <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
@@ -2535,13 +2570,13 @@
     </row>
     <row r="16" ht="138" spans="1:20">
       <c r="A16" s="5">
-        <v>10205</v>
+        <v>10204</v>
       </c>
       <c r="B16" s="5">
         <v>0</v>
       </c>
       <c r="C16" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D16" s="5">
         <v>1</v>
@@ -2556,18 +2591,18 @@
         <v>0</v>
       </c>
       <c r="H16" s="5">
-        <v>0</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>63</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="I16" s="4"/>
       <c r="J16" s="5">
         <v>0</v>
       </c>
       <c r="K16" s="5">
-        <v>10206</v>
-      </c>
-      <c r="L16" s="4"/>
+        <v>10205</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>64</v>
+      </c>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
@@ -2577,97 +2612,97 @@
       <c r="S16" s="5"/>
       <c r="T16" s="5"/>
     </row>
-    <row r="17" s="1" customFormat="1" ht="104" spans="1:20">
+    <row r="17" ht="138" spans="1:20">
       <c r="A17" s="5">
+        <v>10205</v>
+      </c>
+      <c r="B17" s="5">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
         <v>10206</v>
       </c>
-      <c r="B17" s="6">
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="104" spans="1:20">
+      <c r="A18" s="5">
+        <v>10206</v>
+      </c>
+      <c r="B18" s="6">
         <v>2</v>
       </c>
-      <c r="C17" s="6">
-        <v>0</v>
-      </c>
-      <c r="D17" s="6">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17" s="6">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6">
-        <v>0</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="J17" s="6">
-        <v>0</v>
-      </c>
-      <c r="K17" s="5">
+      <c r="C18" s="6">
+        <v>0</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" s="6">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6">
+        <v>0</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J18" s="6">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5">
         <v>10207</v>
       </c>
-      <c r="L17" s="4"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="6"/>
-      <c r="T17" s="6"/>
-    </row>
-    <row r="18" ht="35" spans="1:20">
-      <c r="A18" s="5">
-        <v>10207</v>
-      </c>
-      <c r="B18" s="5">
-        <v>0</v>
-      </c>
-      <c r="C18" s="5">
-        <v>0</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G18" s="5">
-        <v>0</v>
-      </c>
-      <c r="H18" s="5">
-        <v>0</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J18" s="5">
-        <v>0</v>
-      </c>
-      <c r="K18" s="5">
-        <v>10208</v>
-      </c>
       <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6"/>
     </row>
     <row r="19" ht="35" spans="1:20">
       <c r="A19" s="5">
-        <v>10208</v>
+        <v>10207</v>
       </c>
       <c r="B19" s="5">
         <v>0</v>
@@ -2691,13 +2726,13 @@
         <v>0</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J19" s="5">
         <v>0</v>
       </c>
       <c r="K19" s="5">
-        <v>0</v>
+        <v>10208</v>
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -2709,27 +2744,27 @@
       <c r="S19" s="5"/>
       <c r="T19" s="5"/>
     </row>
-    <row r="20" ht="69" spans="1:20">
+    <row r="20" ht="35" spans="1:20">
       <c r="A20" s="5">
-        <v>1301</v>
+        <v>10208</v>
       </c>
       <c r="B20" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C20" s="5">
         <v>0</v>
       </c>
       <c r="D20" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G20" s="5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="5">
         <v>0</v>
@@ -2741,7 +2776,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="5">
-        <v>1302</v>
+        <v>0</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -2753,21 +2788,21 @@
       <c r="S20" s="5"/>
       <c r="T20" s="5"/>
     </row>
-    <row r="21" ht="138" spans="1:20">
+    <row r="21" ht="69" spans="1:20">
       <c r="A21" s="5">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B21" s="5">
         <v>7</v>
       </c>
       <c r="C21" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D21" s="5">
         <v>0</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>47</v>
@@ -2776,18 +2811,18 @@
         <v>-1</v>
       </c>
       <c r="H21" s="5">
-        <v>5</v>
-      </c>
-      <c r="I21" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="J21" s="5">
         <v>0</v>
       </c>
       <c r="K21" s="5">
-        <v>0</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>69</v>
-      </c>
+        <v>1302</v>
+      </c>
+      <c r="L21" s="4"/>
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
@@ -2797,21 +2832,21 @@
       <c r="S21" s="5"/>
       <c r="T21" s="5"/>
     </row>
-    <row r="22" ht="69" spans="1:20">
+    <row r="22" ht="138" spans="1:20">
       <c r="A22" s="5">
-        <v>1401</v>
+        <v>1302</v>
       </c>
       <c r="B22" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D22" s="5">
         <v>0</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>47</v>
@@ -2820,18 +2855,18 @@
         <v>-1</v>
       </c>
       <c r="H22" s="5">
-        <v>0</v>
-      </c>
-      <c r="I22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="4"/>
+      <c r="J22" s="5">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5">
+        <v>0</v>
+      </c>
+      <c r="L22" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="J22" s="5">
-        <v>0</v>
-      </c>
-      <c r="K22" s="5">
-        <v>1402</v>
-      </c>
-      <c r="L22" s="4"/>
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
@@ -2841,21 +2876,21 @@
       <c r="S22" s="5"/>
       <c r="T22" s="5"/>
     </row>
-    <row r="23" ht="138" spans="1:20">
+    <row r="23" ht="69" spans="1:20">
       <c r="A23" s="5">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="B23" s="5">
         <v>8</v>
       </c>
       <c r="C23" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D23" s="5">
         <v>0</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>47</v>
@@ -2864,18 +2899,18 @@
         <v>-1</v>
       </c>
       <c r="H23" s="5">
-        <v>5</v>
-      </c>
-      <c r="I23" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>73</v>
+      </c>
       <c r="J23" s="5">
         <v>0</v>
       </c>
       <c r="K23" s="5">
-        <v>0</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>72</v>
-      </c>
+        <v>1402</v>
+      </c>
+      <c r="L23" s="4"/>
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
@@ -2885,21 +2920,21 @@
       <c r="S23" s="5"/>
       <c r="T23" s="5"/>
     </row>
-    <row r="24" ht="104" spans="1:20">
+    <row r="24" ht="138" spans="1:20">
       <c r="A24" s="5">
-        <v>1501</v>
+        <v>1402</v>
       </c>
       <c r="B24" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D24" s="5">
         <v>0</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>47</v>
@@ -2910,16 +2945,16 @@
       <c r="H24" s="5">
         <v>5</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="4"/>
+      <c r="J24" s="5">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5">
+        <v>0</v>
+      </c>
+      <c r="L24" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J24" s="5">
-        <v>0</v>
-      </c>
-      <c r="K24" s="5">
-        <v>1502</v>
-      </c>
-      <c r="L24" s="4"/>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
@@ -2929,21 +2964,21 @@
       <c r="S24" s="5"/>
       <c r="T24" s="5"/>
     </row>
-    <row r="25" ht="172" spans="1:20">
+    <row r="25" ht="104" spans="1:20">
       <c r="A25" s="5">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="B25" s="5">
         <v>9</v>
       </c>
       <c r="C25" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D25" s="5">
         <v>0</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>47</v>
@@ -2954,16 +2989,16 @@
       <c r="H25" s="5">
         <v>5</v>
       </c>
-      <c r="I25" s="4"/>
+      <c r="I25" s="4" t="s">
+        <v>76</v>
+      </c>
       <c r="J25" s="5">
         <v>0</v>
       </c>
       <c r="K25" s="5">
-        <v>0</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>75</v>
-      </c>
+        <v>1502</v>
+      </c>
+      <c r="L25" s="4"/>
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
       <c r="O25" s="4"/>
@@ -2973,21 +3008,21 @@
       <c r="S25" s="5"/>
       <c r="T25" s="5"/>
     </row>
-    <row r="26" ht="104" spans="1:20">
+    <row r="26" ht="172" spans="1:20">
       <c r="A26" s="5">
-        <v>1601</v>
+        <v>1502</v>
       </c>
       <c r="B26" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D26" s="5">
         <v>0</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>47</v>
@@ -2996,18 +3031,18 @@
         <v>-1</v>
       </c>
       <c r="H26" s="5">
-        <v>0</v>
-      </c>
-      <c r="I26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="4"/>
+      <c r="J26" s="5">
+        <v>0</v>
+      </c>
+      <c r="K26" s="5">
+        <v>0</v>
+      </c>
+      <c r="L26" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="J26" s="5">
-        <v>0</v>
-      </c>
-      <c r="K26" s="5">
-        <v>0</v>
-      </c>
-      <c r="L26" s="4"/>
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
@@ -3017,12 +3052,12 @@
       <c r="S26" s="5"/>
       <c r="T26" s="5"/>
     </row>
-    <row r="27" ht="69" spans="1:20">
+    <row r="27" ht="104" spans="1:20">
       <c r="A27" s="5">
-        <v>1701</v>
+        <v>1601</v>
       </c>
       <c r="B27" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C27" s="5">
         <v>0</v>
@@ -3063,10 +3098,10 @@
     </row>
     <row r="28" ht="69" spans="1:20">
       <c r="A28" s="5">
-        <v>10301</v>
+        <v>1701</v>
       </c>
       <c r="B28" s="5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C28" s="5">
         <v>0</v>
@@ -3074,20 +3109,20 @@
       <c r="D28" s="5">
         <v>0</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G28" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H28" s="6">
+      <c r="E28" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G28" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H28" s="5">
         <v>0</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J28" s="5">
         <v>0</v>
@@ -3105,29 +3140,29 @@
       <c r="S28" s="5"/>
       <c r="T28" s="5"/>
     </row>
-    <row r="29" ht="104" spans="1:20">
+    <row r="29" ht="69" spans="1:20">
       <c r="A29" s="5">
-        <v>10401</v>
+        <v>10301</v>
       </c>
       <c r="B29" s="5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C29" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="5">
         <v>0</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G29" s="5">
-        <v>-1</v>
-      </c>
-      <c r="H29" s="5">
+      <c r="E29" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29" s="6">
+        <v>-1</v>
+      </c>
+      <c r="H29" s="6">
         <v>0</v>
       </c>
       <c r="I29" s="4" t="s">
@@ -3137,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="5">
-        <v>10402</v>
+        <v>0</v>
       </c>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -3151,16 +3186,16 @@
     </row>
     <row r="30" ht="104" spans="1:20">
       <c r="A30" s="5">
-        <v>10402</v>
+        <v>10401</v>
       </c>
       <c r="B30" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C30" s="5">
         <v>1</v>
       </c>
       <c r="D30" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>83</v>
@@ -3181,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="5">
-        <v>10404</v>
+        <v>10402</v>
       </c>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -3193,9 +3228,9 @@
       <c r="S30" s="5"/>
       <c r="T30" s="5"/>
     </row>
-    <row r="31" ht="138" spans="1:20">
+    <row r="31" ht="104" spans="1:20">
       <c r="A31" s="5">
-        <v>10404</v>
+        <v>10402</v>
       </c>
       <c r="B31" s="5">
         <v>13</v>
@@ -3207,7 +3242,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>47</v>
@@ -3219,13 +3254,13 @@
         <v>0</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J31" s="5">
         <v>0</v>
       </c>
       <c r="K31" s="5">
-        <v>10403</v>
+        <v>10404</v>
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -3237,12 +3272,12 @@
       <c r="S31" s="5"/>
       <c r="T31" s="5"/>
     </row>
-    <row r="32" ht="35" spans="1:20">
+    <row r="32" ht="138" spans="1:20">
       <c r="A32" s="5">
-        <v>10403</v>
+        <v>10404</v>
       </c>
       <c r="B32" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C32" s="5">
         <v>1</v>
@@ -3251,7 +3286,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>47</v>
@@ -3263,13 +3298,13 @@
         <v>0</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="J32" s="5">
         <v>0</v>
       </c>
       <c r="K32" s="5">
-        <v>0</v>
+        <v>10403</v>
       </c>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
@@ -3281,23 +3316,23 @@
       <c r="S32" s="5"/>
       <c r="T32" s="5"/>
     </row>
-    <row r="33" ht="104" spans="1:20">
+    <row r="33" ht="35" spans="1:20">
       <c r="A33" s="5">
-        <v>10501</v>
+        <v>10403</v>
       </c>
       <c r="B33" s="5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C33" s="5">
         <v>1</v>
       </c>
       <c r="D33" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F33" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G33" s="5">
@@ -3307,13 +3342,13 @@
         <v>0</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="J33" s="5">
         <v>0</v>
       </c>
       <c r="K33" s="5">
-        <v>10502</v>
+        <v>0</v>
       </c>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
@@ -3327,37 +3362,37 @@
     </row>
     <row r="34" ht="104" spans="1:20">
       <c r="A34" s="5">
+        <v>10501</v>
+      </c>
+      <c r="B34" s="5">
+        <v>3</v>
+      </c>
+      <c r="C34" s="5">
+        <v>1</v>
+      </c>
+      <c r="D34" s="5">
+        <v>0</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G34" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H34" s="5">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="J34" s="5">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5">
         <v>10502</v>
-      </c>
-      <c r="B34" s="5">
-        <v>0</v>
-      </c>
-      <c r="C34" s="5">
-        <v>1</v>
-      </c>
-      <c r="D34" s="5">
-        <v>1</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G34" s="5">
-        <v>-1</v>
-      </c>
-      <c r="H34" s="5">
-        <v>0</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="J34" s="5">
-        <v>0</v>
-      </c>
-      <c r="K34" s="5">
-        <v>0</v>
       </c>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
@@ -3369,200 +3404,198 @@
       <c r="S34" s="5"/>
       <c r="T34" s="5"/>
     </row>
-    <row r="35" s="1" customFormat="1" ht="172" spans="1:20">
-      <c r="A35" s="6">
+    <row r="35" ht="104" spans="1:20">
+      <c r="A35" s="5">
+        <v>10502</v>
+      </c>
+      <c r="B35" s="5">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5">
+        <v>1</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G35" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H35" s="5">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="J35" s="5">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5">
+        <v>10503</v>
+      </c>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="138" spans="1:20">
+      <c r="A36" s="5">
+        <v>10503</v>
+      </c>
+      <c r="B36" s="5">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5">
+        <v>5</v>
+      </c>
+      <c r="D36" s="5">
+        <v>1</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G36" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H36" s="5">
+        <v>0</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="J36" s="5">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5">
+        <v>0</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="172" spans="1:20">
+      <c r="A37" s="6">
+        <v>10550</v>
+      </c>
+      <c r="B37" s="5">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5">
+        <v>5</v>
+      </c>
+      <c r="D37" s="5">
+        <v>0</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G37" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H37" s="5">
+        <v>0</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J37" s="5">
+        <v>0</v>
+      </c>
+      <c r="K37" s="5">
+        <v>0</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="6"/>
+      <c r="R37" s="6"/>
+      <c r="S37" s="6"/>
+      <c r="T37" s="6"/>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="172" spans="1:20">
+      <c r="A38" s="6">
         <v>1801</v>
       </c>
-      <c r="B35" s="6">
-        <v>0</v>
-      </c>
-      <c r="C35" s="6">
-        <v>0</v>
-      </c>
-      <c r="D35" s="6">
-        <v>0</v>
-      </c>
-      <c r="E35" s="6" t="s">
+      <c r="B38" s="6">
+        <v>0</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0</v>
+      </c>
+      <c r="D38" s="6">
+        <v>0</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F38" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G35" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H35" s="6">
-        <v>0</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="J35" s="6">
-        <v>0</v>
-      </c>
-      <c r="K35" s="6">
+      <c r="G38" s="6">
+        <v>-1</v>
+      </c>
+      <c r="H38" s="6">
+        <v>0</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="J38" s="6">
+        <v>0</v>
+      </c>
+      <c r="K38" s="6">
         <v>1802</v>
       </c>
-      <c r="L35" s="4"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
-      <c r="Q35" s="6"/>
-      <c r="R35" s="6"/>
-      <c r="S35" s="6"/>
-      <c r="T35" s="6"/>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="1:20">
-      <c r="A36" s="5">
+      <c r="L38" s="4"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="6"/>
+      <c r="R38" s="6"/>
+      <c r="S38" s="6"/>
+      <c r="T38" s="6"/>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="1:20">
+      <c r="A39" s="5">
         <v>1802</v>
       </c>
-      <c r="B36" s="5">
-        <v>0</v>
-      </c>
-      <c r="C36" s="5">
-        <v>0</v>
-      </c>
-      <c r="D36" s="5">
-        <v>0</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G36" s="5">
-        <v>-1</v>
-      </c>
-      <c r="H36" s="5">
-        <v>0</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="J36" s="5">
-        <v>0</v>
-      </c>
-      <c r="K36" s="5">
-        <v>1803</v>
-      </c>
-      <c r="L36" s="4"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-    </row>
-    <row r="37" customFormat="1" ht="69" spans="1:20">
-      <c r="A37" s="5">
-        <v>1803</v>
-      </c>
-      <c r="B37" s="5">
-        <v>0</v>
-      </c>
-      <c r="C37" s="5">
-        <v>3</v>
-      </c>
-      <c r="D37" s="5">
-        <v>1</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G37" s="5">
-        <v>-1</v>
-      </c>
-      <c r="H37" s="5">
-        <v>0</v>
-      </c>
-      <c r="I37" s="4"/>
-      <c r="J37" s="5">
-        <v>0</v>
-      </c>
-      <c r="K37" s="5">
-        <v>0</v>
-      </c>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="N37" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="O37" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="P37" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="5"/>
-      <c r="S37" s="5"/>
-      <c r="T37" s="5"/>
-    </row>
-    <row r="38" ht="69" spans="1:20">
-      <c r="A38" s="5">
-        <v>10601</v>
-      </c>
-      <c r="B38" s="5">
-        <v>1</v>
-      </c>
-      <c r="C38" s="5">
-        <v>1</v>
-      </c>
-      <c r="D38" s="5">
-        <v>0</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G38" s="5">
-        <v>-1</v>
-      </c>
-      <c r="H38" s="5">
-        <v>0</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="J38" s="5">
-        <v>0</v>
-      </c>
-      <c r="K38" s="5">
-        <v>10602</v>
-      </c>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="5"/>
-      <c r="S38" s="5"/>
-      <c r="T38" s="5"/>
-    </row>
-    <row r="39" ht="35" spans="1:20">
-      <c r="A39" s="5">
-        <v>10602</v>
-      </c>
       <c r="B39" s="5">
         <v>0</v>
       </c>
       <c r="C39" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>42</v>
@@ -3576,64 +3609,70 @@
       <c r="H39" s="5">
         <v>0</v>
       </c>
-      <c r="I39" s="4" t="s">
+      <c r="I39" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J39" s="5">
+        <v>0</v>
+      </c>
+      <c r="K39" s="5">
+        <v>1803</v>
+      </c>
+      <c r="L39" s="4"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="6"/>
+      <c r="R39" s="6"/>
+      <c r="S39" s="6"/>
+      <c r="T39" s="6"/>
+    </row>
+    <row r="40" customFormat="1" ht="69" spans="1:20">
+      <c r="A40" s="5">
+        <v>1803</v>
+      </c>
+      <c r="B40" s="5">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5">
+        <v>3</v>
+      </c>
+      <c r="D40" s="5">
+        <v>1</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G40" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H40" s="5">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4"/>
+      <c r="J40" s="5">
+        <v>0</v>
+      </c>
+      <c r="K40" s="5">
+        <v>0</v>
+      </c>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="N40" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="P40" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="J39" s="5">
-        <v>0</v>
-      </c>
-      <c r="K39" s="5">
-        <v>10603</v>
-      </c>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="5"/>
-      <c r="S39" s="5"/>
-      <c r="T39" s="5"/>
-    </row>
-    <row r="40" ht="69" spans="1:20">
-      <c r="A40" s="5">
-        <v>10603</v>
-      </c>
-      <c r="B40" s="5">
-        <v>1</v>
-      </c>
-      <c r="C40" s="5">
-        <v>1</v>
-      </c>
-      <c r="D40" s="5">
-        <v>1</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G40" s="5">
-        <v>-1</v>
-      </c>
-      <c r="H40" s="5">
-        <v>0</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="J40" s="5">
-        <v>0</v>
-      </c>
-      <c r="K40" s="5">
-        <v>10604</v>
-      </c>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
-      <c r="P40" s="4"/>
       <c r="Q40" s="5"/>
       <c r="R40" s="5"/>
       <c r="S40" s="5"/>
@@ -3641,22 +3680,22 @@
     </row>
     <row r="41" ht="69" spans="1:20">
       <c r="A41" s="5">
-        <v>10604</v>
+        <v>10601</v>
       </c>
       <c r="B41" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="G41" s="5">
         <v>-1</v>
@@ -3665,13 +3704,13 @@
         <v>0</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J41" s="5">
         <v>0</v>
       </c>
       <c r="K41" s="5">
-        <v>0</v>
+        <v>10602</v>
       </c>
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
@@ -3683,18 +3722,18 @@
       <c r="S41" s="5"/>
       <c r="T41" s="5"/>
     </row>
-    <row r="42" ht="69" spans="1:20">
+    <row r="42" ht="35" spans="1:20">
       <c r="A42" s="5">
-        <v>10701</v>
+        <v>10602</v>
       </c>
       <c r="B42" s="5">
         <v>0</v>
       </c>
       <c r="C42" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>42</v>
@@ -3709,13 +3748,13 @@
         <v>0</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J42" s="5">
         <v>0</v>
       </c>
       <c r="K42" s="5">
-        <v>10702</v>
+        <v>10603</v>
       </c>
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
@@ -3729,22 +3768,22 @@
     </row>
     <row r="43" ht="69" spans="1:20">
       <c r="A43" s="5">
-        <v>10702</v>
+        <v>10603</v>
       </c>
       <c r="B43" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" s="5">
         <v>1</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="G43" s="5">
         <v>-1</v>
@@ -3753,13 +3792,13 @@
         <v>0</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J43" s="5">
         <v>0</v>
       </c>
       <c r="K43" s="5">
-        <v>10703</v>
+        <v>10604</v>
       </c>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
@@ -3771,9 +3810,9 @@
       <c r="S43" s="5"/>
       <c r="T43" s="5"/>
     </row>
-    <row r="44" ht="138" spans="1:20">
+    <row r="44" ht="69" spans="1:20">
       <c r="A44" s="5">
-        <v>10703</v>
+        <v>10604</v>
       </c>
       <c r="B44" s="5">
         <v>0</v>
@@ -3797,13 +3836,13 @@
         <v>0</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J44" s="5">
         <v>0</v>
       </c>
       <c r="K44" s="5">
-        <v>10704</v>
+        <v>0</v>
       </c>
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
@@ -3817,7 +3856,7 @@
     </row>
     <row r="45" ht="69" spans="1:20">
       <c r="A45" s="5">
-        <v>10704</v>
+        <v>10701</v>
       </c>
       <c r="B45" s="5">
         <v>0</v>
@@ -3826,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>42</v>
@@ -3841,13 +3880,13 @@
         <v>0</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J45" s="5">
         <v>0</v>
       </c>
       <c r="K45" s="5">
-        <v>0</v>
+        <v>10702</v>
       </c>
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
@@ -3861,7 +3900,7 @@
     </row>
     <row r="46" ht="69" spans="1:20">
       <c r="A46" s="5">
-        <v>10801</v>
+        <v>10702</v>
       </c>
       <c r="B46" s="5">
         <v>0</v>
@@ -3870,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>42</v>
@@ -3885,13 +3924,13 @@
         <v>0</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J46" s="5">
         <v>0</v>
       </c>
       <c r="K46" s="5">
-        <v>10802</v>
+        <v>10703</v>
       </c>
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
@@ -3905,16 +3944,16 @@
     </row>
     <row r="47" ht="138" spans="1:20">
       <c r="A47" s="5">
-        <v>10802</v>
+        <v>10703</v>
       </c>
       <c r="B47" s="5">
         <v>0</v>
       </c>
       <c r="C47" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D47" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>42</v>
@@ -3926,18 +3965,18 @@
         <v>-1</v>
       </c>
       <c r="H47" s="5">
-        <v>-10</v>
-      </c>
-      <c r="I47" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>107</v>
+      </c>
       <c r="J47" s="5">
         <v>0</v>
       </c>
       <c r="K47" s="5">
-        <v>10803</v>
-      </c>
-      <c r="L47" s="4" t="s">
-        <v>106</v>
-      </c>
+        <v>10704</v>
+      </c>
+      <c r="L47" s="4"/>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
@@ -3949,7 +3988,7 @@
     </row>
     <row r="48" ht="69" spans="1:20">
       <c r="A48" s="5">
-        <v>10803</v>
+        <v>10704</v>
       </c>
       <c r="B48" s="5">
         <v>0</v>
@@ -3973,13 +4012,13 @@
         <v>0</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J48" s="5">
         <v>0</v>
       </c>
       <c r="K48" s="5">
-        <v>10804</v>
+        <v>0</v>
       </c>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
@@ -3993,7 +4032,7 @@
     </row>
     <row r="49" ht="69" spans="1:20">
       <c r="A49" s="5">
-        <v>10804</v>
+        <v>10801</v>
       </c>
       <c r="B49" s="5">
         <v>0</v>
@@ -4002,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="D49" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>42</v>
@@ -4017,13 +4056,13 @@
         <v>0</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J49" s="5">
         <v>0</v>
       </c>
       <c r="K49" s="5">
-        <v>0</v>
+        <v>10802</v>
       </c>
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
@@ -4035,15 +4074,15 @@
       <c r="S49" s="5"/>
       <c r="T49" s="5"/>
     </row>
-    <row r="50" ht="104" spans="1:20">
+    <row r="50" ht="138" spans="1:20">
       <c r="A50" s="5">
-        <v>10901</v>
+        <v>10802</v>
       </c>
       <c r="B50" s="5">
         <v>0</v>
       </c>
       <c r="C50" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D50" s="5">
         <v>0</v>
@@ -4058,18 +4097,18 @@
         <v>-1</v>
       </c>
       <c r="H50" s="5">
-        <v>0</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>108</v>
-      </c>
+        <v>-10</v>
+      </c>
+      <c r="I50" s="4"/>
       <c r="J50" s="5">
         <v>0</v>
       </c>
       <c r="K50" s="5">
-        <v>10902</v>
-      </c>
-      <c r="L50" s="4"/>
+        <v>10803</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>110</v>
+      </c>
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
@@ -4079,15 +4118,15 @@
       <c r="S50" s="5"/>
       <c r="T50" s="5"/>
     </row>
-    <row r="51" ht="104" spans="1:20">
+    <row r="51" ht="69" spans="1:20">
       <c r="A51" s="5">
-        <v>10902</v>
+        <v>10803</v>
       </c>
       <c r="B51" s="5">
         <v>0</v>
       </c>
       <c r="C51" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" s="5">
         <v>1</v>
@@ -4105,13 +4144,13 @@
         <v>0</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J51" s="5">
         <v>0</v>
       </c>
       <c r="K51" s="5">
-        <v>10903</v>
+        <v>10804</v>
       </c>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
@@ -4123,15 +4162,15 @@
       <c r="S51" s="5"/>
       <c r="T51" s="5"/>
     </row>
-    <row r="52" ht="104" spans="1:20">
+    <row r="52" ht="69" spans="1:20">
       <c r="A52" s="5">
-        <v>10903</v>
+        <v>10804</v>
       </c>
       <c r="B52" s="5">
         <v>0</v>
       </c>
       <c r="C52" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52" s="5">
         <v>1</v>
@@ -4149,13 +4188,13 @@
         <v>0</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="J52" s="5">
         <v>0</v>
       </c>
       <c r="K52" s="5">
-        <v>10904</v>
+        <v>0</v>
       </c>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
@@ -4167,9 +4206,9 @@
       <c r="S52" s="5"/>
       <c r="T52" s="5"/>
     </row>
-    <row r="53" ht="69" spans="1:20">
+    <row r="53" ht="104" spans="1:20">
       <c r="A53" s="5">
-        <v>10904</v>
+        <v>10901</v>
       </c>
       <c r="B53" s="5">
         <v>0</v>
@@ -4178,7 +4217,7 @@
         <v>1</v>
       </c>
       <c r="D53" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>42</v>
@@ -4193,13 +4232,13 @@
         <v>0</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J53" s="5">
         <v>0</v>
       </c>
       <c r="K53" s="5">
-        <v>10905</v>
+        <v>10902</v>
       </c>
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
@@ -4211,12 +4250,12 @@
       <c r="S53" s="5"/>
       <c r="T53" s="5"/>
     </row>
-    <row r="54" ht="138" spans="1:20">
+    <row r="54" ht="104" spans="1:20">
       <c r="A54" s="5">
-        <v>10905</v>
+        <v>10902</v>
       </c>
       <c r="B54" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C54" s="5">
         <v>1</v>
@@ -4224,11 +4263,11 @@
       <c r="D54" s="5">
         <v>1</v>
       </c>
-      <c r="E54" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>57</v>
+      <c r="E54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G54" s="5">
         <v>-1</v>
@@ -4237,13 +4276,13 @@
         <v>0</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J54" s="5">
         <v>0</v>
       </c>
       <c r="K54" s="5">
-        <v>10906</v>
+        <v>10903</v>
       </c>
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
@@ -4255,9 +4294,9 @@
       <c r="S54" s="5"/>
       <c r="T54" s="5"/>
     </row>
-    <row r="55" ht="138" spans="1:20">
+    <row r="55" ht="104" spans="1:20">
       <c r="A55" s="5">
-        <v>10906</v>
+        <v>10903</v>
       </c>
       <c r="B55" s="5">
         <v>0</v>
@@ -4281,13 +4320,13 @@
         <v>0</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J55" s="5">
         <v>0</v>
       </c>
       <c r="K55" s="5">
-        <v>10907</v>
+        <v>10904</v>
       </c>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
@@ -4301,10 +4340,10 @@
     </row>
     <row r="56" ht="69" spans="1:20">
       <c r="A56" s="5">
-        <v>10907</v>
+        <v>10904</v>
       </c>
       <c r="B56" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C56" s="5">
         <v>1</v>
@@ -4312,11 +4351,11 @@
       <c r="D56" s="5">
         <v>1</v>
       </c>
-      <c r="E56" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>57</v>
+      <c r="E56" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G56" s="5">
         <v>-1</v>
@@ -4325,13 +4364,13 @@
         <v>0</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J56" s="5">
         <v>0</v>
       </c>
       <c r="K56" s="5">
-        <v>10908</v>
+        <v>10905</v>
       </c>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
@@ -4343,12 +4382,12 @@
       <c r="S56" s="5"/>
       <c r="T56" s="5"/>
     </row>
-    <row r="57" ht="69" spans="1:20">
+    <row r="57" ht="138" spans="1:20">
       <c r="A57" s="5">
-        <v>10908</v>
+        <v>10905</v>
       </c>
       <c r="B57" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C57" s="5">
         <v>1</v>
@@ -4356,11 +4395,11 @@
       <c r="D57" s="5">
         <v>1</v>
       </c>
-      <c r="E57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>43</v>
+      <c r="E57" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="G57" s="5">
         <v>-1</v>
@@ -4369,13 +4408,13 @@
         <v>0</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J57" s="5">
         <v>0</v>
       </c>
       <c r="K57" s="5">
-        <v>10909</v>
+        <v>10906</v>
       </c>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
@@ -4387,9 +4426,9 @@
       <c r="S57" s="5"/>
       <c r="T57" s="5"/>
     </row>
-    <row r="58" ht="104" spans="1:20">
+    <row r="58" ht="138" spans="1:20">
       <c r="A58" s="5">
-        <v>10909</v>
+        <v>10906</v>
       </c>
       <c r="B58" s="5">
         <v>0</v>
@@ -4413,13 +4452,13 @@
         <v>0</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J58" s="5">
         <v>0</v>
       </c>
       <c r="K58" s="5">
-        <v>10910</v>
+        <v>10907</v>
       </c>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
@@ -4431,9 +4470,9 @@
       <c r="S58" s="5"/>
       <c r="T58" s="5"/>
     </row>
-    <row r="59" ht="104" spans="1:20">
+    <row r="59" ht="69" spans="1:20">
       <c r="A59" s="5">
-        <v>10910</v>
+        <v>10907</v>
       </c>
       <c r="B59" s="5">
         <v>2</v>
@@ -4445,10 +4484,10 @@
         <v>1</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G59" s="5">
         <v>-1</v>
@@ -4457,13 +4496,13 @@
         <v>0</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J59" s="5">
         <v>0</v>
       </c>
       <c r="K59" s="5">
-        <v>10911</v>
+        <v>10908</v>
       </c>
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
@@ -4477,7 +4516,7 @@
     </row>
     <row r="60" ht="69" spans="1:20">
       <c r="A60" s="5">
-        <v>10911</v>
+        <v>10908</v>
       </c>
       <c r="B60" s="5">
         <v>0</v>
@@ -4501,13 +4540,13 @@
         <v>0</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J60" s="5">
         <v>0</v>
       </c>
       <c r="K60" s="5">
-        <v>0</v>
+        <v>10909</v>
       </c>
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
@@ -4521,22 +4560,22 @@
     </row>
     <row r="61" ht="104" spans="1:20">
       <c r="A61" s="5">
-        <v>11001</v>
+        <v>10909</v>
       </c>
       <c r="B61" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" s="5">
         <v>1</v>
       </c>
       <c r="D61" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="G61" s="5">
         <v>-1</v>
@@ -4545,13 +4584,13 @@
         <v>0</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J61" s="5">
         <v>0</v>
       </c>
       <c r="K61" s="5">
-        <v>11002</v>
+        <v>10910</v>
       </c>
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
@@ -4563,12 +4602,12 @@
       <c r="S61" s="5"/>
       <c r="T61" s="5"/>
     </row>
-    <row r="62" ht="35" spans="1:20">
+    <row r="62" ht="104" spans="1:20">
       <c r="A62" s="5">
-        <v>11002</v>
+        <v>10910</v>
       </c>
       <c r="B62" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C62" s="5">
         <v>1</v>
@@ -4576,11 +4615,11 @@
       <c r="D62" s="5">
         <v>1</v>
       </c>
-      <c r="E62" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>43</v>
+      <c r="E62" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G62" s="5">
         <v>-1</v>
@@ -4589,13 +4628,13 @@
         <v>0</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="J62" s="5">
         <v>0</v>
       </c>
       <c r="K62" s="5">
-        <v>0</v>
+        <v>10911</v>
       </c>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
@@ -4607,9 +4646,9 @@
       <c r="S62" s="5"/>
       <c r="T62" s="5"/>
     </row>
-    <row r="63" ht="104" spans="1:20">
+    <row r="63" ht="69" spans="1:20">
       <c r="A63" s="5">
-        <v>11101</v>
+        <v>10911</v>
       </c>
       <c r="B63" s="5">
         <v>0</v>
@@ -4618,7 +4657,7 @@
         <v>1</v>
       </c>
       <c r="D63" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>42</v>
@@ -4633,13 +4672,13 @@
         <v>0</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J63" s="5">
         <v>0</v>
       </c>
       <c r="K63" s="5">
-        <v>11102</v>
+        <v>10912</v>
       </c>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
@@ -4651,24 +4690,24 @@
       <c r="S63" s="5"/>
       <c r="T63" s="5"/>
     </row>
-    <row r="64" ht="69" spans="1:20">
+    <row r="64" ht="104" spans="1:20">
       <c r="A64" s="5">
-        <v>11102</v>
+        <v>10912</v>
       </c>
       <c r="B64" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C64" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D64" s="5">
         <v>1</v>
       </c>
-      <c r="E64" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>57</v>
+      <c r="E64" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G64" s="5">
         <v>-1</v>
@@ -4677,15 +4716,17 @@
         <v>0</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J64" s="5">
         <v>0</v>
       </c>
       <c r="K64" s="5">
-        <v>11103</v>
-      </c>
-      <c r="L64" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
@@ -4695,41 +4736,41 @@
       <c r="S64" s="5"/>
       <c r="T64" s="5"/>
     </row>
-    <row r="65" ht="172" spans="1:20">
+    <row r="65" ht="104" spans="1:20">
       <c r="A65" s="5">
-        <v>11103</v>
+        <v>11001</v>
       </c>
       <c r="B65" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C65" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D65" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="G65" s="5">
         <v>-1</v>
       </c>
       <c r="H65" s="5">
-        <v>-5</v>
-      </c>
-      <c r="I65" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="J65" s="5">
         <v>0</v>
       </c>
       <c r="K65" s="5">
-        <v>0</v>
-      </c>
-      <c r="L65" s="4" t="s">
-        <v>122</v>
-      </c>
+        <v>11002</v>
+      </c>
+      <c r="L65" s="4"/>
       <c r="M65" s="4"/>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
@@ -4739,24 +4780,24 @@
       <c r="S65" s="5"/>
       <c r="T65" s="5"/>
     </row>
-    <row r="66" ht="104" spans="1:20">
+    <row r="66" ht="35" spans="1:20">
       <c r="A66" s="5">
-        <v>1901</v>
+        <v>11002</v>
       </c>
       <c r="B66" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C66" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G66" s="5">
         <v>-1</v>
@@ -4765,13 +4806,13 @@
         <v>0</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="J66" s="5">
         <v>0</v>
       </c>
       <c r="K66" s="5">
-        <v>1902</v>
+        <v>0</v>
       </c>
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
@@ -4783,41 +4824,41 @@
       <c r="S66" s="5"/>
       <c r="T66" s="5"/>
     </row>
-    <row r="67" ht="138" spans="1:20">
+    <row r="67" ht="104" spans="1:20">
       <c r="A67" s="5">
-        <v>1902</v>
+        <v>11101</v>
       </c>
       <c r="B67" s="5">
         <v>0</v>
       </c>
       <c r="C67" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D67" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G67" s="5">
         <v>-1</v>
       </c>
       <c r="H67" s="5">
-        <v>-5</v>
-      </c>
-      <c r="I67" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="J67" s="5">
         <v>0</v>
       </c>
       <c r="K67" s="5">
-        <v>0</v>
-      </c>
-      <c r="L67" s="4" t="s">
-        <v>124</v>
-      </c>
+        <v>11102</v>
+      </c>
+      <c r="L67" s="4"/>
       <c r="M67" s="4"/>
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
@@ -4827,24 +4868,24 @@
       <c r="S67" s="5"/>
       <c r="T67" s="5"/>
     </row>
-    <row r="68" ht="104" spans="1:20">
+    <row r="68" ht="69" spans="1:20">
       <c r="A68" s="5">
-        <v>11201</v>
+        <v>11102</v>
       </c>
       <c r="B68" s="5">
         <v>2</v>
       </c>
       <c r="C68" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G68" s="5">
         <v>-1</v>
@@ -4853,13 +4894,13 @@
         <v>0</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J68" s="5">
         <v>0</v>
       </c>
       <c r="K68" s="5">
-        <v>11202</v>
+        <v>11103</v>
       </c>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
@@ -4871,15 +4912,15 @@
       <c r="S68" s="5"/>
       <c r="T68" s="5"/>
     </row>
-    <row r="69" ht="69" spans="1:20">
+    <row r="69" ht="172" spans="1:20">
       <c r="A69" s="5">
-        <v>11202</v>
+        <v>11103</v>
       </c>
       <c r="B69" s="5">
         <v>0</v>
       </c>
       <c r="C69" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D69" s="5">
         <v>1</v>
@@ -4891,21 +4932,21 @@
         <v>43</v>
       </c>
       <c r="G69" s="5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H69" s="5">
-        <v>0</v>
-      </c>
-      <c r="I69" s="4" t="s">
-        <v>126</v>
-      </c>
+        <v>-5</v>
+      </c>
+      <c r="I69" s="4"/>
       <c r="J69" s="5">
         <v>0</v>
       </c>
       <c r="K69" s="5">
-        <v>11203</v>
-      </c>
-      <c r="L69" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
@@ -4915,24 +4956,24 @@
       <c r="S69" s="5"/>
       <c r="T69" s="5"/>
     </row>
-    <row r="70" ht="104" spans="1:20">
+    <row r="70" ht="172" spans="1:20">
       <c r="A70" s="5">
-        <v>11203</v>
+        <v>11150</v>
       </c>
       <c r="B70" s="5">
         <v>0</v>
       </c>
       <c r="C70" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D70" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G70" s="5">
         <v>-1</v>
@@ -4941,7 +4982,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J70" s="5">
         <v>0</v>
@@ -4949,7 +4990,9 @@
       <c r="K70" s="5">
         <v>0</v>
       </c>
-      <c r="L70" s="4"/>
+      <c r="L70" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="M70" s="4"/>
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
@@ -4959,24 +5002,24 @@
       <c r="S70" s="5"/>
       <c r="T70" s="5"/>
     </row>
-    <row r="71" ht="69" spans="1:20">
+    <row r="71" ht="104" spans="1:20">
       <c r="A71" s="5">
-        <v>11301</v>
+        <v>1901</v>
       </c>
       <c r="B71" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C71" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G71" s="5">
         <v>-1</v>
@@ -4985,13 +5028,13 @@
         <v>0</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J71" s="5">
         <v>0</v>
       </c>
       <c r="K71" s="5">
-        <v>11302</v>
+        <v>1902</v>
       </c>
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
@@ -5003,41 +5046,41 @@
       <c r="S71" s="5"/>
       <c r="T71" s="5"/>
     </row>
-    <row r="72" ht="104" spans="1:20">
+    <row r="72" ht="138" spans="1:20">
       <c r="A72" s="5">
-        <v>11302</v>
+        <v>1902</v>
       </c>
       <c r="B72" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C72" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D72" s="5">
         <v>1</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F72" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F72" s="5" t="s">
         <v>47</v>
       </c>
       <c r="G72" s="5">
         <v>-1</v>
       </c>
       <c r="H72" s="5">
-        <v>0</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>129</v>
-      </c>
+        <v>-5</v>
+      </c>
+      <c r="I72" s="4"/>
       <c r="J72" s="5">
         <v>0</v>
       </c>
       <c r="K72" s="5">
-        <v>11303</v>
-      </c>
-      <c r="L72" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="L72" s="4" t="s">
+        <v>130</v>
+      </c>
       <c r="M72" s="4"/>
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
@@ -5047,39 +5090,39 @@
       <c r="S72" s="5"/>
       <c r="T72" s="5"/>
     </row>
-    <row r="73" ht="69" spans="1:20">
+    <row r="73" ht="104" spans="1:20">
       <c r="A73" s="5">
-        <v>11303</v>
+        <v>11201</v>
       </c>
       <c r="B73" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C73" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D73" s="5">
-        <v>1</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>43</v>
+        <v>0</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G73" s="5">
         <v>-1</v>
       </c>
       <c r="H73" s="5">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J73" s="5">
         <v>0</v>
       </c>
       <c r="K73" s="5">
-        <v>11304</v>
+        <v>11202</v>
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
@@ -5091,39 +5134,39 @@
       <c r="S73" s="5"/>
       <c r="T73" s="5"/>
     </row>
-    <row r="74" ht="207" spans="1:20">
+    <row r="74" ht="69" spans="1:20">
       <c r="A74" s="5">
-        <v>11304</v>
+        <v>11202</v>
       </c>
       <c r="B74" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C74" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74" s="5">
         <v>1</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G74" s="5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H74" s="5">
         <v>0</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J74" s="5">
         <v>0</v>
       </c>
       <c r="K74" s="5">
-        <v>11305</v>
+        <v>11203</v>
       </c>
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
@@ -5135,41 +5178,41 @@
       <c r="S74" s="5"/>
       <c r="T74" s="5"/>
     </row>
-    <row r="75" ht="138" spans="1:20">
+    <row r="75" ht="207" spans="1:20">
       <c r="A75" s="5">
-        <v>11305</v>
+        <v>11203</v>
       </c>
       <c r="B75" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C75" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D75" s="5">
         <v>1</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G75" s="5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="H75" s="5">
         <v>0</v>
       </c>
-      <c r="I75" s="4" t="s">
-        <v>132</v>
-      </c>
+      <c r="I75" s="4"/>
       <c r="J75" s="5">
         <v>0</v>
       </c>
       <c r="K75" s="5">
-        <v>11306</v>
-      </c>
-      <c r="L75" s="4"/>
+        <v>11204</v>
+      </c>
+      <c r="L75" s="4" t="s">
+        <v>133</v>
+      </c>
       <c r="M75" s="4"/>
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
@@ -5179,24 +5222,24 @@
       <c r="S75" s="5"/>
       <c r="T75" s="5"/>
     </row>
-    <row r="76" ht="138" spans="1:20">
+    <row r="76" ht="104" spans="1:20">
       <c r="A76" s="5">
-        <v>11306</v>
+        <v>11204</v>
       </c>
       <c r="B76" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C76" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76" s="5">
         <v>1</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G76" s="5">
         <v>-1</v>
@@ -5205,13 +5248,13 @@
         <v>0</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J76" s="5">
         <v>0</v>
       </c>
       <c r="K76" s="5">
-        <v>0</v>
+        <v>11205</v>
       </c>
       <c r="L76" s="4"/>
       <c r="M76" s="4"/>
@@ -5223,24 +5266,24 @@
       <c r="S76" s="5"/>
       <c r="T76" s="5"/>
     </row>
-    <row r="77" ht="69" spans="1:20">
+    <row r="77" ht="104" spans="1:20">
       <c r="A77" s="5">
-        <v>2001</v>
+        <v>11205</v>
       </c>
       <c r="B77" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C77" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D77" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G77" s="5">
         <v>-1</v>
@@ -5249,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J77" s="5">
         <v>0</v>
@@ -5257,7 +5300,9 @@
       <c r="K77" s="5">
         <v>0</v>
       </c>
-      <c r="L77" s="4"/>
+      <c r="L77" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="M77" s="4"/>
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
@@ -5269,10 +5314,10 @@
     </row>
     <row r="78" ht="69" spans="1:20">
       <c r="A78" s="5">
-        <v>2101</v>
+        <v>11301</v>
       </c>
       <c r="B78" s="5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C78" s="5">
         <v>0</v>
@@ -5281,10 +5326,10 @@
         <v>0</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G78" s="5">
         <v>-1</v>
@@ -5299,7 +5344,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="5">
-        <v>0</v>
+        <v>11302</v>
       </c>
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
@@ -5311,21 +5356,21 @@
       <c r="S78" s="5"/>
       <c r="T78" s="5"/>
     </row>
-    <row r="79" ht="35" spans="1:20">
+    <row r="79" ht="104" spans="1:20">
       <c r="A79" s="5">
-        <v>2201</v>
+        <v>11302</v>
       </c>
       <c r="B79" s="5">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C79" s="5">
         <v>0</v>
       </c>
       <c r="D79" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>47</v>
@@ -5337,13 +5382,13 @@
         <v>0</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J79" s="5">
         <v>0</v>
       </c>
       <c r="K79" s="5">
-        <v>0</v>
+        <v>11303</v>
       </c>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
@@ -5355,24 +5400,24 @@
       <c r="S79" s="5"/>
       <c r="T79" s="5"/>
     </row>
-    <row r="80" ht="104" spans="1:20">
+    <row r="80" ht="69" spans="1:20">
       <c r="A80" s="5">
-        <v>2301</v>
+        <v>11303</v>
       </c>
       <c r="B80" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C80" s="5">
         <v>0</v>
       </c>
       <c r="D80" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G80" s="5">
         <v>-1</v>
@@ -5381,13 +5426,13 @@
         <v>0</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="J80" s="5">
         <v>0</v>
       </c>
       <c r="K80" s="5">
-        <v>0</v>
+        <v>11304</v>
       </c>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
@@ -5399,41 +5444,41 @@
       <c r="S80" s="5"/>
       <c r="T80" s="5"/>
     </row>
-    <row r="81" ht="69" spans="1:20">
+    <row r="81" ht="138" spans="1:20">
       <c r="A81" s="5">
-        <v>11401</v>
+        <v>11304</v>
       </c>
       <c r="B81" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C81" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D81" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="G81" s="5">
         <v>-1</v>
       </c>
       <c r="H81" s="5">
-        <v>0</v>
-      </c>
-      <c r="I81" s="4" t="s">
+        <v>-5</v>
+      </c>
+      <c r="I81" s="4"/>
+      <c r="J81" s="5">
+        <v>0</v>
+      </c>
+      <c r="K81" s="5">
+        <v>11305</v>
+      </c>
+      <c r="L81" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="J81" s="5">
-        <v>0</v>
-      </c>
-      <c r="K81" s="5">
-        <v>11402</v>
-      </c>
-      <c r="L81" s="4"/>
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
@@ -5443,24 +5488,24 @@
       <c r="S81" s="5"/>
       <c r="T81" s="5"/>
     </row>
-    <row r="82" ht="104" spans="1:20">
+    <row r="82" ht="207" spans="1:20">
       <c r="A82" s="5">
-        <v>11402</v>
+        <v>11305</v>
       </c>
       <c r="B82" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C82" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D82" s="5">
         <v>1</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>43</v>
+        <v>83</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="G82" s="5">
         <v>-1</v>
@@ -5475,7 +5520,7 @@
         <v>0</v>
       </c>
       <c r="K82" s="5">
-        <v>0</v>
+        <v>11306</v>
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
@@ -5487,21 +5532,21 @@
       <c r="S82" s="5"/>
       <c r="T82" s="5"/>
     </row>
-    <row r="83" ht="104" spans="1:20">
+    <row r="83" ht="138" spans="1:20">
       <c r="A83" s="5">
-        <v>11501</v>
+        <v>11306</v>
       </c>
       <c r="B83" s="5">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C83" s="5">
         <v>1</v>
       </c>
       <c r="D83" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>47</v>
@@ -5513,13 +5558,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J83" s="5">
         <v>0</v>
       </c>
       <c r="K83" s="5">
-        <v>11502</v>
+        <v>11307</v>
       </c>
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
@@ -5533,10 +5578,10 @@
     </row>
     <row r="84" ht="138" spans="1:20">
       <c r="A84" s="5">
-        <v>11502</v>
+        <v>11307</v>
       </c>
       <c r="B84" s="5">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C84" s="5">
         <v>1</v>
@@ -5544,11 +5589,11 @@
       <c r="D84" s="5">
         <v>1</v>
       </c>
-      <c r="E84" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>57</v>
+      <c r="E84" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="G84" s="5">
         <v>-1</v>
@@ -5557,13 +5602,13 @@
         <v>0</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J84" s="5">
         <v>0</v>
       </c>
       <c r="K84" s="5">
-        <v>11503</v>
+        <v>11308</v>
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
@@ -5575,24 +5620,24 @@
       <c r="S84" s="5"/>
       <c r="T84" s="5"/>
     </row>
-    <row r="85" ht="138" spans="1:20">
+    <row r="85" ht="172" spans="1:20">
       <c r="A85" s="5">
-        <v>11503</v>
+        <v>11308</v>
       </c>
       <c r="B85" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C85" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D85" s="5">
         <v>1</v>
       </c>
-      <c r="E85" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>57</v>
+      <c r="E85" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G85" s="5">
         <v>-1</v>
@@ -5601,15 +5646,17 @@
         <v>0</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J85" s="5">
         <v>0</v>
       </c>
       <c r="K85" s="5">
-        <v>11504</v>
-      </c>
-      <c r="L85" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="L85" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="M85" s="4"/>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
@@ -5619,24 +5666,24 @@
       <c r="S85" s="5"/>
       <c r="T85" s="5"/>
     </row>
-    <row r="86" ht="35" spans="1:20">
+    <row r="86" ht="69" spans="1:20">
       <c r="A86" s="5">
-        <v>11504</v>
+        <v>2001</v>
       </c>
       <c r="B86" s="5">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C86" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86" s="5">
-        <v>1</v>
-      </c>
-      <c r="E86" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F86" s="8" t="s">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="G86" s="5">
         <v>-1</v>
@@ -5645,13 +5692,13 @@
         <v>0</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>65</v>
+        <v>144</v>
       </c>
       <c r="J86" s="5">
         <v>0</v>
       </c>
       <c r="K86" s="5">
-        <v>11505</v>
+        <v>0</v>
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
@@ -5665,22 +5712,22 @@
     </row>
     <row r="87" ht="69" spans="1:20">
       <c r="A87" s="5">
-        <v>11505</v>
+        <v>2101</v>
       </c>
       <c r="B87" s="5">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C87" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87" s="5">
-        <v>1</v>
-      </c>
-      <c r="E87" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F87" s="8" t="s">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="G87" s="5">
         <v>-1</v>
@@ -5689,13 +5736,13 @@
         <v>0</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J87" s="5">
         <v>0</v>
       </c>
       <c r="K87" s="5">
-        <v>11506</v>
+        <v>0</v>
       </c>
       <c r="L87" s="4"/>
       <c r="M87" s="4"/>
@@ -5709,22 +5756,22 @@
     </row>
     <row r="88" ht="35" spans="1:20">
       <c r="A88" s="5">
-        <v>11506</v>
+        <v>2201</v>
       </c>
       <c r="B88" s="5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C88" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88" s="5">
-        <v>1</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F88" s="8" t="s">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="G88" s="5">
         <v>-1</v>
@@ -5733,13 +5780,13 @@
         <v>0</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J88" s="5">
         <v>0</v>
       </c>
       <c r="K88" s="5">
-        <v>11507</v>
+        <v>0</v>
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
@@ -5751,24 +5798,24 @@
       <c r="S88" s="5"/>
       <c r="T88" s="5"/>
     </row>
-    <row r="89" ht="69" spans="1:20">
+    <row r="89" ht="104" spans="1:20">
       <c r="A89" s="5">
-        <v>11507</v>
+        <v>2301</v>
       </c>
       <c r="B89" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C89" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" s="5">
-        <v>1</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F89" s="8" t="s">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="G89" s="5">
         <v>-1</v>
@@ -5777,7 +5824,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>147</v>
+        <v>89</v>
       </c>
       <c r="J89" s="5">
         <v>0</v>
@@ -5795,24 +5842,24 @@
       <c r="S89" s="5"/>
       <c r="T89" s="5"/>
     </row>
-    <row r="90" ht="172" spans="1:20">
+    <row r="90" ht="69" spans="1:20">
       <c r="A90" s="5">
-        <v>11601</v>
+        <v>11401</v>
       </c>
       <c r="B90" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D90" s="5">
         <v>0</v>
       </c>
-      <c r="E90" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F90" s="8" t="s">
-        <v>57</v>
+      <c r="E90" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="G90" s="5">
         <v>-1</v>
@@ -5821,13 +5868,13 @@
         <v>0</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J90" s="5">
         <v>0</v>
       </c>
       <c r="K90" s="5">
-        <v>11602</v>
+        <v>11402</v>
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
@@ -5841,22 +5888,22 @@
     </row>
     <row r="91" ht="104" spans="1:20">
       <c r="A91" s="5">
-        <v>11602</v>
+        <v>11402</v>
       </c>
       <c r="B91" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C91" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D91" s="5">
         <v>1</v>
       </c>
-      <c r="E91" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F91" s="8" t="s">
-        <v>57</v>
+      <c r="E91" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G91" s="5">
         <v>-1</v>
@@ -5865,13 +5912,13 @@
         <v>0</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J91" s="5">
         <v>0</v>
       </c>
       <c r="K91" s="5">
-        <v>11603</v>
+        <v>11403</v>
       </c>
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
@@ -5883,24 +5930,24 @@
       <c r="S91" s="5"/>
       <c r="T91" s="5"/>
     </row>
-    <row r="92" ht="35" spans="1:20">
+    <row r="92" ht="69" spans="1:20">
       <c r="A92" s="5">
-        <v>11603</v>
+        <v>11403</v>
       </c>
       <c r="B92" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C92" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D92" s="5">
         <v>1</v>
       </c>
-      <c r="E92" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F92" s="8" t="s">
-        <v>57</v>
+      <c r="E92" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G92" s="5">
         <v>-1</v>
@@ -5909,15 +5956,17 @@
         <v>0</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="J92" s="5">
         <v>0</v>
       </c>
       <c r="K92" s="5">
-        <v>11604</v>
-      </c>
-      <c r="L92" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="L92" s="4" t="s">
+        <v>151</v>
+      </c>
       <c r="M92" s="4"/>
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
@@ -5929,22 +5978,22 @@
     </row>
     <row r="93" ht="104" spans="1:20">
       <c r="A93" s="5">
-        <v>11604</v>
+        <v>11501</v>
       </c>
       <c r="B93" s="5">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C93" s="5">
         <v>1</v>
       </c>
       <c r="D93" s="5">
-        <v>1</v>
-      </c>
-      <c r="E93" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F93" s="8" t="s">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="G93" s="5">
         <v>-1</v>
@@ -5953,13 +6002,13 @@
         <v>0</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J93" s="5">
         <v>0</v>
       </c>
       <c r="K93" s="5">
-        <v>11605</v>
+        <v>11502</v>
       </c>
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
@@ -5971,9 +6020,9 @@
       <c r="S93" s="5"/>
       <c r="T93" s="5"/>
     </row>
-    <row r="94" ht="35" spans="1:20">
+    <row r="94" ht="138" spans="1:20">
       <c r="A94" s="5">
-        <v>11605</v>
+        <v>11502</v>
       </c>
       <c r="B94" s="5">
         <v>2</v>
@@ -5985,10 +6034,10 @@
         <v>1</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G94" s="5">
         <v>-1</v>
@@ -5997,13 +6046,13 @@
         <v>0</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="J94" s="5">
         <v>0</v>
       </c>
       <c r="K94" s="5">
-        <v>11606</v>
+        <v>11503</v>
       </c>
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
@@ -6015,9 +6064,9 @@
       <c r="S94" s="5"/>
       <c r="T94" s="5"/>
     </row>
-    <row r="95" ht="104" spans="1:20">
+    <row r="95" ht="138" spans="1:20">
       <c r="A95" s="5">
-        <v>11606</v>
+        <v>11503</v>
       </c>
       <c r="B95" s="5">
         <v>2</v>
@@ -6029,10 +6078,10 @@
         <v>1</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G95" s="5">
         <v>-1</v>
@@ -6041,13 +6090,13 @@
         <v>0</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="J95" s="5">
         <v>0</v>
       </c>
       <c r="K95" s="5">
-        <v>0</v>
+        <v>11504</v>
       </c>
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
@@ -6059,24 +6108,24 @@
       <c r="S95" s="5"/>
       <c r="T95" s="5"/>
     </row>
-    <row r="96" ht="104" spans="1:20">
+    <row r="96" ht="35" spans="1:20">
       <c r="A96" s="5">
-        <v>2401</v>
+        <v>11504</v>
       </c>
       <c r="B96" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C96" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96" s="5">
-        <v>0</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G96" s="5">
         <v>-1</v>
@@ -6085,13 +6134,13 @@
         <v>0</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>152</v>
+        <v>67</v>
       </c>
       <c r="J96" s="5">
         <v>0</v>
       </c>
       <c r="K96" s="5">
-        <v>0</v>
+        <v>11505</v>
       </c>
       <c r="L96" s="4"/>
       <c r="M96" s="4"/>
@@ -6103,39 +6152,39 @@
       <c r="S96" s="5"/>
       <c r="T96" s="5"/>
     </row>
-    <row r="97" ht="104" spans="1:20">
+    <row r="97" ht="69" spans="1:20">
       <c r="A97" s="5">
-        <v>11701</v>
+        <v>11505</v>
       </c>
       <c r="B97" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C97" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D97" s="5">
-        <v>0</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G97" s="5">
         <v>-1</v>
       </c>
       <c r="H97" s="5">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J97" s="5">
         <v>0</v>
       </c>
       <c r="K97" s="5">
-        <v>11702</v>
+        <v>11506</v>
       </c>
       <c r="L97" s="4"/>
       <c r="M97" s="4"/>
@@ -6149,22 +6198,22 @@
     </row>
     <row r="98" ht="35" spans="1:20">
       <c r="A98" s="5">
-        <v>11702</v>
+        <v>11506</v>
       </c>
       <c r="B98" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C98" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98" s="5">
         <v>1</v>
       </c>
-      <c r="E98" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>43</v>
+      <c r="E98" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G98" s="5">
         <v>-1</v>
@@ -6173,13 +6222,13 @@
         <v>0</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J98" s="5">
         <v>0</v>
       </c>
       <c r="K98" s="5">
-        <v>11703</v>
+        <v>11507</v>
       </c>
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
@@ -6193,22 +6242,22 @@
     </row>
     <row r="99" ht="69" spans="1:20">
       <c r="A99" s="5">
-        <v>11703</v>
+        <v>11507</v>
       </c>
       <c r="B99" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C99" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D99" s="5">
         <v>1</v>
       </c>
-      <c r="E99" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>43</v>
+      <c r="E99" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G99" s="5">
         <v>-1</v>
@@ -6217,7 +6266,7 @@
         <v>0</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="J99" s="5">
         <v>0</v>
@@ -6235,24 +6284,24 @@
       <c r="S99" s="5"/>
       <c r="T99" s="5"/>
     </row>
-    <row r="100" ht="69" spans="1:20">
+    <row r="100" ht="172" spans="1:20">
       <c r="A100" s="5">
-        <v>2501</v>
+        <v>11601</v>
       </c>
       <c r="B100" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C100" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D100" s="5">
         <v>0</v>
       </c>
-      <c r="E100" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>43</v>
+      <c r="E100" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G100" s="5">
         <v>-1</v>
@@ -6261,13 +6310,13 @@
         <v>0</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J100" s="5">
         <v>0</v>
       </c>
       <c r="K100" s="5">
-        <v>0</v>
+        <v>11602</v>
       </c>
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
@@ -6279,24 +6328,24 @@
       <c r="S100" s="5"/>
       <c r="T100" s="5"/>
     </row>
-    <row r="101" ht="69" spans="1:20">
+    <row r="101" ht="104" spans="1:20">
       <c r="A101" s="5">
-        <v>2601</v>
+        <v>11602</v>
       </c>
       <c r="B101" s="5">
         <v>2</v>
       </c>
       <c r="C101" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D101" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G101" s="5">
         <v>-1</v>
@@ -6305,13 +6354,13 @@
         <v>0</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J101" s="5">
         <v>0</v>
       </c>
       <c r="K101" s="5">
-        <v>2602</v>
+        <v>11603</v>
       </c>
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
@@ -6323,24 +6372,24 @@
       <c r="S101" s="5"/>
       <c r="T101" s="5"/>
     </row>
-    <row r="102" ht="104" spans="1:20">
+    <row r="102" ht="35" spans="1:20">
       <c r="A102" s="5">
-        <v>2602</v>
+        <v>11603</v>
       </c>
       <c r="B102" s="5">
         <v>2</v>
       </c>
       <c r="C102" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D102" s="5">
         <v>1</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G102" s="5">
         <v>-1</v>
@@ -6349,13 +6398,13 @@
         <v>0</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>158</v>
+        <v>67</v>
       </c>
       <c r="J102" s="5">
         <v>0</v>
       </c>
       <c r="K102" s="5">
-        <v>0</v>
+        <v>11604</v>
       </c>
       <c r="L102" s="4"/>
       <c r="M102" s="4"/>
@@ -6367,39 +6416,39 @@
       <c r="S102" s="5"/>
       <c r="T102" s="5"/>
     </row>
-    <row r="103" ht="69" spans="1:20">
+    <row r="103" ht="104" spans="1:20">
       <c r="A103" s="5">
-        <v>11801</v>
+        <v>11604</v>
       </c>
       <c r="B103" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C103" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D103" s="5">
-        <v>0</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G103" s="5">
         <v>-1</v>
       </c>
       <c r="H103" s="5">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J103" s="5">
         <v>0</v>
       </c>
       <c r="K103" s="5">
-        <v>11802</v>
+        <v>11605</v>
       </c>
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
@@ -6411,39 +6460,39 @@
       <c r="S103" s="5"/>
       <c r="T103" s="5"/>
     </row>
-    <row r="104" ht="138" spans="1:20">
+    <row r="104" ht="35" spans="1:20">
       <c r="A104" s="5">
-        <v>11802</v>
+        <v>11605</v>
       </c>
       <c r="B104" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C104" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D104" s="5">
         <v>1</v>
       </c>
-      <c r="E104" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>43</v>
+      <c r="E104" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G104" s="5">
         <v>-1</v>
       </c>
       <c r="H104" s="5">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>160</v>
+        <v>67</v>
       </c>
       <c r="J104" s="5">
         <v>0</v>
       </c>
       <c r="K104" s="5">
-        <v>11803</v>
+        <v>11606</v>
       </c>
       <c r="L104" s="4"/>
       <c r="M104" s="4"/>
@@ -6455,33 +6504,33 @@
       <c r="S104" s="5"/>
       <c r="T104" s="5"/>
     </row>
-    <row r="105" ht="69" spans="1:20">
+    <row r="105" ht="104" spans="1:20">
       <c r="A105" s="5">
-        <v>11803</v>
+        <v>11606</v>
       </c>
       <c r="B105" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C105" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D105" s="5">
         <v>1</v>
       </c>
-      <c r="E105" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F105" s="5" t="s">
-        <v>43</v>
+      <c r="E105" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G105" s="5">
         <v>-1</v>
       </c>
       <c r="H105" s="5">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J105" s="5">
         <v>0</v>
@@ -6499,10 +6548,450 @@
       <c r="S105" s="5"/>
       <c r="T105" s="5"/>
     </row>
-    <row r="106" spans="1:3">
-      <c r="A106" s="5"/>
-      <c r="B106" s="5"/>
-      <c r="C106" s="5"/>
+    <row r="106" ht="104" spans="1:20">
+      <c r="A106" s="5">
+        <v>2401</v>
+      </c>
+      <c r="B106" s="5">
+        <v>0</v>
+      </c>
+      <c r="C106" s="5">
+        <v>0</v>
+      </c>
+      <c r="D106" s="5">
+        <v>0</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G106" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H106" s="5">
+        <v>0</v>
+      </c>
+      <c r="I106" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="J106" s="5">
+        <v>0</v>
+      </c>
+      <c r="K106" s="5">
+        <v>0</v>
+      </c>
+      <c r="L106" s="4"/>
+      <c r="M106" s="4"/>
+      <c r="N106" s="4"/>
+      <c r="O106" s="4"/>
+      <c r="P106" s="4"/>
+      <c r="Q106" s="5"/>
+      <c r="R106" s="5"/>
+      <c r="S106" s="5"/>
+      <c r="T106" s="5"/>
+    </row>
+    <row r="107" ht="104" spans="1:20">
+      <c r="A107" s="5">
+        <v>11701</v>
+      </c>
+      <c r="B107" s="5">
+        <v>0</v>
+      </c>
+      <c r="C107" s="5">
+        <v>4</v>
+      </c>
+      <c r="D107" s="5">
+        <v>0</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G107" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H107" s="5">
+        <v>-20</v>
+      </c>
+      <c r="I107" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="J107" s="5">
+        <v>0</v>
+      </c>
+      <c r="K107" s="5">
+        <v>11702</v>
+      </c>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+      <c r="N107" s="4"/>
+      <c r="O107" s="4"/>
+      <c r="P107" s="4"/>
+      <c r="Q107" s="5"/>
+      <c r="R107" s="5"/>
+      <c r="S107" s="5"/>
+      <c r="T107" s="5"/>
+    </row>
+    <row r="108" ht="35" spans="1:20">
+      <c r="A108" s="5">
+        <v>11702</v>
+      </c>
+      <c r="B108" s="5">
+        <v>0</v>
+      </c>
+      <c r="C108" s="5">
+        <v>0</v>
+      </c>
+      <c r="D108" s="5">
+        <v>1</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G108" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H108" s="5">
+        <v>0</v>
+      </c>
+      <c r="I108" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="J108" s="5">
+        <v>0</v>
+      </c>
+      <c r="K108" s="5">
+        <v>11703</v>
+      </c>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
+      <c r="N108" s="4"/>
+      <c r="O108" s="4"/>
+      <c r="P108" s="4"/>
+      <c r="Q108" s="5"/>
+      <c r="R108" s="5"/>
+      <c r="S108" s="5"/>
+      <c r="T108" s="5"/>
+    </row>
+    <row r="109" ht="69" spans="1:20">
+      <c r="A109" s="5">
+        <v>11703</v>
+      </c>
+      <c r="B109" s="5">
+        <v>0</v>
+      </c>
+      <c r="C109" s="5">
+        <v>0</v>
+      </c>
+      <c r="D109" s="5">
+        <v>1</v>
+      </c>
+      <c r="E109" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G109" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H109" s="5">
+        <v>0</v>
+      </c>
+      <c r="I109" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="J109" s="5">
+        <v>0</v>
+      </c>
+      <c r="K109" s="5">
+        <v>0</v>
+      </c>
+      <c r="L109" s="4"/>
+      <c r="M109" s="4"/>
+      <c r="N109" s="4"/>
+      <c r="O109" s="4"/>
+      <c r="P109" s="4"/>
+      <c r="Q109" s="5"/>
+      <c r="R109" s="5"/>
+      <c r="S109" s="5"/>
+      <c r="T109" s="5"/>
+    </row>
+    <row r="110" ht="69" spans="1:20">
+      <c r="A110" s="5">
+        <v>2501</v>
+      </c>
+      <c r="B110" s="5">
+        <v>0</v>
+      </c>
+      <c r="C110" s="5">
+        <v>0</v>
+      </c>
+      <c r="D110" s="5">
+        <v>0</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G110" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H110" s="5">
+        <v>0</v>
+      </c>
+      <c r="I110" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="J110" s="5">
+        <v>0</v>
+      </c>
+      <c r="K110" s="5">
+        <v>0</v>
+      </c>
+      <c r="L110" s="4"/>
+      <c r="M110" s="4"/>
+      <c r="N110" s="4"/>
+      <c r="O110" s="4"/>
+      <c r="P110" s="4"/>
+      <c r="Q110" s="5"/>
+      <c r="R110" s="5"/>
+      <c r="S110" s="5"/>
+      <c r="T110" s="5"/>
+    </row>
+    <row r="111" ht="69" spans="1:20">
+      <c r="A111" s="5">
+        <v>2601</v>
+      </c>
+      <c r="B111" s="5">
+        <v>2</v>
+      </c>
+      <c r="C111" s="5">
+        <v>0</v>
+      </c>
+      <c r="D111" s="5">
+        <v>0</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G111" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H111" s="5">
+        <v>0</v>
+      </c>
+      <c r="I111" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="J111" s="5">
+        <v>0</v>
+      </c>
+      <c r="K111" s="5">
+        <v>2602</v>
+      </c>
+      <c r="L111" s="4"/>
+      <c r="M111" s="4"/>
+      <c r="N111" s="4"/>
+      <c r="O111" s="4"/>
+      <c r="P111" s="4"/>
+      <c r="Q111" s="5"/>
+      <c r="R111" s="5"/>
+      <c r="S111" s="5"/>
+      <c r="T111" s="5"/>
+    </row>
+    <row r="112" ht="104" spans="1:20">
+      <c r="A112" s="5">
+        <v>2602</v>
+      </c>
+      <c r="B112" s="5">
+        <v>2</v>
+      </c>
+      <c r="C112" s="5">
+        <v>0</v>
+      </c>
+      <c r="D112" s="5">
+        <v>1</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G112" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H112" s="5">
+        <v>0</v>
+      </c>
+      <c r="I112" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="J112" s="5">
+        <v>0</v>
+      </c>
+      <c r="K112" s="5">
+        <v>0</v>
+      </c>
+      <c r="L112" s="4"/>
+      <c r="M112" s="4"/>
+      <c r="N112" s="4"/>
+      <c r="O112" s="4"/>
+      <c r="P112" s="4"/>
+      <c r="Q112" s="5"/>
+      <c r="R112" s="5"/>
+      <c r="S112" s="5"/>
+      <c r="T112" s="5"/>
+    </row>
+    <row r="113" ht="69" spans="1:20">
+      <c r="A113" s="5">
+        <v>11801</v>
+      </c>
+      <c r="B113" s="5">
+        <v>0</v>
+      </c>
+      <c r="C113" s="5">
+        <v>4</v>
+      </c>
+      <c r="D113" s="5">
+        <v>0</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G113" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H113" s="5">
+        <v>-10</v>
+      </c>
+      <c r="I113" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="J113" s="5">
+        <v>0</v>
+      </c>
+      <c r="K113" s="5">
+        <v>11802</v>
+      </c>
+      <c r="L113" s="4"/>
+      <c r="M113" s="4"/>
+      <c r="N113" s="4"/>
+      <c r="O113" s="4"/>
+      <c r="P113" s="4"/>
+      <c r="Q113" s="5"/>
+      <c r="R113" s="5"/>
+      <c r="S113" s="5"/>
+      <c r="T113" s="5"/>
+    </row>
+    <row r="114" ht="138" spans="1:20">
+      <c r="A114" s="5">
+        <v>11802</v>
+      </c>
+      <c r="B114" s="5">
+        <v>0</v>
+      </c>
+      <c r="C114" s="5">
+        <v>4</v>
+      </c>
+      <c r="D114" s="5">
+        <v>1</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F114" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G114" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H114" s="5">
+        <v>-10</v>
+      </c>
+      <c r="I114" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="J114" s="5">
+        <v>0</v>
+      </c>
+      <c r="K114" s="5">
+        <v>11803</v>
+      </c>
+      <c r="L114" s="4"/>
+      <c r="M114" s="4"/>
+      <c r="N114" s="4"/>
+      <c r="O114" s="4"/>
+      <c r="P114" s="4"/>
+      <c r="Q114" s="5"/>
+      <c r="R114" s="5"/>
+      <c r="S114" s="5"/>
+      <c r="T114" s="5"/>
+    </row>
+    <row r="115" ht="69" spans="1:20">
+      <c r="A115" s="5">
+        <v>11803</v>
+      </c>
+      <c r="B115" s="5">
+        <v>0</v>
+      </c>
+      <c r="C115" s="5">
+        <v>4</v>
+      </c>
+      <c r="D115" s="5">
+        <v>1</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G115" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H115" s="5">
+        <v>-10</v>
+      </c>
+      <c r="I115" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="J115" s="5">
+        <v>0</v>
+      </c>
+      <c r="K115" s="5">
+        <v>0</v>
+      </c>
+      <c r="L115" s="4"/>
+      <c r="M115" s="4"/>
+      <c r="N115" s="4"/>
+      <c r="O115" s="4"/>
+      <c r="P115" s="4"/>
+      <c r="Q115" s="5"/>
+      <c r="R115" s="5"/>
+      <c r="S115" s="5"/>
+      <c r="T115" s="5"/>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="5"/>
+      <c r="B116" s="5"/>
+      <c r="C116" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Excel/DialogDatas.xlsx
+++ b/Excel/DialogDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="14880"/>
+    <workbookView windowWidth="21000" windowHeight="12780"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="173">
   <si>
     <t>int</t>
   </si>
@@ -801,7 +801,7 @@
     </font>
     <font>
       <sz val="24"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -813,7 +813,7 @@
     </font>
     <font>
       <sz val="24"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1828,29 +1828,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T116"/>
-  <sheetFormatPr defaultColWidth="9.22115384615385" defaultRowHeight="34.4"/>
+  <dimension ref="A1:T117"/>
+  <sheetFormatPr defaultColWidth="9.22222222222222" defaultRowHeight="30.6"/>
   <cols>
     <col min="1" max="1" width="21" style="2" customWidth="1"/>
-    <col min="2" max="2" width="33.6634615384615" style="2" customWidth="1"/>
-    <col min="3" max="3" width="37.6634615384615" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25.4423076923077" style="2" customWidth="1"/>
-    <col min="5" max="5" width="26.1153846153846" style="2" customWidth="1"/>
-    <col min="6" max="6" width="50.8846153846154" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23.6634615384615" style="2" customWidth="1"/>
-    <col min="8" max="8" width="26.1153846153846" style="2" customWidth="1"/>
-    <col min="9" max="9" width="40.8365384615385" style="2" customWidth="1"/>
-    <col min="10" max="10" width="30.1153846153846" style="2" customWidth="1"/>
-    <col min="11" max="11" width="25.6634615384615" style="2" customWidth="1"/>
-    <col min="12" max="16" width="25.6634615384615" style="3" customWidth="1"/>
-    <col min="17" max="17" width="40.0673076923077" style="2" customWidth="1"/>
-    <col min="18" max="18" width="48.4807692307692" style="2" customWidth="1"/>
-    <col min="19" max="19" width="43.2692307692308" style="2" customWidth="1"/>
-    <col min="20" max="20" width="38.8557692307692" style="2" customWidth="1"/>
-    <col min="21" max="16384" width="9.22115384615385" style="2"/>
+    <col min="2" max="2" width="33.6666666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="37.6666666666667" style="2" customWidth="1"/>
+    <col min="4" max="4" width="25.4444444444444" style="2" customWidth="1"/>
+    <col min="5" max="5" width="26.1111111111111" style="2" customWidth="1"/>
+    <col min="6" max="6" width="50.8888888888889" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.6666666666667" style="2" customWidth="1"/>
+    <col min="8" max="8" width="26.1111111111111" style="2" customWidth="1"/>
+    <col min="9" max="9" width="40.8333333333333" style="2" customWidth="1"/>
+    <col min="10" max="10" width="30.1111111111111" style="2" customWidth="1"/>
+    <col min="11" max="11" width="25.6666666666667" style="2" customWidth="1"/>
+    <col min="12" max="16" width="25.6666666666667" style="3" customWidth="1"/>
+    <col min="17" max="17" width="40.0648148148148" style="2" customWidth="1"/>
+    <col min="18" max="18" width="48.4814814814815" style="2" customWidth="1"/>
+    <col min="19" max="19" width="43.2685185185185" style="2" customWidth="1"/>
+    <col min="20" max="20" width="38.8518518518519" style="2" customWidth="1"/>
+    <col min="21" max="16384" width="9.22222222222222" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" spans="1:20">
+    <row r="1" spans="1:20">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" ht="35" spans="1:20">
+    <row r="3" spans="1:20">
       <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
@@ -2036,7 +2036,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" ht="104" spans="1:20">
+    <row r="4" ht="90" spans="1:20">
       <c r="A4" s="5">
         <v>10001</v>
       </c>
@@ -2080,7 +2080,7 @@
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
     </row>
-    <row r="5" ht="104" spans="1:20">
+    <row r="5" ht="90" spans="1:20">
       <c r="A5" s="5">
         <v>10002</v>
       </c>
@@ -2124,7 +2124,7 @@
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
     </row>
-    <row r="6" ht="138" spans="1:20">
+    <row r="6" ht="120" spans="1:20">
       <c r="A6" s="5">
         <v>1001</v>
       </c>
@@ -2168,7 +2168,7 @@
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
     </row>
-    <row r="7" ht="104" spans="1:20">
+    <row r="7" ht="90" spans="1:20">
       <c r="A7" s="5">
         <v>1101</v>
       </c>
@@ -2212,7 +2212,7 @@
       <c r="S7" s="5"/>
       <c r="T7" s="5"/>
     </row>
-    <row r="8" ht="104" spans="1:20">
+    <row r="8" ht="90" spans="1:20">
       <c r="A8" s="5">
         <v>1201</v>
       </c>
@@ -2256,7 +2256,7 @@
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
     </row>
-    <row r="9" ht="138" spans="1:20">
+    <row r="9" ht="120" spans="1:20">
       <c r="A9" s="5">
         <v>1202</v>
       </c>
@@ -2300,7 +2300,7 @@
       <c r="S9" s="5"/>
       <c r="T9" s="5"/>
     </row>
-    <row r="10" ht="104" spans="1:20">
+    <row r="10" ht="90" spans="1:20">
       <c r="A10" s="5">
         <v>1203</v>
       </c>
@@ -2344,7 +2344,7 @@
       <c r="S10" s="5"/>
       <c r="T10" s="5"/>
     </row>
-    <row r="11" ht="138" spans="1:20">
+    <row r="11" ht="120" spans="1:20">
       <c r="A11" s="5">
         <v>10050</v>
       </c>
@@ -2390,7 +2390,7 @@
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
     </row>
-    <row r="12" ht="69" spans="1:20">
+    <row r="12" ht="60" spans="1:20">
       <c r="A12" s="5">
         <v>10101</v>
       </c>
@@ -2434,7 +2434,7 @@
       <c r="S12" s="5"/>
       <c r="T12" s="5"/>
     </row>
-    <row r="13" s="1" customFormat="1" ht="104" spans="1:20">
+    <row r="13" s="1" customFormat="1" ht="90" spans="1:20">
       <c r="A13" s="6">
         <v>10201</v>
       </c>
@@ -2478,7 +2478,7 @@
       <c r="S13" s="6"/>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" ht="104" spans="1:20">
+    <row r="14" ht="90" spans="1:20">
       <c r="A14" s="5">
         <v>10202</v>
       </c>
@@ -2524,7 +2524,7 @@
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
     </row>
-    <row r="15" ht="69" spans="1:20">
+    <row r="15" ht="60" spans="1:20">
       <c r="A15" s="5">
         <v>10203</v>
       </c>
@@ -2568,7 +2568,7 @@
       <c r="S15" s="5"/>
       <c r="T15" s="5"/>
     </row>
-    <row r="16" ht="138" spans="1:20">
+    <row r="16" ht="120" spans="1:20">
       <c r="A16" s="5">
         <v>10204</v>
       </c>
@@ -2612,7 +2612,7 @@
       <c r="S16" s="5"/>
       <c r="T16" s="5"/>
     </row>
-    <row r="17" ht="138" spans="1:20">
+    <row r="17" ht="120" spans="1:20">
       <c r="A17" s="5">
         <v>10205</v>
       </c>
@@ -2656,7 +2656,7 @@
       <c r="S17" s="5"/>
       <c r="T17" s="5"/>
     </row>
-    <row r="18" s="1" customFormat="1" ht="104" spans="1:20">
+    <row r="18" s="1" customFormat="1" ht="90" spans="1:20">
       <c r="A18" s="5">
         <v>10206</v>
       </c>
@@ -2700,7 +2700,7 @@
       <c r="S18" s="6"/>
       <c r="T18" s="6"/>
     </row>
-    <row r="19" ht="35" spans="1:20">
+    <row r="19" spans="1:20">
       <c r="A19" s="5">
         <v>10207</v>
       </c>
@@ -2744,7 +2744,7 @@
       <c r="S19" s="5"/>
       <c r="T19" s="5"/>
     </row>
-    <row r="20" ht="35" spans="1:20">
+    <row r="20" spans="1:20">
       <c r="A20" s="5">
         <v>10208</v>
       </c>
@@ -2788,7 +2788,7 @@
       <c r="S20" s="5"/>
       <c r="T20" s="5"/>
     </row>
-    <row r="21" ht="69" spans="1:20">
+    <row r="21" ht="60" spans="1:20">
       <c r="A21" s="5">
         <v>1301</v>
       </c>
@@ -2832,7 +2832,7 @@
       <c r="S21" s="5"/>
       <c r="T21" s="5"/>
     </row>
-    <row r="22" ht="138" spans="1:20">
+    <row r="22" ht="120" spans="1:20">
       <c r="A22" s="5">
         <v>1302</v>
       </c>
@@ -2876,7 +2876,7 @@
       <c r="S22" s="5"/>
       <c r="T22" s="5"/>
     </row>
-    <row r="23" ht="69" spans="1:20">
+    <row r="23" ht="60" spans="1:20">
       <c r="A23" s="5">
         <v>1401</v>
       </c>
@@ -2920,7 +2920,7 @@
       <c r="S23" s="5"/>
       <c r="T23" s="5"/>
     </row>
-    <row r="24" ht="138" spans="1:20">
+    <row r="24" ht="120" spans="1:20">
       <c r="A24" s="5">
         <v>1402</v>
       </c>
@@ -2964,7 +2964,7 @@
       <c r="S24" s="5"/>
       <c r="T24" s="5"/>
     </row>
-    <row r="25" ht="104" spans="1:20">
+    <row r="25" ht="90" spans="1:20">
       <c r="A25" s="5">
         <v>1501</v>
       </c>
@@ -3008,7 +3008,7 @@
       <c r="S25" s="5"/>
       <c r="T25" s="5"/>
     </row>
-    <row r="26" ht="172" spans="1:20">
+    <row r="26" ht="150" spans="1:20">
       <c r="A26" s="5">
         <v>1502</v>
       </c>
@@ -3052,7 +3052,7 @@
       <c r="S26" s="5"/>
       <c r="T26" s="5"/>
     </row>
-    <row r="27" ht="104" spans="1:20">
+    <row r="27" ht="90" spans="1:20">
       <c r="A27" s="5">
         <v>1601</v>
       </c>
@@ -3096,7 +3096,7 @@
       <c r="S27" s="5"/>
       <c r="T27" s="5"/>
     </row>
-    <row r="28" ht="69" spans="1:20">
+    <row r="28" ht="60" spans="1:20">
       <c r="A28" s="5">
         <v>1701</v>
       </c>
@@ -3140,7 +3140,7 @@
       <c r="S28" s="5"/>
       <c r="T28" s="5"/>
     </row>
-    <row r="29" ht="69" spans="1:20">
+    <row r="29" ht="60" spans="1:20">
       <c r="A29" s="5">
         <v>10301</v>
       </c>
@@ -3184,7 +3184,7 @@
       <c r="S29" s="5"/>
       <c r="T29" s="5"/>
     </row>
-    <row r="30" ht="104" spans="1:20">
+    <row r="30" ht="90" spans="1:20">
       <c r="A30" s="5">
         <v>10401</v>
       </c>
@@ -3228,7 +3228,7 @@
       <c r="S30" s="5"/>
       <c r="T30" s="5"/>
     </row>
-    <row r="31" ht="104" spans="1:20">
+    <row r="31" ht="90" spans="1:20">
       <c r="A31" s="5">
         <v>10402</v>
       </c>
@@ -3272,7 +3272,7 @@
       <c r="S31" s="5"/>
       <c r="T31" s="5"/>
     </row>
-    <row r="32" ht="138" spans="1:20">
+    <row r="32" ht="120" spans="1:20">
       <c r="A32" s="5">
         <v>10404</v>
       </c>
@@ -3316,7 +3316,7 @@
       <c r="S32" s="5"/>
       <c r="T32" s="5"/>
     </row>
-    <row r="33" ht="35" spans="1:20">
+    <row r="33" spans="1:20">
       <c r="A33" s="5">
         <v>10403</v>
       </c>
@@ -3360,7 +3360,7 @@
       <c r="S33" s="5"/>
       <c r="T33" s="5"/>
     </row>
-    <row r="34" ht="104" spans="1:20">
+    <row r="34" ht="90" spans="1:20">
       <c r="A34" s="5">
         <v>10501</v>
       </c>
@@ -3404,7 +3404,7 @@
       <c r="S34" s="5"/>
       <c r="T34" s="5"/>
     </row>
-    <row r="35" ht="104" spans="1:20">
+    <row r="35" ht="90" spans="1:20">
       <c r="A35" s="5">
         <v>10502</v>
       </c>
@@ -3448,7 +3448,7 @@
       <c r="S35" s="5"/>
       <c r="T35" s="5"/>
     </row>
-    <row r="36" s="1" customFormat="1" ht="138" spans="1:20">
+    <row r="36" s="1" customFormat="1" ht="120" spans="1:20">
       <c r="A36" s="5">
         <v>10503</v>
       </c>
@@ -3494,7 +3494,7 @@
       <c r="S36" s="5"/>
       <c r="T36" s="5"/>
     </row>
-    <row r="37" s="1" customFormat="1" ht="172" spans="1:20">
+    <row r="37" s="1" customFormat="1" ht="150" spans="1:20">
       <c r="A37" s="6">
         <v>10550</v>
       </c>
@@ -3540,7 +3540,7 @@
       <c r="S37" s="6"/>
       <c r="T37" s="6"/>
     </row>
-    <row r="38" s="1" customFormat="1" ht="172" spans="1:20">
+    <row r="38" s="1" customFormat="1" ht="150" spans="1:20">
       <c r="A38" s="6">
         <v>1801</v>
       </c>
@@ -3628,7 +3628,7 @@
       <c r="S39" s="6"/>
       <c r="T39" s="6"/>
     </row>
-    <row r="40" customFormat="1" ht="69" spans="1:20">
+    <row r="40" customFormat="1" ht="60" spans="1:20">
       <c r="A40" s="5">
         <v>1803</v>
       </c>
@@ -3678,7 +3678,7 @@
       <c r="S40" s="5"/>
       <c r="T40" s="5"/>
     </row>
-    <row r="41" ht="69" spans="1:20">
+    <row r="41" ht="60" spans="1:20">
       <c r="A41" s="5">
         <v>10601</v>
       </c>
@@ -3722,7 +3722,7 @@
       <c r="S41" s="5"/>
       <c r="T41" s="5"/>
     </row>
-    <row r="42" ht="35" spans="1:20">
+    <row r="42" spans="1:20">
       <c r="A42" s="5">
         <v>10602</v>
       </c>
@@ -3766,7 +3766,7 @@
       <c r="S42" s="5"/>
       <c r="T42" s="5"/>
     </row>
-    <row r="43" ht="69" spans="1:20">
+    <row r="43" ht="60" spans="1:20">
       <c r="A43" s="5">
         <v>10603</v>
       </c>
@@ -3810,7 +3810,7 @@
       <c r="S43" s="5"/>
       <c r="T43" s="5"/>
     </row>
-    <row r="44" ht="69" spans="1:20">
+    <row r="44" ht="60" spans="1:20">
       <c r="A44" s="5">
         <v>10604</v>
       </c>
@@ -3854,7 +3854,7 @@
       <c r="S44" s="5"/>
       <c r="T44" s="5"/>
     </row>
-    <row r="45" ht="69" spans="1:20">
+    <row r="45" ht="60" spans="1:20">
       <c r="A45" s="5">
         <v>10701</v>
       </c>
@@ -3898,7 +3898,7 @@
       <c r="S45" s="5"/>
       <c r="T45" s="5"/>
     </row>
-    <row r="46" ht="69" spans="1:20">
+    <row r="46" ht="60" spans="1:20">
       <c r="A46" s="5">
         <v>10702</v>
       </c>
@@ -3942,7 +3942,7 @@
       <c r="S46" s="5"/>
       <c r="T46" s="5"/>
     </row>
-    <row r="47" ht="138" spans="1:20">
+    <row r="47" ht="132" spans="1:20">
       <c r="A47" s="5">
         <v>10703</v>
       </c>
@@ -3986,7 +3986,7 @@
       <c r="S47" s="5"/>
       <c r="T47" s="5"/>
     </row>
-    <row r="48" ht="69" spans="1:20">
+    <row r="48" ht="60" spans="1:20">
       <c r="A48" s="5">
         <v>10704</v>
       </c>
@@ -4030,7 +4030,7 @@
       <c r="S48" s="5"/>
       <c r="T48" s="5"/>
     </row>
-    <row r="49" ht="69" spans="1:20">
+    <row r="49" ht="60" spans="1:20">
       <c r="A49" s="5">
         <v>10801</v>
       </c>
@@ -4074,7 +4074,7 @@
       <c r="S49" s="5"/>
       <c r="T49" s="5"/>
     </row>
-    <row r="50" ht="138" spans="1:20">
+    <row r="50" ht="120" spans="1:20">
       <c r="A50" s="5">
         <v>10802</v>
       </c>
@@ -4118,7 +4118,7 @@
       <c r="S50" s="5"/>
       <c r="T50" s="5"/>
     </row>
-    <row r="51" ht="69" spans="1:20">
+    <row r="51" ht="63" spans="1:20">
       <c r="A51" s="5">
         <v>10803</v>
       </c>
@@ -4162,7 +4162,7 @@
       <c r="S51" s="5"/>
       <c r="T51" s="5"/>
     </row>
-    <row r="52" ht="69" spans="1:20">
+    <row r="52" ht="60" spans="1:20">
       <c r="A52" s="5">
         <v>10804</v>
       </c>
@@ -4206,7 +4206,7 @@
       <c r="S52" s="5"/>
       <c r="T52" s="5"/>
     </row>
-    <row r="53" ht="104" spans="1:20">
+    <row r="53" ht="90" spans="1:20">
       <c r="A53" s="5">
         <v>10901</v>
       </c>
@@ -4250,7 +4250,7 @@
       <c r="S53" s="5"/>
       <c r="T53" s="5"/>
     </row>
-    <row r="54" ht="104" spans="1:20">
+    <row r="54" ht="90" spans="1:20">
       <c r="A54" s="5">
         <v>10902</v>
       </c>
@@ -4294,7 +4294,7 @@
       <c r="S54" s="5"/>
       <c r="T54" s="5"/>
     </row>
-    <row r="55" ht="104" spans="1:20">
+    <row r="55" ht="90" spans="1:20">
       <c r="A55" s="5">
         <v>10903</v>
       </c>
@@ -4338,7 +4338,7 @@
       <c r="S55" s="5"/>
       <c r="T55" s="5"/>
     </row>
-    <row r="56" ht="69" spans="1:20">
+    <row r="56" ht="60" spans="1:20">
       <c r="A56" s="5">
         <v>10904</v>
       </c>
@@ -4382,7 +4382,7 @@
       <c r="S56" s="5"/>
       <c r="T56" s="5"/>
     </row>
-    <row r="57" ht="138" spans="1:20">
+    <row r="57" ht="120" spans="1:20">
       <c r="A57" s="5">
         <v>10905</v>
       </c>
@@ -4426,7 +4426,7 @@
       <c r="S57" s="5"/>
       <c r="T57" s="5"/>
     </row>
-    <row r="58" ht="138" spans="1:20">
+    <row r="58" ht="120" spans="1:20">
       <c r="A58" s="5">
         <v>10906</v>
       </c>
@@ -4470,7 +4470,7 @@
       <c r="S58" s="5"/>
       <c r="T58" s="5"/>
     </row>
-    <row r="59" ht="69" spans="1:20">
+    <row r="59" ht="60" spans="1:20">
       <c r="A59" s="5">
         <v>10907</v>
       </c>
@@ -4514,7 +4514,7 @@
       <c r="S59" s="5"/>
       <c r="T59" s="5"/>
     </row>
-    <row r="60" ht="69" spans="1:20">
+    <row r="60" ht="60" spans="1:20">
       <c r="A60" s="5">
         <v>10908</v>
       </c>
@@ -4558,7 +4558,7 @@
       <c r="S60" s="5"/>
       <c r="T60" s="5"/>
     </row>
-    <row r="61" ht="104" spans="1:20">
+    <row r="61" ht="90" spans="1:20">
       <c r="A61" s="5">
         <v>10909</v>
       </c>
@@ -4602,7 +4602,7 @@
       <c r="S61" s="5"/>
       <c r="T61" s="5"/>
     </row>
-    <row r="62" ht="104" spans="1:20">
+    <row r="62" ht="90" spans="1:20">
       <c r="A62" s="5">
         <v>10910</v>
       </c>
@@ -4646,7 +4646,7 @@
       <c r="S62" s="5"/>
       <c r="T62" s="5"/>
     </row>
-    <row r="63" ht="69" spans="1:20">
+    <row r="63" ht="60" spans="1:20">
       <c r="A63" s="5">
         <v>10911</v>
       </c>
@@ -4690,7 +4690,7 @@
       <c r="S63" s="5"/>
       <c r="T63" s="5"/>
     </row>
-    <row r="64" ht="104" spans="1:20">
+    <row r="64" ht="90" spans="1:20">
       <c r="A64" s="5">
         <v>10912</v>
       </c>
@@ -4736,24 +4736,24 @@
       <c r="S64" s="5"/>
       <c r="T64" s="5"/>
     </row>
-    <row r="65" ht="104" spans="1:20">
+    <row r="65" ht="90" spans="1:20">
       <c r="A65" s="5">
-        <v>11001</v>
+        <v>10950</v>
       </c>
       <c r="B65" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C65" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D65" s="5">
         <v>0</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="G65" s="5">
         <v>-1</v>
@@ -4762,15 +4762,17 @@
         <v>0</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J65" s="5">
         <v>0</v>
       </c>
       <c r="K65" s="5">
-        <v>11002</v>
-      </c>
-      <c r="L65" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="M65" s="4"/>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
@@ -4780,39 +4782,39 @@
       <c r="S65" s="5"/>
       <c r="T65" s="5"/>
     </row>
-    <row r="66" ht="35" spans="1:20">
+    <row r="66" ht="90" spans="1:20">
       <c r="A66" s="5">
+        <v>11001</v>
+      </c>
+      <c r="B66" s="5">
+        <v>1</v>
+      </c>
+      <c r="C66" s="5">
+        <v>1</v>
+      </c>
+      <c r="D66" s="5">
+        <v>0</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G66" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H66" s="5">
+        <v>0</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J66" s="5">
+        <v>0</v>
+      </c>
+      <c r="K66" s="5">
         <v>11002</v>
-      </c>
-      <c r="B66" s="5">
-        <v>0</v>
-      </c>
-      <c r="C66" s="5">
-        <v>1</v>
-      </c>
-      <c r="D66" s="5">
-        <v>1</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G66" s="5">
-        <v>-1</v>
-      </c>
-      <c r="H66" s="5">
-        <v>0</v>
-      </c>
-      <c r="I66" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="J66" s="5">
-        <v>0</v>
-      </c>
-      <c r="K66" s="5">
-        <v>0</v>
       </c>
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
@@ -4824,9 +4826,9 @@
       <c r="S66" s="5"/>
       <c r="T66" s="5"/>
     </row>
-    <row r="67" ht="104" spans="1:20">
+    <row r="67" spans="1:20">
       <c r="A67" s="5">
-        <v>11101</v>
+        <v>11002</v>
       </c>
       <c r="B67" s="5">
         <v>0</v>
@@ -4835,7 +4837,7 @@
         <v>1</v>
       </c>
       <c r="D67" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>42</v>
@@ -4850,13 +4852,13 @@
         <v>0</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>125</v>
+        <v>67</v>
       </c>
       <c r="J67" s="5">
         <v>0</v>
       </c>
       <c r="K67" s="5">
-        <v>11102</v>
+        <v>0</v>
       </c>
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
@@ -4868,39 +4870,39 @@
       <c r="S67" s="5"/>
       <c r="T67" s="5"/>
     </row>
-    <row r="68" ht="69" spans="1:20">
+    <row r="68" ht="90" spans="1:20">
       <c r="A68" s="5">
+        <v>11101</v>
+      </c>
+      <c r="B68" s="5">
+        <v>0</v>
+      </c>
+      <c r="C68" s="5">
+        <v>1</v>
+      </c>
+      <c r="D68" s="5">
+        <v>0</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G68" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H68" s="5">
+        <v>0</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="J68" s="5">
+        <v>0</v>
+      </c>
+      <c r="K68" s="5">
         <v>11102</v>
-      </c>
-      <c r="B68" s="5">
-        <v>2</v>
-      </c>
-      <c r="C68" s="5">
-        <v>0</v>
-      </c>
-      <c r="D68" s="5">
-        <v>1</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G68" s="5">
-        <v>-1</v>
-      </c>
-      <c r="H68" s="5">
-        <v>0</v>
-      </c>
-      <c r="I68" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="J68" s="5">
-        <v>0</v>
-      </c>
-      <c r="K68" s="5">
-        <v>11103</v>
       </c>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
@@ -4912,41 +4914,41 @@
       <c r="S68" s="5"/>
       <c r="T68" s="5"/>
     </row>
-    <row r="69" ht="172" spans="1:20">
+    <row r="69" ht="60" spans="1:20">
       <c r="A69" s="5">
+        <v>11102</v>
+      </c>
+      <c r="B69" s="5">
+        <v>2</v>
+      </c>
+      <c r="C69" s="5">
+        <v>0</v>
+      </c>
+      <c r="D69" s="5">
+        <v>1</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G69" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H69" s="5">
+        <v>0</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J69" s="5">
+        <v>0</v>
+      </c>
+      <c r="K69" s="5">
         <v>11103</v>
       </c>
-      <c r="B69" s="5">
-        <v>0</v>
-      </c>
-      <c r="C69" s="5">
-        <v>4</v>
-      </c>
-      <c r="D69" s="5">
-        <v>1</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G69" s="5">
-        <v>-1</v>
-      </c>
-      <c r="H69" s="5">
-        <v>-5</v>
-      </c>
-      <c r="I69" s="4"/>
-      <c r="J69" s="5">
-        <v>0</v>
-      </c>
-      <c r="K69" s="5">
-        <v>0</v>
-      </c>
-      <c r="L69" s="4" t="s">
-        <v>127</v>
-      </c>
+      <c r="L69" s="4"/>
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
@@ -4956,34 +4958,32 @@
       <c r="S69" s="5"/>
       <c r="T69" s="5"/>
     </row>
-    <row r="70" ht="172" spans="1:20">
+    <row r="70" ht="150" spans="1:20">
       <c r="A70" s="5">
-        <v>11150</v>
+        <v>11103</v>
       </c>
       <c r="B70" s="5">
         <v>0</v>
       </c>
       <c r="C70" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D70" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G70" s="5">
         <v>-1</v>
       </c>
       <c r="H70" s="5">
-        <v>0</v>
-      </c>
-      <c r="I70" s="4" t="s">
-        <v>128</v>
-      </c>
+        <v>-5</v>
+      </c>
+      <c r="I70" s="4"/>
       <c r="J70" s="5">
         <v>0</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M70" s="4"/>
       <c r="N70" s="4"/>
@@ -5002,21 +5002,21 @@
       <c r="S70" s="5"/>
       <c r="T70" s="5"/>
     </row>
-    <row r="71" ht="104" spans="1:20">
+    <row r="71" ht="150" spans="1:20">
       <c r="A71" s="5">
-        <v>1901</v>
+        <v>11150</v>
       </c>
       <c r="B71" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C71" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D71" s="5">
         <v>0</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>47</v>
@@ -5028,15 +5028,17 @@
         <v>0</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J71" s="5">
         <v>0</v>
       </c>
       <c r="K71" s="5">
-        <v>1902</v>
-      </c>
-      <c r="L71" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="L71" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="M71" s="4"/>
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
@@ -5046,18 +5048,18 @@
       <c r="S71" s="5"/>
       <c r="T71" s="5"/>
     </row>
-    <row r="72" ht="138" spans="1:20">
+    <row r="72" ht="90" spans="1:20">
       <c r="A72" s="5">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="B72" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C72" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D72" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>88</v>
@@ -5069,18 +5071,18 @@
         <v>-1</v>
       </c>
       <c r="H72" s="5">
-        <v>-5</v>
-      </c>
-      <c r="I72" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>129</v>
+      </c>
       <c r="J72" s="5">
         <v>0</v>
       </c>
       <c r="K72" s="5">
-        <v>0</v>
-      </c>
-      <c r="L72" s="4" t="s">
-        <v>130</v>
-      </c>
+        <v>1902</v>
+      </c>
+      <c r="L72" s="4"/>
       <c r="M72" s="4"/>
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
@@ -5090,41 +5092,41 @@
       <c r="S72" s="5"/>
       <c r="T72" s="5"/>
     </row>
-    <row r="73" ht="104" spans="1:20">
+    <row r="73" ht="120" spans="1:20">
       <c r="A73" s="5">
-        <v>11201</v>
+        <v>1902</v>
       </c>
       <c r="B73" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C73" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D73" s="5">
-        <v>0</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>59</v>
+        <v>1</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="G73" s="5">
         <v>-1</v>
       </c>
       <c r="H73" s="5">
-        <v>0</v>
-      </c>
-      <c r="I73" s="4" t="s">
-        <v>131</v>
-      </c>
+        <v>-5</v>
+      </c>
+      <c r="I73" s="4"/>
       <c r="J73" s="5">
         <v>0</v>
       </c>
       <c r="K73" s="5">
-        <v>11202</v>
-      </c>
-      <c r="L73" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="L73" s="4" t="s">
+        <v>130</v>
+      </c>
       <c r="M73" s="4"/>
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
@@ -5134,39 +5136,39 @@
       <c r="S73" s="5"/>
       <c r="T73" s="5"/>
     </row>
-    <row r="74" ht="69" spans="1:20">
+    <row r="74" ht="90" spans="1:20">
       <c r="A74" s="5">
+        <v>11201</v>
+      </c>
+      <c r="B74" s="5">
+        <v>2</v>
+      </c>
+      <c r="C74" s="5">
+        <v>0</v>
+      </c>
+      <c r="D74" s="5">
+        <v>0</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G74" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H74" s="5">
+        <v>0</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="J74" s="5">
+        <v>0</v>
+      </c>
+      <c r="K74" s="5">
         <v>11202</v>
-      </c>
-      <c r="B74" s="5">
-        <v>0</v>
-      </c>
-      <c r="C74" s="5">
-        <v>0</v>
-      </c>
-      <c r="D74" s="5">
-        <v>1</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G74" s="5">
-        <v>0</v>
-      </c>
-      <c r="H74" s="5">
-        <v>0</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="J74" s="5">
-        <v>0</v>
-      </c>
-      <c r="K74" s="5">
-        <v>11203</v>
       </c>
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
@@ -5178,15 +5180,15 @@
       <c r="S74" s="5"/>
       <c r="T74" s="5"/>
     </row>
-    <row r="75" ht="207" spans="1:20">
+    <row r="75" ht="60" spans="1:20">
       <c r="A75" s="5">
-        <v>11203</v>
+        <v>11202</v>
       </c>
       <c r="B75" s="5">
         <v>0</v>
       </c>
       <c r="C75" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D75" s="5">
         <v>1</v>
@@ -5198,21 +5200,21 @@
         <v>43</v>
       </c>
       <c r="G75" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H75" s="5">
         <v>0</v>
       </c>
-      <c r="I75" s="4"/>
+      <c r="I75" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="J75" s="5">
         <v>0</v>
       </c>
       <c r="K75" s="5">
-        <v>11204</v>
-      </c>
-      <c r="L75" s="4" t="s">
-        <v>133</v>
-      </c>
+        <v>11203</v>
+      </c>
+      <c r="L75" s="4"/>
       <c r="M75" s="4"/>
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
@@ -5222,15 +5224,15 @@
       <c r="S75" s="5"/>
       <c r="T75" s="5"/>
     </row>
-    <row r="76" ht="104" spans="1:20">
+    <row r="76" ht="180" spans="1:20">
       <c r="A76" s="5">
-        <v>11204</v>
+        <v>11203</v>
       </c>
       <c r="B76" s="5">
         <v>0</v>
       </c>
       <c r="C76" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D76" s="5">
         <v>1</v>
@@ -5242,21 +5244,21 @@
         <v>43</v>
       </c>
       <c r="G76" s="5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="H76" s="5">
         <v>0</v>
       </c>
-      <c r="I76" s="4" t="s">
-        <v>134</v>
-      </c>
+      <c r="I76" s="4"/>
       <c r="J76" s="5">
         <v>0</v>
       </c>
       <c r="K76" s="5">
-        <v>11205</v>
-      </c>
-      <c r="L76" s="4"/>
+        <v>11204</v>
+      </c>
+      <c r="L76" s="4" t="s">
+        <v>133</v>
+      </c>
       <c r="M76" s="4"/>
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
@@ -5266,15 +5268,15 @@
       <c r="S76" s="5"/>
       <c r="T76" s="5"/>
     </row>
-    <row r="77" ht="104" spans="1:20">
+    <row r="77" ht="90" spans="1:20">
       <c r="A77" s="5">
-        <v>11205</v>
+        <v>11204</v>
       </c>
       <c r="B77" s="5">
         <v>0</v>
       </c>
       <c r="C77" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D77" s="5">
         <v>1</v>
@@ -5292,17 +5294,15 @@
         <v>0</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J77" s="5">
         <v>0</v>
       </c>
       <c r="K77" s="5">
-        <v>0</v>
-      </c>
-      <c r="L77" s="4" t="s">
-        <v>135</v>
-      </c>
+        <v>11205</v>
+      </c>
+      <c r="L77" s="4"/>
       <c r="M77" s="4"/>
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
@@ -5312,18 +5312,18 @@
       <c r="S77" s="5"/>
       <c r="T77" s="5"/>
     </row>
-    <row r="78" ht="69" spans="1:20">
+    <row r="78" ht="90" spans="1:20">
       <c r="A78" s="5">
-        <v>11301</v>
+        <v>11205</v>
       </c>
       <c r="B78" s="5">
         <v>0</v>
       </c>
       <c r="C78" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D78" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>42</v>
@@ -5338,15 +5338,17 @@
         <v>0</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J78" s="5">
         <v>0</v>
       </c>
       <c r="K78" s="5">
-        <v>11302</v>
-      </c>
-      <c r="L78" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="L78" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="M78" s="4"/>
       <c r="N78" s="4"/>
       <c r="O78" s="4"/>
@@ -5356,39 +5358,39 @@
       <c r="S78" s="5"/>
       <c r="T78" s="5"/>
     </row>
-    <row r="79" ht="104" spans="1:20">
+    <row r="79" ht="60" spans="1:20">
       <c r="A79" s="5">
+        <v>11301</v>
+      </c>
+      <c r="B79" s="5">
+        <v>0</v>
+      </c>
+      <c r="C79" s="5">
+        <v>0</v>
+      </c>
+      <c r="D79" s="5">
+        <v>0</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G79" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H79" s="5">
+        <v>0</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="J79" s="5">
+        <v>0</v>
+      </c>
+      <c r="K79" s="5">
         <v>11302</v>
-      </c>
-      <c r="B79" s="5">
-        <v>12</v>
-      </c>
-      <c r="C79" s="5">
-        <v>0</v>
-      </c>
-      <c r="D79" s="5">
-        <v>1</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G79" s="5">
-        <v>-1</v>
-      </c>
-      <c r="H79" s="5">
-        <v>0</v>
-      </c>
-      <c r="I79" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="J79" s="5">
-        <v>0</v>
-      </c>
-      <c r="K79" s="5">
-        <v>11303</v>
       </c>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
@@ -5400,39 +5402,39 @@
       <c r="S79" s="5"/>
       <c r="T79" s="5"/>
     </row>
-    <row r="80" ht="69" spans="1:20">
+    <row r="80" ht="90" spans="1:20">
       <c r="A80" s="5">
+        <v>11302</v>
+      </c>
+      <c r="B80" s="5">
+        <v>12</v>
+      </c>
+      <c r="C80" s="5">
+        <v>0</v>
+      </c>
+      <c r="D80" s="5">
+        <v>1</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G80" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H80" s="5">
+        <v>0</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J80" s="5">
+        <v>0</v>
+      </c>
+      <c r="K80" s="5">
         <v>11303</v>
-      </c>
-      <c r="B80" s="5">
-        <v>0</v>
-      </c>
-      <c r="C80" s="5">
-        <v>0</v>
-      </c>
-      <c r="D80" s="5">
-        <v>1</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G80" s="5">
-        <v>-1</v>
-      </c>
-      <c r="H80" s="5">
-        <v>0</v>
-      </c>
-      <c r="I80" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="J80" s="5">
-        <v>0</v>
-      </c>
-      <c r="K80" s="5">
-        <v>11304</v>
       </c>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
@@ -5444,15 +5446,15 @@
       <c r="S80" s="5"/>
       <c r="T80" s="5"/>
     </row>
-    <row r="81" ht="138" spans="1:20">
+    <row r="81" spans="1:20">
       <c r="A81" s="5">
-        <v>11304</v>
+        <v>11303</v>
       </c>
       <c r="B81" s="5">
         <v>0</v>
       </c>
       <c r="C81" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D81" s="5">
         <v>1</v>
@@ -5467,18 +5469,18 @@
         <v>-1</v>
       </c>
       <c r="H81" s="5">
-        <v>-5</v>
-      </c>
-      <c r="I81" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="J81" s="5">
         <v>0</v>
       </c>
       <c r="K81" s="5">
-        <v>11305</v>
-      </c>
-      <c r="L81" s="4" t="s">
-        <v>139</v>
-      </c>
+        <v>11304</v>
+      </c>
+      <c r="L81" s="4"/>
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
@@ -5488,41 +5490,41 @@
       <c r="S81" s="5"/>
       <c r="T81" s="5"/>
     </row>
-    <row r="82" ht="207" spans="1:20">
+    <row r="82" ht="120" spans="1:20">
       <c r="A82" s="5">
+        <v>11304</v>
+      </c>
+      <c r="B82" s="5">
+        <v>0</v>
+      </c>
+      <c r="C82" s="5">
+        <v>4</v>
+      </c>
+      <c r="D82" s="5">
+        <v>1</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G82" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H82" s="5">
+        <v>-5</v>
+      </c>
+      <c r="I82" s="4"/>
+      <c r="J82" s="5">
+        <v>0</v>
+      </c>
+      <c r="K82" s="5">
         <v>11305</v>
       </c>
-      <c r="B82" s="5">
-        <v>12</v>
-      </c>
-      <c r="C82" s="5">
-        <v>0</v>
-      </c>
-      <c r="D82" s="5">
-        <v>1</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G82" s="5">
-        <v>-1</v>
-      </c>
-      <c r="H82" s="5">
-        <v>0</v>
-      </c>
-      <c r="I82" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="J82" s="5">
-        <v>0</v>
-      </c>
-      <c r="K82" s="5">
-        <v>11306</v>
-      </c>
-      <c r="L82" s="4"/>
+      <c r="L82" s="4" t="s">
+        <v>139</v>
+      </c>
       <c r="M82" s="4"/>
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
@@ -5532,15 +5534,15 @@
       <c r="S82" s="5"/>
       <c r="T82" s="5"/>
     </row>
-    <row r="83" ht="138" spans="1:20">
+    <row r="83" ht="180" spans="1:20">
       <c r="A83" s="5">
-        <v>11306</v>
+        <v>11305</v>
       </c>
       <c r="B83" s="5">
         <v>12</v>
       </c>
       <c r="C83" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83" s="5">
         <v>1</v>
@@ -5558,13 +5560,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J83" s="5">
         <v>0</v>
       </c>
       <c r="K83" s="5">
-        <v>11307</v>
+        <v>11306</v>
       </c>
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
@@ -5576,9 +5578,9 @@
       <c r="S83" s="5"/>
       <c r="T83" s="5"/>
     </row>
-    <row r="84" ht="138" spans="1:20">
+    <row r="84" ht="120" spans="1:20">
       <c r="A84" s="5">
-        <v>11307</v>
+        <v>11306</v>
       </c>
       <c r="B84" s="5">
         <v>12</v>
@@ -5602,13 +5604,13 @@
         <v>0</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J84" s="5">
         <v>0</v>
       </c>
       <c r="K84" s="5">
-        <v>11308</v>
+        <v>11307</v>
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
@@ -5620,43 +5622,41 @@
       <c r="S84" s="5"/>
       <c r="T84" s="5"/>
     </row>
-    <row r="85" ht="172" spans="1:20">
+    <row r="85" ht="120" spans="1:20">
       <c r="A85" s="5">
+        <v>11307</v>
+      </c>
+      <c r="B85" s="5">
+        <v>12</v>
+      </c>
+      <c r="C85" s="5">
+        <v>1</v>
+      </c>
+      <c r="D85" s="5">
+        <v>1</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G85" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H85" s="5">
+        <v>0</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J85" s="5">
+        <v>0</v>
+      </c>
+      <c r="K85" s="5">
         <v>11308</v>
       </c>
-      <c r="B85" s="5">
-        <v>0</v>
-      </c>
-      <c r="C85" s="5">
-        <v>5</v>
-      </c>
-      <c r="D85" s="5">
-        <v>1</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G85" s="5">
-        <v>-1</v>
-      </c>
-      <c r="H85" s="5">
-        <v>0</v>
-      </c>
-      <c r="I85" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="J85" s="5">
-        <v>0</v>
-      </c>
-      <c r="K85" s="5">
-        <v>0</v>
-      </c>
-      <c r="L85" s="4" t="s">
-        <v>143</v>
-      </c>
+      <c r="L85" s="4"/>
       <c r="M85" s="4"/>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
@@ -5666,24 +5666,24 @@
       <c r="S85" s="5"/>
       <c r="T85" s="5"/>
     </row>
-    <row r="86" ht="69" spans="1:20">
+    <row r="86" ht="150" spans="1:20">
       <c r="A86" s="5">
-        <v>2001</v>
+        <v>11308</v>
       </c>
       <c r="B86" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C86" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D86" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G86" s="5">
         <v>-1</v>
@@ -5692,7 +5692,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J86" s="5">
         <v>0</v>
@@ -5700,7 +5700,9 @@
       <c r="K86" s="5">
         <v>0</v>
       </c>
-      <c r="L86" s="4"/>
+      <c r="L86" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="M86" s="4"/>
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
@@ -5710,12 +5712,12 @@
       <c r="S86" s="5"/>
       <c r="T86" s="5"/>
     </row>
-    <row r="87" ht="69" spans="1:20">
+    <row r="87" ht="60" spans="1:20">
       <c r="A87" s="5">
-        <v>2101</v>
+        <v>2001</v>
       </c>
       <c r="B87" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C87" s="5">
         <v>0</v>
@@ -5724,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>47</v>
@@ -5736,7 +5738,7 @@
         <v>0</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J87" s="5">
         <v>0</v>
@@ -5754,12 +5756,12 @@
       <c r="S87" s="5"/>
       <c r="T87" s="5"/>
     </row>
-    <row r="88" ht="35" spans="1:20">
+    <row r="88" ht="60" spans="1:20">
       <c r="A88" s="5">
-        <v>2201</v>
+        <v>2101</v>
       </c>
       <c r="B88" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C88" s="5">
         <v>0</v>
@@ -5768,7 +5770,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>47</v>
@@ -5780,7 +5782,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J88" s="5">
         <v>0</v>
@@ -5798,12 +5800,12 @@
       <c r="S88" s="5"/>
       <c r="T88" s="5"/>
     </row>
-    <row r="89" ht="104" spans="1:20">
+    <row r="89" spans="1:20">
       <c r="A89" s="5">
-        <v>2301</v>
+        <v>2201</v>
       </c>
       <c r="B89" s="5">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C89" s="5">
         <v>0</v>
@@ -5812,9 +5814,9 @@
         <v>0</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F89" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F89" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G89" s="5">
@@ -5824,7 +5826,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="J89" s="5">
         <v>0</v>
@@ -5842,12 +5844,12 @@
       <c r="S89" s="5"/>
       <c r="T89" s="5"/>
     </row>
-    <row r="90" ht="69" spans="1:20">
+    <row r="90" ht="90" spans="1:20">
       <c r="A90" s="5">
-        <v>11401</v>
+        <v>2301</v>
       </c>
       <c r="B90" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C90" s="5">
         <v>0</v>
@@ -5856,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="G90" s="5">
         <v>-1</v>
@@ -5868,13 +5870,13 @@
         <v>0</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="J90" s="5">
         <v>0</v>
       </c>
       <c r="K90" s="5">
-        <v>11402</v>
+        <v>0</v>
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
@@ -5886,39 +5888,39 @@
       <c r="S90" s="5"/>
       <c r="T90" s="5"/>
     </row>
-    <row r="91" ht="104" spans="1:20">
+    <row r="91" ht="60" spans="1:20">
       <c r="A91" s="5">
+        <v>11401</v>
+      </c>
+      <c r="B91" s="5">
+        <v>1</v>
+      </c>
+      <c r="C91" s="5">
+        <v>0</v>
+      </c>
+      <c r="D91" s="5">
+        <v>0</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G91" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H91" s="5">
+        <v>0</v>
+      </c>
+      <c r="I91" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J91" s="5">
+        <v>0</v>
+      </c>
+      <c r="K91" s="5">
         <v>11402</v>
-      </c>
-      <c r="B91" s="5">
-        <v>0</v>
-      </c>
-      <c r="C91" s="5">
-        <v>0</v>
-      </c>
-      <c r="D91" s="5">
-        <v>1</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G91" s="5">
-        <v>-1</v>
-      </c>
-      <c r="H91" s="5">
-        <v>0</v>
-      </c>
-      <c r="I91" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J91" s="5">
-        <v>0</v>
-      </c>
-      <c r="K91" s="5">
-        <v>11403</v>
       </c>
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
@@ -5930,15 +5932,15 @@
       <c r="S91" s="5"/>
       <c r="T91" s="5"/>
     </row>
-    <row r="92" ht="69" spans="1:20">
+    <row r="92" ht="90" spans="1:20">
       <c r="A92" s="5">
-        <v>11403</v>
+        <v>11402</v>
       </c>
       <c r="B92" s="5">
         <v>0</v>
       </c>
       <c r="C92" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D92" s="5">
         <v>1</v>
@@ -5956,17 +5958,15 @@
         <v>0</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J92" s="5">
         <v>0</v>
       </c>
       <c r="K92" s="5">
-        <v>0</v>
-      </c>
-      <c r="L92" s="4" t="s">
-        <v>151</v>
-      </c>
+        <v>11403</v>
+      </c>
+      <c r="L92" s="4"/>
       <c r="M92" s="4"/>
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
@@ -5976,24 +5976,24 @@
       <c r="S92" s="5"/>
       <c r="T92" s="5"/>
     </row>
-    <row r="93" ht="104" spans="1:20">
+    <row r="93" ht="60" spans="1:20">
       <c r="A93" s="5">
-        <v>11501</v>
+        <v>11403</v>
       </c>
       <c r="B93" s="5">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C93" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D93" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G93" s="5">
         <v>-1</v>
@@ -6002,15 +6002,17 @@
         <v>0</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J93" s="5">
         <v>0</v>
       </c>
       <c r="K93" s="5">
-        <v>11502</v>
-      </c>
-      <c r="L93" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="L93" s="4" t="s">
+        <v>151</v>
+      </c>
       <c r="M93" s="4"/>
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
@@ -6020,39 +6022,39 @@
       <c r="S93" s="5"/>
       <c r="T93" s="5"/>
     </row>
-    <row r="94" ht="138" spans="1:20">
+    <row r="94" ht="90" spans="1:20">
       <c r="A94" s="5">
+        <v>11501</v>
+      </c>
+      <c r="B94" s="5">
+        <v>16</v>
+      </c>
+      <c r="C94" s="5">
+        <v>1</v>
+      </c>
+      <c r="D94" s="5">
+        <v>0</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G94" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H94" s="5">
+        <v>0</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="J94" s="5">
+        <v>0</v>
+      </c>
+      <c r="K94" s="5">
         <v>11502</v>
-      </c>
-      <c r="B94" s="5">
-        <v>2</v>
-      </c>
-      <c r="C94" s="5">
-        <v>1</v>
-      </c>
-      <c r="D94" s="5">
-        <v>1</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F94" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G94" s="5">
-        <v>-1</v>
-      </c>
-      <c r="H94" s="5">
-        <v>0</v>
-      </c>
-      <c r="I94" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="J94" s="5">
-        <v>0</v>
-      </c>
-      <c r="K94" s="5">
-        <v>11503</v>
       </c>
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
@@ -6064,9 +6066,9 @@
       <c r="S94" s="5"/>
       <c r="T94" s="5"/>
     </row>
-    <row r="95" ht="138" spans="1:20">
+    <row r="95" ht="120" spans="1:20">
       <c r="A95" s="5">
-        <v>11503</v>
+        <v>11502</v>
       </c>
       <c r="B95" s="5">
         <v>2</v>
@@ -6090,13 +6092,13 @@
         <v>0</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J95" s="5">
         <v>0</v>
       </c>
       <c r="K95" s="5">
-        <v>11504</v>
+        <v>11503</v>
       </c>
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
@@ -6108,9 +6110,9 @@
       <c r="S95" s="5"/>
       <c r="T95" s="5"/>
     </row>
-    <row r="96" ht="35" spans="1:20">
+    <row r="96" ht="120" spans="1:20">
       <c r="A96" s="5">
-        <v>11504</v>
+        <v>11503</v>
       </c>
       <c r="B96" s="5">
         <v>2</v>
@@ -6134,13 +6136,13 @@
         <v>0</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>67</v>
+        <v>155</v>
       </c>
       <c r="J96" s="5">
         <v>0</v>
       </c>
       <c r="K96" s="5">
-        <v>11505</v>
+        <v>11504</v>
       </c>
       <c r="L96" s="4"/>
       <c r="M96" s="4"/>
@@ -6152,9 +6154,9 @@
       <c r="S96" s="5"/>
       <c r="T96" s="5"/>
     </row>
-    <row r="97" ht="69" spans="1:20">
+    <row r="97" spans="1:20">
       <c r="A97" s="5">
-        <v>11505</v>
+        <v>11504</v>
       </c>
       <c r="B97" s="5">
         <v>2</v>
@@ -6178,13 +6180,13 @@
         <v>0</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>156</v>
+        <v>67</v>
       </c>
       <c r="J97" s="5">
         <v>0</v>
       </c>
       <c r="K97" s="5">
-        <v>11506</v>
+        <v>11505</v>
       </c>
       <c r="L97" s="4"/>
       <c r="M97" s="4"/>
@@ -6196,9 +6198,9 @@
       <c r="S97" s="5"/>
       <c r="T97" s="5"/>
     </row>
-    <row r="98" ht="35" spans="1:20">
+    <row r="98" ht="60" spans="1:20">
       <c r="A98" s="5">
-        <v>11506</v>
+        <v>11505</v>
       </c>
       <c r="B98" s="5">
         <v>2</v>
@@ -6222,13 +6224,13 @@
         <v>0</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J98" s="5">
         <v>0</v>
       </c>
       <c r="K98" s="5">
-        <v>11507</v>
+        <v>11506</v>
       </c>
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
@@ -6240,9 +6242,9 @@
       <c r="S98" s="5"/>
       <c r="T98" s="5"/>
     </row>
-    <row r="99" ht="69" spans="1:20">
+    <row r="99" spans="1:20">
       <c r="A99" s="5">
-        <v>11507</v>
+        <v>11506</v>
       </c>
       <c r="B99" s="5">
         <v>2</v>
@@ -6266,13 +6268,13 @@
         <v>0</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J99" s="5">
         <v>0</v>
       </c>
       <c r="K99" s="5">
-        <v>0</v>
+        <v>11507</v>
       </c>
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
@@ -6284,9 +6286,9 @@
       <c r="S99" s="5"/>
       <c r="T99" s="5"/>
     </row>
-    <row r="100" ht="172" spans="1:20">
+    <row r="100" ht="60" spans="1:20">
       <c r="A100" s="5">
-        <v>11601</v>
+        <v>11507</v>
       </c>
       <c r="B100" s="5">
         <v>2</v>
@@ -6295,7 +6297,7 @@
         <v>1</v>
       </c>
       <c r="D100" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100" s="8" t="s">
         <v>58</v>
@@ -6310,13 +6312,13 @@
         <v>0</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J100" s="5">
         <v>0</v>
       </c>
       <c r="K100" s="5">
-        <v>11602</v>
+        <v>0</v>
       </c>
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
@@ -6328,9 +6330,9 @@
       <c r="S100" s="5"/>
       <c r="T100" s="5"/>
     </row>
-    <row r="101" ht="104" spans="1:20">
+    <row r="101" ht="150" spans="1:20">
       <c r="A101" s="5">
-        <v>11602</v>
+        <v>11601</v>
       </c>
       <c r="B101" s="5">
         <v>2</v>
@@ -6339,7 +6341,7 @@
         <v>1</v>
       </c>
       <c r="D101" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" s="8" t="s">
         <v>58</v>
@@ -6354,13 +6356,13 @@
         <v>0</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J101" s="5">
         <v>0</v>
       </c>
       <c r="K101" s="5">
-        <v>11603</v>
+        <v>11602</v>
       </c>
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
@@ -6372,9 +6374,9 @@
       <c r="S101" s="5"/>
       <c r="T101" s="5"/>
     </row>
-    <row r="102" ht="35" spans="1:20">
+    <row r="102" ht="90" spans="1:20">
       <c r="A102" s="5">
-        <v>11603</v>
+        <v>11602</v>
       </c>
       <c r="B102" s="5">
         <v>2</v>
@@ -6398,13 +6400,13 @@
         <v>0</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>67</v>
+        <v>160</v>
       </c>
       <c r="J102" s="5">
         <v>0</v>
       </c>
       <c r="K102" s="5">
-        <v>11604</v>
+        <v>11603</v>
       </c>
       <c r="L102" s="4"/>
       <c r="M102" s="4"/>
@@ -6416,9 +6418,9 @@
       <c r="S102" s="5"/>
       <c r="T102" s="5"/>
     </row>
-    <row r="103" ht="104" spans="1:20">
+    <row r="103" spans="1:20">
       <c r="A103" s="5">
-        <v>11604</v>
+        <v>11603</v>
       </c>
       <c r="B103" s="5">
         <v>2</v>
@@ -6442,13 +6444,13 @@
         <v>0</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="J103" s="5">
         <v>0</v>
       </c>
       <c r="K103" s="5">
-        <v>11605</v>
+        <v>11604</v>
       </c>
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
@@ -6460,9 +6462,9 @@
       <c r="S103" s="5"/>
       <c r="T103" s="5"/>
     </row>
-    <row r="104" ht="35" spans="1:20">
+    <row r="104" ht="90" spans="1:20">
       <c r="A104" s="5">
-        <v>11605</v>
+        <v>11604</v>
       </c>
       <c r="B104" s="5">
         <v>2</v>
@@ -6486,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>67</v>
+        <v>161</v>
       </c>
       <c r="J104" s="5">
         <v>0</v>
       </c>
       <c r="K104" s="5">
-        <v>11606</v>
+        <v>11605</v>
       </c>
       <c r="L104" s="4"/>
       <c r="M104" s="4"/>
@@ -6504,9 +6506,9 @@
       <c r="S104" s="5"/>
       <c r="T104" s="5"/>
     </row>
-    <row r="105" ht="104" spans="1:20">
+    <row r="105" spans="1:20">
       <c r="A105" s="5">
-        <v>11606</v>
+        <v>11605</v>
       </c>
       <c r="B105" s="5">
         <v>2</v>
@@ -6530,13 +6532,13 @@
         <v>0</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>162</v>
+        <v>67</v>
       </c>
       <c r="J105" s="5">
         <v>0</v>
       </c>
       <c r="K105" s="5">
-        <v>0</v>
+        <v>11606</v>
       </c>
       <c r="L105" s="4"/>
       <c r="M105" s="4"/>
@@ -6548,24 +6550,24 @@
       <c r="S105" s="5"/>
       <c r="T105" s="5"/>
     </row>
-    <row r="106" ht="104" spans="1:20">
+    <row r="106" ht="90" spans="1:20">
       <c r="A106" s="5">
-        <v>2401</v>
+        <v>11606</v>
       </c>
       <c r="B106" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C106" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106" s="5">
-        <v>0</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G106" s="5">
         <v>-1</v>
@@ -6574,7 +6576,7 @@
         <v>0</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J106" s="5">
         <v>0</v>
@@ -6592,15 +6594,15 @@
       <c r="S106" s="5"/>
       <c r="T106" s="5"/>
     </row>
-    <row r="107" ht="104" spans="1:20">
+    <row r="107" ht="90" spans="1:20">
       <c r="A107" s="5">
-        <v>11701</v>
+        <v>2401</v>
       </c>
       <c r="B107" s="5">
         <v>0</v>
       </c>
       <c r="C107" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D107" s="5">
         <v>0</v>
@@ -6615,16 +6617,16 @@
         <v>-1</v>
       </c>
       <c r="H107" s="5">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J107" s="5">
         <v>0</v>
       </c>
       <c r="K107" s="5">
-        <v>11702</v>
+        <v>0</v>
       </c>
       <c r="L107" s="4"/>
       <c r="M107" s="4"/>
@@ -6636,18 +6638,18 @@
       <c r="S107" s="5"/>
       <c r="T107" s="5"/>
     </row>
-    <row r="108" ht="35" spans="1:20">
+    <row r="108" ht="90" spans="1:20">
       <c r="A108" s="5">
-        <v>11702</v>
+        <v>11701</v>
       </c>
       <c r="B108" s="5">
         <v>0</v>
       </c>
       <c r="C108" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D108" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108" s="5" t="s">
         <v>42</v>
@@ -6659,16 +6661,16 @@
         <v>-1</v>
       </c>
       <c r="H108" s="5">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J108" s="5">
         <v>0</v>
       </c>
       <c r="K108" s="5">
-        <v>11703</v>
+        <v>11702</v>
       </c>
       <c r="L108" s="4"/>
       <c r="M108" s="4"/>
@@ -6680,9 +6682,9 @@
       <c r="S108" s="5"/>
       <c r="T108" s="5"/>
     </row>
-    <row r="109" ht="69" spans="1:20">
+    <row r="109" spans="1:20">
       <c r="A109" s="5">
-        <v>11703</v>
+        <v>11702</v>
       </c>
       <c r="B109" s="5">
         <v>0</v>
@@ -6706,13 +6708,13 @@
         <v>0</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J109" s="5">
         <v>0</v>
       </c>
       <c r="K109" s="5">
-        <v>0</v>
+        <v>11703</v>
       </c>
       <c r="L109" s="4"/>
       <c r="M109" s="4"/>
@@ -6724,9 +6726,9 @@
       <c r="S109" s="5"/>
       <c r="T109" s="5"/>
     </row>
-    <row r="110" ht="69" spans="1:20">
+    <row r="110" ht="60" spans="1:20">
       <c r="A110" s="5">
-        <v>2501</v>
+        <v>11703</v>
       </c>
       <c r="B110" s="5">
         <v>0</v>
@@ -6735,7 +6737,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>42</v>
@@ -6750,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J110" s="5">
         <v>0</v>
@@ -6768,12 +6770,12 @@
       <c r="S110" s="5"/>
       <c r="T110" s="5"/>
     </row>
-    <row r="111" ht="69" spans="1:20">
+    <row r="111" ht="60" spans="1:20">
       <c r="A111" s="5">
-        <v>2601</v>
+        <v>2501</v>
       </c>
       <c r="B111" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C111" s="5">
         <v>0</v>
@@ -6781,11 +6783,11 @@
       <c r="D111" s="5">
         <v>0</v>
       </c>
-      <c r="E111" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F111" s="8" t="s">
-        <v>59</v>
+      <c r="E111" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G111" s="5">
         <v>-1</v>
@@ -6794,13 +6796,13 @@
         <v>0</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J111" s="5">
         <v>0</v>
       </c>
       <c r="K111" s="5">
-        <v>2602</v>
+        <v>0</v>
       </c>
       <c r="L111" s="4"/>
       <c r="M111" s="4"/>
@@ -6812,9 +6814,9 @@
       <c r="S111" s="5"/>
       <c r="T111" s="5"/>
     </row>
-    <row r="112" ht="104" spans="1:20">
+    <row r="112" ht="60" spans="1:20">
       <c r="A112" s="5">
-        <v>2602</v>
+        <v>2601</v>
       </c>
       <c r="B112" s="5">
         <v>2</v>
@@ -6823,7 +6825,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" s="8" t="s">
         <v>58</v>
@@ -6838,13 +6840,13 @@
         <v>0</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J112" s="5">
         <v>0</v>
       </c>
       <c r="K112" s="5">
-        <v>0</v>
+        <v>2602</v>
       </c>
       <c r="L112" s="4"/>
       <c r="M112" s="4"/>
@@ -6856,39 +6858,39 @@
       <c r="S112" s="5"/>
       <c r="T112" s="5"/>
     </row>
-    <row r="113" ht="69" spans="1:20">
+    <row r="113" ht="90" spans="1:20">
       <c r="A113" s="5">
-        <v>11801</v>
+        <v>2602</v>
       </c>
       <c r="B113" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C113" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D113" s="5">
-        <v>0</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G113" s="5">
         <v>-1</v>
       </c>
       <c r="H113" s="5">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J113" s="5">
         <v>0</v>
       </c>
       <c r="K113" s="5">
-        <v>11802</v>
+        <v>0</v>
       </c>
       <c r="L113" s="4"/>
       <c r="M113" s="4"/>
@@ -6900,9 +6902,9 @@
       <c r="S113" s="5"/>
       <c r="T113" s="5"/>
     </row>
-    <row r="114" ht="138" spans="1:20">
+    <row r="114" ht="63" spans="1:20">
       <c r="A114" s="5">
-        <v>11802</v>
+        <v>11801</v>
       </c>
       <c r="B114" s="5">
         <v>0</v>
@@ -6911,7 +6913,7 @@
         <v>4</v>
       </c>
       <c r="D114" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" s="5" t="s">
         <v>42</v>
@@ -6926,13 +6928,13 @@
         <v>-10</v>
       </c>
       <c r="I114" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J114" s="5">
         <v>0</v>
       </c>
       <c r="K114" s="5">
-        <v>11803</v>
+        <v>11802</v>
       </c>
       <c r="L114" s="4"/>
       <c r="M114" s="4"/>
@@ -6944,9 +6946,9 @@
       <c r="S114" s="5"/>
       <c r="T114" s="5"/>
     </row>
-    <row r="115" ht="69" spans="1:20">
+    <row r="115" ht="120" spans="1:20">
       <c r="A115" s="5">
-        <v>11803</v>
+        <v>11802</v>
       </c>
       <c r="B115" s="5">
         <v>0</v>
@@ -6970,13 +6972,13 @@
         <v>-10</v>
       </c>
       <c r="I115" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J115" s="5">
         <v>0</v>
       </c>
       <c r="K115" s="5">
-        <v>0</v>
+        <v>11803</v>
       </c>
       <c r="L115" s="4"/>
       <c r="M115" s="4"/>
@@ -6988,10 +6990,54 @@
       <c r="S115" s="5"/>
       <c r="T115" s="5"/>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="5"/>
-      <c r="B116" s="5"/>
-      <c r="C116" s="5"/>
+    <row r="116" ht="60" spans="1:20">
+      <c r="A116" s="5">
+        <v>11803</v>
+      </c>
+      <c r="B116" s="5">
+        <v>0</v>
+      </c>
+      <c r="C116" s="5">
+        <v>4</v>
+      </c>
+      <c r="D116" s="5">
+        <v>1</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G116" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H116" s="5">
+        <v>-10</v>
+      </c>
+      <c r="I116" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="J116" s="5">
+        <v>0</v>
+      </c>
+      <c r="K116" s="5">
+        <v>0</v>
+      </c>
+      <c r="L116" s="4"/>
+      <c r="M116" s="4"/>
+      <c r="N116" s="4"/>
+      <c r="O116" s="4"/>
+      <c r="P116" s="4"/>
+      <c r="Q116" s="5"/>
+      <c r="R116" s="5"/>
+      <c r="S116" s="5"/>
+      <c r="T116" s="5"/>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="5"/>
+      <c r="B117" s="5"/>
+      <c r="C117" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Excel/DialogDatas.xlsx
+++ b/Excel/DialogDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="12780"/>
+    <workbookView windowHeight="14900"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="181">
   <si>
     <t>int</t>
   </si>
@@ -344,33 +344,40 @@
     <t>我才不怕呢，有怪兽我会打败它的。</t>
   </si>
   <si>
-    <t xml:space="preserve">这里感觉好像平常的街道 </t>
-  </si>
-  <si>
-    <t>哇我穿着勇士的铠甲，还有一把剑</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <color rgb="FF000000"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>又是怪兽！</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>等等，那个人好像是我们镇上的，得快点去救他！</t>
-    </r>
-  </si>
-  <si>
-    <t>水晶闪着奇异的光芒</t>
+    <t>这是怎么回事？</t>
+  </si>
+  <si>
+    <t>我为什么会变成这幅模样</t>
+  </si>
+  <si>
+    <t>等等，我感觉身体变得很轻盈，感觉跑的速度更快了，一跳可以跳的很高</t>
+  </si>
+  <si>
+    <t>按下&lt;color=yellow&gt;A&lt;/color&gt;和&lt;color=yellow&gt;D&lt;/color&gt;键进行左右移动</t>
+  </si>
+  <si>
+    <t>按下A和D键进行左右移动</t>
+  </si>
+  <si>
+    <t>按下&lt;color=yellow&gt;Space&lt;/color&gt;键进行跳跃，连续按下可以进行二连跳</t>
+  </si>
+  <si>
+    <t>按下Space键进行跳跃，连续按下可以进行而连跳</t>
+  </si>
+  <si>
+    <t>在平台上可以通过&lt;color=yellow&gt;S+Space&lt;/color&gt;进行下平台</t>
+  </si>
+  <si>
+    <t>在平台上可以通过S+Space进行下平台</t>
+  </si>
+  <si>
+    <t>按下&lt;color=yellow&gt;J&lt;/color&gt;键可以进行普通攻击1，按下&lt;color=yellow&gt;K&lt;/color&gt;键可以进行普通攻击2</t>
+  </si>
+  <si>
+    <t>按下J键可以进行普通攻击1，按下K键可以进行普通攻击2</t>
+  </si>
+  <si>
+    <t>你已经熟悉了全部操作，尝试通过这里吧</t>
   </si>
   <si>
     <t>这太奇怪了，我居然又做了这种梦</t>
@@ -609,7 +616,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -808,12 +815,6 @@
     <font>
       <sz val="24"/>
       <color rgb="FF333333"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="24"/>
-      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1828,29 +1829,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T117"/>
-  <sheetFormatPr defaultColWidth="9.22222222222222" defaultRowHeight="30.6"/>
+  <dimension ref="A1:T121"/>
+  <sheetFormatPr defaultColWidth="9.22115384615385" defaultRowHeight="34.4"/>
   <cols>
     <col min="1" max="1" width="21" style="2" customWidth="1"/>
-    <col min="2" max="2" width="33.6666666666667" style="2" customWidth="1"/>
-    <col min="3" max="3" width="37.6666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25.4444444444444" style="2" customWidth="1"/>
-    <col min="5" max="5" width="26.1111111111111" style="2" customWidth="1"/>
-    <col min="6" max="6" width="50.8888888888889" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23.6666666666667" style="2" customWidth="1"/>
-    <col min="8" max="8" width="26.1111111111111" style="2" customWidth="1"/>
-    <col min="9" max="9" width="40.8333333333333" style="2" customWidth="1"/>
-    <col min="10" max="10" width="30.1111111111111" style="2" customWidth="1"/>
-    <col min="11" max="11" width="25.6666666666667" style="2" customWidth="1"/>
-    <col min="12" max="16" width="25.6666666666667" style="3" customWidth="1"/>
-    <col min="17" max="17" width="40.0648148148148" style="2" customWidth="1"/>
-    <col min="18" max="18" width="48.4814814814815" style="2" customWidth="1"/>
-    <col min="19" max="19" width="43.2685185185185" style="2" customWidth="1"/>
-    <col min="20" max="20" width="38.8518518518519" style="2" customWidth="1"/>
-    <col min="21" max="16384" width="9.22222222222222" style="2"/>
+    <col min="2" max="2" width="33.6634615384615" style="2" customWidth="1"/>
+    <col min="3" max="3" width="37.6634615384615" style="2" customWidth="1"/>
+    <col min="4" max="4" width="25.4423076923077" style="2" customWidth="1"/>
+    <col min="5" max="5" width="26.1153846153846" style="2" customWidth="1"/>
+    <col min="6" max="6" width="50.8846153846154" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.6634615384615" style="2" customWidth="1"/>
+    <col min="8" max="8" width="26.1153846153846" style="2" customWidth="1"/>
+    <col min="9" max="9" width="40.8365384615385" style="2" customWidth="1"/>
+    <col min="10" max="10" width="30.1153846153846" style="2" customWidth="1"/>
+    <col min="11" max="11" width="25.6634615384615" style="2" customWidth="1"/>
+    <col min="12" max="16" width="25.6634615384615" style="3" customWidth="1"/>
+    <col min="17" max="17" width="40.0673076923077" style="2" customWidth="1"/>
+    <col min="18" max="18" width="48.4807692307692" style="2" customWidth="1"/>
+    <col min="19" max="19" width="43.2692307692308" style="2" customWidth="1"/>
+    <col min="20" max="20" width="38.8557692307692" style="2" customWidth="1"/>
+    <col min="21" max="16384" width="9.22115384615385" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" ht="35" spans="1:20">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1974,7 +1975,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" ht="35" spans="1:20">
       <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
@@ -2036,7 +2037,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" ht="90" spans="1:20">
+    <row r="4" ht="104" spans="1:20">
       <c r="A4" s="5">
         <v>10001</v>
       </c>
@@ -2080,7 +2081,7 @@
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
     </row>
-    <row r="5" ht="90" spans="1:20">
+    <row r="5" ht="104" spans="1:20">
       <c r="A5" s="5">
         <v>10002</v>
       </c>
@@ -2124,7 +2125,7 @@
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
     </row>
-    <row r="6" ht="120" spans="1:20">
+    <row r="6" ht="138" spans="1:20">
       <c r="A6" s="5">
         <v>1001</v>
       </c>
@@ -2168,7 +2169,7 @@
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
     </row>
-    <row r="7" ht="90" spans="1:20">
+    <row r="7" ht="104" spans="1:20">
       <c r="A7" s="5">
         <v>1101</v>
       </c>
@@ -2212,7 +2213,7 @@
       <c r="S7" s="5"/>
       <c r="T7" s="5"/>
     </row>
-    <row r="8" ht="90" spans="1:20">
+    <row r="8" ht="104" spans="1:20">
       <c r="A8" s="5">
         <v>1201</v>
       </c>
@@ -2256,7 +2257,7 @@
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
     </row>
-    <row r="9" ht="120" spans="1:20">
+    <row r="9" ht="138" spans="1:20">
       <c r="A9" s="5">
         <v>1202</v>
       </c>
@@ -2300,7 +2301,7 @@
       <c r="S9" s="5"/>
       <c r="T9" s="5"/>
     </row>
-    <row r="10" ht="90" spans="1:20">
+    <row r="10" ht="104" spans="1:20">
       <c r="A10" s="5">
         <v>1203</v>
       </c>
@@ -2344,7 +2345,7 @@
       <c r="S10" s="5"/>
       <c r="T10" s="5"/>
     </row>
-    <row r="11" ht="120" spans="1:20">
+    <row r="11" ht="138" spans="1:20">
       <c r="A11" s="5">
         <v>10050</v>
       </c>
@@ -2390,7 +2391,7 @@
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
     </row>
-    <row r="12" ht="60" spans="1:20">
+    <row r="12" ht="69" spans="1:20">
       <c r="A12" s="5">
         <v>10101</v>
       </c>
@@ -2434,7 +2435,7 @@
       <c r="S12" s="5"/>
       <c r="T12" s="5"/>
     </row>
-    <row r="13" s="1" customFormat="1" ht="90" spans="1:20">
+    <row r="13" s="1" customFormat="1" ht="104" spans="1:20">
       <c r="A13" s="6">
         <v>10201</v>
       </c>
@@ -2478,7 +2479,7 @@
       <c r="S13" s="6"/>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" ht="90" spans="1:20">
+    <row r="14" ht="104" spans="1:20">
       <c r="A14" s="5">
         <v>10202</v>
       </c>
@@ -2524,7 +2525,7 @@
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
     </row>
-    <row r="15" ht="60" spans="1:20">
+    <row r="15" ht="69" spans="1:20">
       <c r="A15" s="5">
         <v>10203</v>
       </c>
@@ -2568,7 +2569,7 @@
       <c r="S15" s="5"/>
       <c r="T15" s="5"/>
     </row>
-    <row r="16" ht="120" spans="1:20">
+    <row r="16" ht="138" spans="1:20">
       <c r="A16" s="5">
         <v>10204</v>
       </c>
@@ -2612,7 +2613,7 @@
       <c r="S16" s="5"/>
       <c r="T16" s="5"/>
     </row>
-    <row r="17" ht="120" spans="1:20">
+    <row r="17" ht="138" spans="1:20">
       <c r="A17" s="5">
         <v>10205</v>
       </c>
@@ -2656,7 +2657,7 @@
       <c r="S17" s="5"/>
       <c r="T17" s="5"/>
     </row>
-    <row r="18" s="1" customFormat="1" ht="90" spans="1:20">
+    <row r="18" s="1" customFormat="1" ht="104" spans="1:20">
       <c r="A18" s="5">
         <v>10206</v>
       </c>
@@ -2700,7 +2701,7 @@
       <c r="S18" s="6"/>
       <c r="T18" s="6"/>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" ht="35" spans="1:20">
       <c r="A19" s="5">
         <v>10207</v>
       </c>
@@ -2744,7 +2745,7 @@
       <c r="S19" s="5"/>
       <c r="T19" s="5"/>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" ht="35" spans="1:20">
       <c r="A20" s="5">
         <v>10208</v>
       </c>
@@ -2788,7 +2789,7 @@
       <c r="S20" s="5"/>
       <c r="T20" s="5"/>
     </row>
-    <row r="21" ht="60" spans="1:20">
+    <row r="21" ht="69" spans="1:20">
       <c r="A21" s="5">
         <v>1301</v>
       </c>
@@ -2832,7 +2833,7 @@
       <c r="S21" s="5"/>
       <c r="T21" s="5"/>
     </row>
-    <row r="22" ht="120" spans="1:20">
+    <row r="22" ht="138" spans="1:20">
       <c r="A22" s="5">
         <v>1302</v>
       </c>
@@ -2876,7 +2877,7 @@
       <c r="S22" s="5"/>
       <c r="T22" s="5"/>
     </row>
-    <row r="23" ht="60" spans="1:20">
+    <row r="23" ht="69" spans="1:20">
       <c r="A23" s="5">
         <v>1401</v>
       </c>
@@ -2920,7 +2921,7 @@
       <c r="S23" s="5"/>
       <c r="T23" s="5"/>
     </row>
-    <row r="24" ht="120" spans="1:20">
+    <row r="24" ht="138" spans="1:20">
       <c r="A24" s="5">
         <v>1402</v>
       </c>
@@ -2964,7 +2965,7 @@
       <c r="S24" s="5"/>
       <c r="T24" s="5"/>
     </row>
-    <row r="25" ht="90" spans="1:20">
+    <row r="25" ht="104" spans="1:20">
       <c r="A25" s="5">
         <v>1501</v>
       </c>
@@ -3008,7 +3009,7 @@
       <c r="S25" s="5"/>
       <c r="T25" s="5"/>
     </row>
-    <row r="26" ht="150" spans="1:20">
+    <row r="26" ht="172" spans="1:20">
       <c r="A26" s="5">
         <v>1502</v>
       </c>
@@ -3052,7 +3053,7 @@
       <c r="S26" s="5"/>
       <c r="T26" s="5"/>
     </row>
-    <row r="27" ht="90" spans="1:20">
+    <row r="27" ht="104" spans="1:20">
       <c r="A27" s="5">
         <v>1601</v>
       </c>
@@ -3096,7 +3097,7 @@
       <c r="S27" s="5"/>
       <c r="T27" s="5"/>
     </row>
-    <row r="28" ht="60" spans="1:20">
+    <row r="28" ht="69" spans="1:20">
       <c r="A28" s="5">
         <v>1701</v>
       </c>
@@ -3140,7 +3141,7 @@
       <c r="S28" s="5"/>
       <c r="T28" s="5"/>
     </row>
-    <row r="29" ht="60" spans="1:20">
+    <row r="29" ht="69" spans="1:20">
       <c r="A29" s="5">
         <v>10301</v>
       </c>
@@ -3184,7 +3185,7 @@
       <c r="S29" s="5"/>
       <c r="T29" s="5"/>
     </row>
-    <row r="30" ht="90" spans="1:20">
+    <row r="30" ht="104" spans="1:20">
       <c r="A30" s="5">
         <v>10401</v>
       </c>
@@ -3228,7 +3229,7 @@
       <c r="S30" s="5"/>
       <c r="T30" s="5"/>
     </row>
-    <row r="31" ht="90" spans="1:20">
+    <row r="31" ht="104" spans="1:20">
       <c r="A31" s="5">
         <v>10402</v>
       </c>
@@ -3272,7 +3273,7 @@
       <c r="S31" s="5"/>
       <c r="T31" s="5"/>
     </row>
-    <row r="32" ht="120" spans="1:20">
+    <row r="32" ht="138" spans="1:20">
       <c r="A32" s="5">
         <v>10404</v>
       </c>
@@ -3316,7 +3317,7 @@
       <c r="S32" s="5"/>
       <c r="T32" s="5"/>
     </row>
-    <row r="33" spans="1:20">
+    <row r="33" ht="35" spans="1:20">
       <c r="A33" s="5">
         <v>10403</v>
       </c>
@@ -3360,7 +3361,7 @@
       <c r="S33" s="5"/>
       <c r="T33" s="5"/>
     </row>
-    <row r="34" ht="90" spans="1:20">
+    <row r="34" ht="104" spans="1:20">
       <c r="A34" s="5">
         <v>10501</v>
       </c>
@@ -3404,7 +3405,7 @@
       <c r="S34" s="5"/>
       <c r="T34" s="5"/>
     </row>
-    <row r="35" ht="90" spans="1:20">
+    <row r="35" ht="104" spans="1:20">
       <c r="A35" s="5">
         <v>10502</v>
       </c>
@@ -3448,7 +3449,7 @@
       <c r="S35" s="5"/>
       <c r="T35" s="5"/>
     </row>
-    <row r="36" s="1" customFormat="1" ht="120" spans="1:20">
+    <row r="36" s="1" customFormat="1" ht="138" spans="1:20">
       <c r="A36" s="5">
         <v>10503</v>
       </c>
@@ -3494,7 +3495,7 @@
       <c r="S36" s="5"/>
       <c r="T36" s="5"/>
     </row>
-    <row r="37" s="1" customFormat="1" ht="150" spans="1:20">
+    <row r="37" s="1" customFormat="1" ht="172" spans="1:20">
       <c r="A37" s="6">
         <v>10550</v>
       </c>
@@ -3540,7 +3541,7 @@
       <c r="S37" s="6"/>
       <c r="T37" s="6"/>
     </row>
-    <row r="38" s="1" customFormat="1" ht="150" spans="1:20">
+    <row r="38" s="1" customFormat="1" ht="172" spans="1:20">
       <c r="A38" s="6">
         <v>1801</v>
       </c>
@@ -3628,7 +3629,7 @@
       <c r="S39" s="6"/>
       <c r="T39" s="6"/>
     </row>
-    <row r="40" customFormat="1" ht="60" spans="1:20">
+    <row r="40" customFormat="1" ht="69" spans="1:20">
       <c r="A40" s="5">
         <v>1803</v>
       </c>
@@ -3678,7 +3679,7 @@
       <c r="S40" s="5"/>
       <c r="T40" s="5"/>
     </row>
-    <row r="41" ht="60" spans="1:20">
+    <row r="41" ht="69" spans="1:20">
       <c r="A41" s="5">
         <v>10601</v>
       </c>
@@ -3722,7 +3723,7 @@
       <c r="S41" s="5"/>
       <c r="T41" s="5"/>
     </row>
-    <row r="42" spans="1:20">
+    <row r="42" ht="35" spans="1:20">
       <c r="A42" s="5">
         <v>10602</v>
       </c>
@@ -3766,7 +3767,7 @@
       <c r="S42" s="5"/>
       <c r="T42" s="5"/>
     </row>
-    <row r="43" ht="60" spans="1:20">
+    <row r="43" ht="69" spans="1:20">
       <c r="A43" s="5">
         <v>10603</v>
       </c>
@@ -3810,7 +3811,7 @@
       <c r="S43" s="5"/>
       <c r="T43" s="5"/>
     </row>
-    <row r="44" ht="60" spans="1:20">
+    <row r="44" ht="69" spans="1:20">
       <c r="A44" s="5">
         <v>10604</v>
       </c>
@@ -3854,7 +3855,7 @@
       <c r="S44" s="5"/>
       <c r="T44" s="5"/>
     </row>
-    <row r="45" ht="60" spans="1:20">
+    <row r="45" ht="35" spans="1:20">
       <c r="A45" s="5">
         <v>10701</v>
       </c>
@@ -3898,7 +3899,7 @@
       <c r="S45" s="5"/>
       <c r="T45" s="5"/>
     </row>
-    <row r="46" ht="60" spans="1:20">
+    <row r="46" ht="69" spans="1:20">
       <c r="A46" s="5">
         <v>10702</v>
       </c>
@@ -3942,7 +3943,7 @@
       <c r="S46" s="5"/>
       <c r="T46" s="5"/>
     </row>
-    <row r="47" ht="132" spans="1:20">
+    <row r="47" ht="138" spans="1:20">
       <c r="A47" s="5">
         <v>10703</v>
       </c>
@@ -3986,7 +3987,7 @@
       <c r="S47" s="5"/>
       <c r="T47" s="5"/>
     </row>
-    <row r="48" ht="60" spans="1:20">
+    <row r="48" ht="207" spans="1:20">
       <c r="A48" s="5">
         <v>10704</v>
       </c>
@@ -3994,7 +3995,7 @@
         <v>0</v>
       </c>
       <c r="C48" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D48" s="5">
         <v>1</v>
@@ -4018,9 +4019,11 @@
         <v>0</v>
       </c>
       <c r="K48" s="5">
-        <v>0</v>
-      </c>
-      <c r="L48" s="4"/>
+        <v>10705</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>109</v>
+      </c>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
@@ -4030,18 +4033,18 @@
       <c r="S48" s="5"/>
       <c r="T48" s="5"/>
     </row>
-    <row r="49" ht="60" spans="1:20">
+    <row r="49" ht="172" spans="1:20">
       <c r="A49" s="5">
-        <v>10801</v>
+        <v>10705</v>
       </c>
       <c r="B49" s="5">
         <v>0</v>
       </c>
       <c r="C49" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D49" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>42</v>
@@ -4056,15 +4059,17 @@
         <v>0</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J49" s="5">
         <v>0</v>
       </c>
       <c r="K49" s="5">
-        <v>10802</v>
-      </c>
-      <c r="L49" s="4"/>
+        <v>10706</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>111</v>
+      </c>
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
@@ -4074,18 +4079,18 @@
       <c r="S49" s="5"/>
       <c r="T49" s="5"/>
     </row>
-    <row r="50" ht="120" spans="1:20">
+    <row r="50" ht="138" spans="1:20">
       <c r="A50" s="5">
-        <v>10802</v>
+        <v>10706</v>
       </c>
       <c r="B50" s="5">
         <v>0</v>
       </c>
       <c r="C50" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D50" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>42</v>
@@ -4097,17 +4102,19 @@
         <v>-1</v>
       </c>
       <c r="H50" s="5">
-        <v>-10</v>
-      </c>
-      <c r="I50" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>112</v>
+      </c>
       <c r="J50" s="5">
         <v>0</v>
       </c>
       <c r="K50" s="5">
-        <v>10803</v>
+        <v>10707</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
@@ -4118,15 +4125,15 @@
       <c r="S50" s="5"/>
       <c r="T50" s="5"/>
     </row>
-    <row r="51" ht="63" spans="1:20">
+    <row r="51" ht="241" spans="1:20">
       <c r="A51" s="5">
-        <v>10803</v>
+        <v>10707</v>
       </c>
       <c r="B51" s="5">
         <v>0</v>
       </c>
       <c r="C51" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D51" s="5">
         <v>1</v>
@@ -4144,15 +4151,17 @@
         <v>0</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J51" s="5">
         <v>0</v>
       </c>
       <c r="K51" s="5">
-        <v>10804</v>
-      </c>
-      <c r="L51" s="4"/>
+        <v>10708</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>115</v>
+      </c>
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
@@ -4162,15 +4171,15 @@
       <c r="S51" s="5"/>
       <c r="T51" s="5"/>
     </row>
-    <row r="52" ht="60" spans="1:20">
+    <row r="52" ht="138" spans="1:20">
       <c r="A52" s="5">
-        <v>10804</v>
+        <v>10708</v>
       </c>
       <c r="B52" s="5">
         <v>0</v>
       </c>
       <c r="C52" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D52" s="5">
         <v>1</v>
@@ -4188,7 +4197,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="J52" s="5">
         <v>0</v>
@@ -4196,7 +4205,9 @@
       <c r="K52" s="5">
         <v>0</v>
       </c>
-      <c r="L52" s="4"/>
+      <c r="L52" s="4" t="s">
+        <v>116</v>
+      </c>
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
@@ -4206,15 +4217,15 @@
       <c r="S52" s="5"/>
       <c r="T52" s="5"/>
     </row>
-    <row r="53" ht="90" spans="1:20">
+    <row r="53" ht="69" spans="1:20">
       <c r="A53" s="5">
-        <v>10901</v>
+        <v>10801</v>
       </c>
       <c r="B53" s="5">
         <v>0</v>
       </c>
       <c r="C53" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" s="5">
         <v>0</v>
@@ -4232,13 +4243,13 @@
         <v>0</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J53" s="5">
         <v>0</v>
       </c>
       <c r="K53" s="5">
-        <v>10902</v>
+        <v>10802</v>
       </c>
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
@@ -4250,18 +4261,18 @@
       <c r="S53" s="5"/>
       <c r="T53" s="5"/>
     </row>
-    <row r="54" ht="90" spans="1:20">
+    <row r="54" ht="138" spans="1:20">
       <c r="A54" s="5">
-        <v>10902</v>
+        <v>10802</v>
       </c>
       <c r="B54" s="5">
         <v>0</v>
       </c>
       <c r="C54" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D54" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>42</v>
@@ -4273,18 +4284,18 @@
         <v>-1</v>
       </c>
       <c r="H54" s="5">
-        <v>0</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>113</v>
-      </c>
+        <v>-10</v>
+      </c>
+      <c r="I54" s="4"/>
       <c r="J54" s="5">
         <v>0</v>
       </c>
       <c r="K54" s="5">
-        <v>10903</v>
-      </c>
-      <c r="L54" s="4"/>
+        <v>10803</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>118</v>
+      </c>
       <c r="M54" s="4"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
@@ -4294,15 +4305,15 @@
       <c r="S54" s="5"/>
       <c r="T54" s="5"/>
     </row>
-    <row r="55" ht="90" spans="1:20">
+    <row r="55" ht="69" spans="1:20">
       <c r="A55" s="5">
-        <v>10903</v>
+        <v>10803</v>
       </c>
       <c r="B55" s="5">
         <v>0</v>
       </c>
       <c r="C55" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55" s="5">
         <v>1</v>
@@ -4320,13 +4331,13 @@
         <v>0</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="J55" s="5">
         <v>0</v>
       </c>
       <c r="K55" s="5">
-        <v>10904</v>
+        <v>10804</v>
       </c>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
@@ -4338,15 +4349,15 @@
       <c r="S55" s="5"/>
       <c r="T55" s="5"/>
     </row>
-    <row r="56" ht="60" spans="1:20">
+    <row r="56" ht="69" spans="1:20">
       <c r="A56" s="5">
-        <v>10904</v>
+        <v>10804</v>
       </c>
       <c r="B56" s="5">
         <v>0</v>
       </c>
       <c r="C56" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" s="5">
         <v>1</v>
@@ -4364,13 +4375,13 @@
         <v>0</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="J56" s="5">
         <v>0</v>
       </c>
       <c r="K56" s="5">
-        <v>10905</v>
+        <v>0</v>
       </c>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
@@ -4382,24 +4393,24 @@
       <c r="S56" s="5"/>
       <c r="T56" s="5"/>
     </row>
-    <row r="57" ht="120" spans="1:20">
+    <row r="57" ht="104" spans="1:20">
       <c r="A57" s="5">
-        <v>10905</v>
+        <v>10901</v>
       </c>
       <c r="B57" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C57" s="5">
         <v>1</v>
       </c>
       <c r="D57" s="5">
-        <v>1</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>59</v>
+        <v>0</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G57" s="5">
         <v>-1</v>
@@ -4408,13 +4419,13 @@
         <v>0</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J57" s="5">
         <v>0</v>
       </c>
       <c r="K57" s="5">
-        <v>10906</v>
+        <v>10902</v>
       </c>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
@@ -4426,9 +4437,9 @@
       <c r="S57" s="5"/>
       <c r="T57" s="5"/>
     </row>
-    <row r="58" ht="120" spans="1:20">
+    <row r="58" ht="104" spans="1:20">
       <c r="A58" s="5">
-        <v>10906</v>
+        <v>10902</v>
       </c>
       <c r="B58" s="5">
         <v>0</v>
@@ -4452,13 +4463,13 @@
         <v>0</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="J58" s="5">
         <v>0</v>
       </c>
       <c r="K58" s="5">
-        <v>10907</v>
+        <v>10903</v>
       </c>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
@@ -4470,12 +4481,12 @@
       <c r="S58" s="5"/>
       <c r="T58" s="5"/>
     </row>
-    <row r="59" ht="60" spans="1:20">
+    <row r="59" ht="104" spans="1:20">
       <c r="A59" s="5">
-        <v>10907</v>
+        <v>10903</v>
       </c>
       <c r="B59" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C59" s="5">
         <v>1</v>
@@ -4483,11 +4494,11 @@
       <c r="D59" s="5">
         <v>1</v>
       </c>
-      <c r="E59" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>59</v>
+      <c r="E59" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G59" s="5">
         <v>-1</v>
@@ -4496,13 +4507,13 @@
         <v>0</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J59" s="5">
         <v>0</v>
       </c>
       <c r="K59" s="5">
-        <v>10908</v>
+        <v>10904</v>
       </c>
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
@@ -4514,9 +4525,9 @@
       <c r="S59" s="5"/>
       <c r="T59" s="5"/>
     </row>
-    <row r="60" ht="60" spans="1:20">
+    <row r="60" ht="69" spans="1:20">
       <c r="A60" s="5">
-        <v>10908</v>
+        <v>10904</v>
       </c>
       <c r="B60" s="5">
         <v>0</v>
@@ -4540,13 +4551,13 @@
         <v>0</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="J60" s="5">
         <v>0</v>
       </c>
       <c r="K60" s="5">
-        <v>10909</v>
+        <v>10905</v>
       </c>
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
@@ -4558,12 +4569,12 @@
       <c r="S60" s="5"/>
       <c r="T60" s="5"/>
     </row>
-    <row r="61" ht="90" spans="1:20">
+    <row r="61" ht="138" spans="1:20">
       <c r="A61" s="5">
-        <v>10909</v>
+        <v>10905</v>
       </c>
       <c r="B61" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C61" s="5">
         <v>1</v>
@@ -4571,11 +4582,11 @@
       <c r="D61" s="5">
         <v>1</v>
       </c>
-      <c r="E61" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>43</v>
+      <c r="E61" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="G61" s="5">
         <v>-1</v>
@@ -4584,13 +4595,13 @@
         <v>0</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J61" s="5">
         <v>0</v>
       </c>
       <c r="K61" s="5">
-        <v>10910</v>
+        <v>10906</v>
       </c>
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
@@ -4602,12 +4613,12 @@
       <c r="S61" s="5"/>
       <c r="T61" s="5"/>
     </row>
-    <row r="62" ht="90" spans="1:20">
+    <row r="62" ht="138" spans="1:20">
       <c r="A62" s="5">
-        <v>10910</v>
+        <v>10906</v>
       </c>
       <c r="B62" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C62" s="5">
         <v>1</v>
@@ -4615,11 +4626,11 @@
       <c r="D62" s="5">
         <v>1</v>
       </c>
-      <c r="E62" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>59</v>
+      <c r="E62" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G62" s="5">
         <v>-1</v>
@@ -4628,13 +4639,13 @@
         <v>0</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J62" s="5">
         <v>0</v>
       </c>
       <c r="K62" s="5">
-        <v>10911</v>
+        <v>10907</v>
       </c>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
@@ -4646,12 +4657,12 @@
       <c r="S62" s="5"/>
       <c r="T62" s="5"/>
     </row>
-    <row r="63" ht="60" spans="1:20">
+    <row r="63" ht="69" spans="1:20">
       <c r="A63" s="5">
-        <v>10911</v>
+        <v>10907</v>
       </c>
       <c r="B63" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C63" s="5">
         <v>1</v>
@@ -4659,11 +4670,11 @@
       <c r="D63" s="5">
         <v>1</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>43</v>
+      <c r="E63" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G63" s="5">
         <v>-1</v>
@@ -4672,13 +4683,13 @@
         <v>0</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="J63" s="5">
         <v>0</v>
       </c>
       <c r="K63" s="5">
-        <v>10912</v>
+        <v>10908</v>
       </c>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
@@ -4690,15 +4701,15 @@
       <c r="S63" s="5"/>
       <c r="T63" s="5"/>
     </row>
-    <row r="64" ht="90" spans="1:20">
+    <row r="64" ht="69" spans="1:20">
       <c r="A64" s="5">
-        <v>10912</v>
+        <v>10908</v>
       </c>
       <c r="B64" s="5">
         <v>0</v>
       </c>
       <c r="C64" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D64" s="5">
         <v>1</v>
@@ -4716,17 +4727,15 @@
         <v>0</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J64" s="5">
         <v>0</v>
       </c>
       <c r="K64" s="5">
-        <v>0</v>
-      </c>
-      <c r="L64" s="4" t="s">
-        <v>123</v>
-      </c>
+        <v>10909</v>
+      </c>
+      <c r="L64" s="4"/>
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
@@ -4736,24 +4745,24 @@
       <c r="S64" s="5"/>
       <c r="T64" s="5"/>
     </row>
-    <row r="65" ht="90" spans="1:20">
+    <row r="65" ht="104" spans="1:20">
       <c r="A65" s="5">
-        <v>10950</v>
+        <v>10909</v>
       </c>
       <c r="B65" s="5">
         <v>0</v>
       </c>
       <c r="C65" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D65" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G65" s="5">
         <v>-1</v>
@@ -4762,17 +4771,15 @@
         <v>0</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J65" s="5">
         <v>0</v>
       </c>
       <c r="K65" s="5">
-        <v>0</v>
-      </c>
-      <c r="L65" s="4" t="s">
-        <v>123</v>
-      </c>
+        <v>10910</v>
+      </c>
+      <c r="L65" s="4"/>
       <c r="M65" s="4"/>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
@@ -4782,24 +4789,24 @@
       <c r="S65" s="5"/>
       <c r="T65" s="5"/>
     </row>
-    <row r="66" ht="90" spans="1:20">
+    <row r="66" ht="104" spans="1:20">
       <c r="A66" s="5">
-        <v>11001</v>
+        <v>10910</v>
       </c>
       <c r="B66" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66" s="5">
         <v>1</v>
       </c>
       <c r="D66" s="5">
-        <v>0</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G66" s="5">
         <v>-1</v>
@@ -4808,13 +4815,13 @@
         <v>0</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J66" s="5">
         <v>0</v>
       </c>
       <c r="K66" s="5">
-        <v>11002</v>
+        <v>10911</v>
       </c>
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
@@ -4826,9 +4833,9 @@
       <c r="S66" s="5"/>
       <c r="T66" s="5"/>
     </row>
-    <row r="67" spans="1:20">
+    <row r="67" ht="69" spans="1:20">
       <c r="A67" s="5">
-        <v>11002</v>
+        <v>10911</v>
       </c>
       <c r="B67" s="5">
         <v>0</v>
@@ -4852,13 +4859,13 @@
         <v>0</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="J67" s="5">
         <v>0</v>
       </c>
       <c r="K67" s="5">
-        <v>0</v>
+        <v>10912</v>
       </c>
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
@@ -4870,18 +4877,18 @@
       <c r="S67" s="5"/>
       <c r="T67" s="5"/>
     </row>
-    <row r="68" ht="90" spans="1:20">
+    <row r="68" ht="104" spans="1:20">
       <c r="A68" s="5">
-        <v>11101</v>
+        <v>10912</v>
       </c>
       <c r="B68" s="5">
         <v>0</v>
       </c>
       <c r="C68" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D68" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>42</v>
@@ -4896,15 +4903,17 @@
         <v>0</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="J68" s="5">
         <v>0</v>
       </c>
       <c r="K68" s="5">
-        <v>11102</v>
-      </c>
-      <c r="L68" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="L68" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="M68" s="4"/>
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
@@ -4914,24 +4923,24 @@
       <c r="S68" s="5"/>
       <c r="T68" s="5"/>
     </row>
-    <row r="69" ht="60" spans="1:20">
+    <row r="69" ht="104" spans="1:20">
       <c r="A69" s="5">
-        <v>11102</v>
+        <v>10950</v>
       </c>
       <c r="B69" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C69" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D69" s="5">
-        <v>1</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>59</v>
+        <v>0</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="G69" s="5">
         <v>-1</v>
@@ -4940,15 +4949,17 @@
         <v>0</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="J69" s="5">
         <v>0</v>
       </c>
       <c r="K69" s="5">
-        <v>11103</v>
-      </c>
-      <c r="L69" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
@@ -4958,41 +4969,41 @@
       <c r="S69" s="5"/>
       <c r="T69" s="5"/>
     </row>
-    <row r="70" ht="150" spans="1:20">
+    <row r="70" ht="104" spans="1:20">
       <c r="A70" s="5">
-        <v>11103</v>
+        <v>11001</v>
       </c>
       <c r="B70" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C70" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D70" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="G70" s="5">
         <v>-1</v>
       </c>
       <c r="H70" s="5">
-        <v>-5</v>
-      </c>
-      <c r="I70" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="J70" s="5">
         <v>0</v>
       </c>
       <c r="K70" s="5">
-        <v>0</v>
-      </c>
-      <c r="L70" s="4" t="s">
-        <v>127</v>
-      </c>
+        <v>11002</v>
+      </c>
+      <c r="L70" s="4"/>
       <c r="M70" s="4"/>
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
@@ -5002,24 +5013,24 @@
       <c r="S70" s="5"/>
       <c r="T70" s="5"/>
     </row>
-    <row r="71" ht="150" spans="1:20">
+    <row r="71" ht="35" spans="1:20">
       <c r="A71" s="5">
-        <v>11150</v>
+        <v>11002</v>
       </c>
       <c r="B71" s="5">
         <v>0</v>
       </c>
       <c r="C71" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D71" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G71" s="5">
         <v>-1</v>
@@ -5028,7 +5039,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="J71" s="5">
         <v>0</v>
@@ -5036,9 +5047,7 @@
       <c r="K71" s="5">
         <v>0</v>
       </c>
-      <c r="L71" s="4" t="s">
-        <v>128</v>
-      </c>
+      <c r="L71" s="4"/>
       <c r="M71" s="4"/>
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
@@ -5048,24 +5057,24 @@
       <c r="S71" s="5"/>
       <c r="T71" s="5"/>
     </row>
-    <row r="72" ht="90" spans="1:20">
+    <row r="72" ht="104" spans="1:20">
       <c r="A72" s="5">
-        <v>1901</v>
+        <v>11101</v>
       </c>
       <c r="B72" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C72" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72" s="5">
         <v>0</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G72" s="5">
         <v>-1</v>
@@ -5074,13 +5083,13 @@
         <v>0</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="J72" s="5">
         <v>0</v>
       </c>
       <c r="K72" s="5">
-        <v>1902</v>
+        <v>11102</v>
       </c>
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
@@ -5092,41 +5101,41 @@
       <c r="S72" s="5"/>
       <c r="T72" s="5"/>
     </row>
-    <row r="73" ht="120" spans="1:20">
+    <row r="73" ht="69" spans="1:20">
       <c r="A73" s="5">
-        <v>1902</v>
+        <v>11102</v>
       </c>
       <c r="B73" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C73" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D73" s="5">
         <v>1</v>
       </c>
-      <c r="E73" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>47</v>
+      <c r="E73" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G73" s="5">
         <v>-1</v>
       </c>
       <c r="H73" s="5">
-        <v>-5</v>
-      </c>
-      <c r="I73" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="J73" s="5">
         <v>0</v>
       </c>
       <c r="K73" s="5">
-        <v>0</v>
-      </c>
-      <c r="L73" s="4" t="s">
-        <v>130</v>
-      </c>
+        <v>11103</v>
+      </c>
+      <c r="L73" s="4"/>
       <c r="M73" s="4"/>
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
@@ -5136,41 +5145,41 @@
       <c r="S73" s="5"/>
       <c r="T73" s="5"/>
     </row>
-    <row r="74" ht="90" spans="1:20">
+    <row r="74" ht="172" spans="1:20">
       <c r="A74" s="5">
-        <v>11201</v>
+        <v>11103</v>
       </c>
       <c r="B74" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C74" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D74" s="5">
-        <v>0</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>59</v>
+        <v>1</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G74" s="5">
         <v>-1</v>
       </c>
       <c r="H74" s="5">
-        <v>0</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>131</v>
-      </c>
+        <v>-5</v>
+      </c>
+      <c r="I74" s="4"/>
       <c r="J74" s="5">
         <v>0</v>
       </c>
       <c r="K74" s="5">
-        <v>11202</v>
-      </c>
-      <c r="L74" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="L74" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
@@ -5180,41 +5189,43 @@
       <c r="S74" s="5"/>
       <c r="T74" s="5"/>
     </row>
-    <row r="75" ht="60" spans="1:20">
+    <row r="75" ht="172" spans="1:20">
       <c r="A75" s="5">
-        <v>11202</v>
+        <v>11150</v>
       </c>
       <c r="B75" s="5">
         <v>0</v>
       </c>
       <c r="C75" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D75" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G75" s="5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H75" s="5">
         <v>0</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J75" s="5">
         <v>0</v>
       </c>
       <c r="K75" s="5">
-        <v>11203</v>
-      </c>
-      <c r="L75" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="L75" s="4" t="s">
+        <v>136</v>
+      </c>
       <c r="M75" s="4"/>
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
@@ -5224,41 +5235,41 @@
       <c r="S75" s="5"/>
       <c r="T75" s="5"/>
     </row>
-    <row r="76" ht="180" spans="1:20">
+    <row r="76" ht="104" spans="1:20">
       <c r="A76" s="5">
-        <v>11203</v>
+        <v>1901</v>
       </c>
       <c r="B76" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C76" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D76" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G76" s="5">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="H76" s="5">
         <v>0</v>
       </c>
-      <c r="I76" s="4"/>
+      <c r="I76" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="J76" s="5">
         <v>0</v>
       </c>
       <c r="K76" s="5">
-        <v>11204</v>
-      </c>
-      <c r="L76" s="4" t="s">
-        <v>133</v>
-      </c>
+        <v>1902</v>
+      </c>
+      <c r="L76" s="4"/>
       <c r="M76" s="4"/>
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
@@ -5268,41 +5279,41 @@
       <c r="S76" s="5"/>
       <c r="T76" s="5"/>
     </row>
-    <row r="77" ht="90" spans="1:20">
+    <row r="77" ht="138" spans="1:20">
       <c r="A77" s="5">
-        <v>11204</v>
+        <v>1902</v>
       </c>
       <c r="B77" s="5">
         <v>0</v>
       </c>
       <c r="C77" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D77" s="5">
         <v>1</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G77" s="5">
         <v>-1</v>
       </c>
       <c r="H77" s="5">
-        <v>0</v>
-      </c>
-      <c r="I77" s="4" t="s">
-        <v>134</v>
-      </c>
+        <v>-5</v>
+      </c>
+      <c r="I77" s="4"/>
       <c r="J77" s="5">
         <v>0</v>
       </c>
       <c r="K77" s="5">
-        <v>11205</v>
-      </c>
-      <c r="L77" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="L77" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="M77" s="4"/>
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
@@ -5312,24 +5323,24 @@
       <c r="S77" s="5"/>
       <c r="T77" s="5"/>
     </row>
-    <row r="78" ht="90" spans="1:20">
+    <row r="78" ht="104" spans="1:20">
       <c r="A78" s="5">
-        <v>11205</v>
+        <v>11201</v>
       </c>
       <c r="B78" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C78" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D78" s="5">
-        <v>1</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>43</v>
+        <v>0</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G78" s="5">
         <v>-1</v>
@@ -5338,17 +5349,15 @@
         <v>0</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="J78" s="5">
         <v>0</v>
       </c>
       <c r="K78" s="5">
-        <v>0</v>
-      </c>
-      <c r="L78" s="4" t="s">
-        <v>135</v>
-      </c>
+        <v>11202</v>
+      </c>
+      <c r="L78" s="4"/>
       <c r="M78" s="4"/>
       <c r="N78" s="4"/>
       <c r="O78" s="4"/>
@@ -5358,9 +5367,9 @@
       <c r="S78" s="5"/>
       <c r="T78" s="5"/>
     </row>
-    <row r="79" ht="60" spans="1:20">
+    <row r="79" ht="69" spans="1:20">
       <c r="A79" s="5">
-        <v>11301</v>
+        <v>11202</v>
       </c>
       <c r="B79" s="5">
         <v>0</v>
@@ -5369,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79" s="5" t="s">
         <v>42</v>
@@ -5378,19 +5387,19 @@
         <v>43</v>
       </c>
       <c r="G79" s="5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H79" s="5">
         <v>0</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="J79" s="5">
         <v>0</v>
       </c>
       <c r="K79" s="5">
-        <v>11302</v>
+        <v>11203</v>
       </c>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
@@ -5402,41 +5411,41 @@
       <c r="S79" s="5"/>
       <c r="T79" s="5"/>
     </row>
-    <row r="80" ht="90" spans="1:20">
+    <row r="80" ht="207" spans="1:20">
       <c r="A80" s="5">
-        <v>11302</v>
+        <v>11203</v>
       </c>
       <c r="B80" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C80" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D80" s="5">
         <v>1</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G80" s="5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="H80" s="5">
         <v>0</v>
       </c>
-      <c r="I80" s="4" t="s">
-        <v>137</v>
-      </c>
+      <c r="I80" s="4"/>
       <c r="J80" s="5">
         <v>0</v>
       </c>
       <c r="K80" s="5">
-        <v>11303</v>
-      </c>
-      <c r="L80" s="4"/>
+        <v>11204</v>
+      </c>
+      <c r="L80" s="4" t="s">
+        <v>141</v>
+      </c>
       <c r="M80" s="4"/>
       <c r="N80" s="4"/>
       <c r="O80" s="4"/>
@@ -5446,9 +5455,9 @@
       <c r="S80" s="5"/>
       <c r="T80" s="5"/>
     </row>
-    <row r="81" spans="1:20">
+    <row r="81" ht="104" spans="1:20">
       <c r="A81" s="5">
-        <v>11303</v>
+        <v>11204</v>
       </c>
       <c r="B81" s="5">
         <v>0</v>
@@ -5472,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J81" s="5">
         <v>0</v>
       </c>
       <c r="K81" s="5">
-        <v>11304</v>
+        <v>11205</v>
       </c>
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
@@ -5490,15 +5499,15 @@
       <c r="S81" s="5"/>
       <c r="T81" s="5"/>
     </row>
-    <row r="82" ht="120" spans="1:20">
+    <row r="82" ht="104" spans="1:20">
       <c r="A82" s="5">
-        <v>11304</v>
+        <v>11205</v>
       </c>
       <c r="B82" s="5">
         <v>0</v>
       </c>
       <c r="C82" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D82" s="5">
         <v>1</v>
@@ -5513,17 +5522,19 @@
         <v>-1</v>
       </c>
       <c r="H82" s="5">
-        <v>-5</v>
-      </c>
-      <c r="I82" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="J82" s="5">
         <v>0</v>
       </c>
       <c r="K82" s="5">
-        <v>11305</v>
+        <v>0</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M82" s="4"/>
       <c r="N82" s="4"/>
@@ -5534,24 +5545,24 @@
       <c r="S82" s="5"/>
       <c r="T82" s="5"/>
     </row>
-    <row r="83" ht="180" spans="1:20">
+    <row r="83" ht="69" spans="1:20">
       <c r="A83" s="5">
-        <v>11305</v>
+        <v>11301</v>
       </c>
       <c r="B83" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C83" s="5">
         <v>0</v>
       </c>
       <c r="D83" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G83" s="5">
         <v>-1</v>
@@ -5560,13 +5571,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="J83" s="5">
         <v>0</v>
       </c>
       <c r="K83" s="5">
-        <v>11306</v>
+        <v>11302</v>
       </c>
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
@@ -5578,15 +5589,15 @@
       <c r="S83" s="5"/>
       <c r="T83" s="5"/>
     </row>
-    <row r="84" ht="120" spans="1:20">
+    <row r="84" ht="104" spans="1:20">
       <c r="A84" s="5">
-        <v>11306</v>
+        <v>11302</v>
       </c>
       <c r="B84" s="5">
         <v>12</v>
       </c>
       <c r="C84" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84" s="5">
         <v>1</v>
@@ -5604,13 +5615,13 @@
         <v>0</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J84" s="5">
         <v>0</v>
       </c>
       <c r="K84" s="5">
-        <v>11307</v>
+        <v>11303</v>
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
@@ -5622,24 +5633,24 @@
       <c r="S84" s="5"/>
       <c r="T84" s="5"/>
     </row>
-    <row r="85" ht="120" spans="1:20">
+    <row r="85" ht="69" spans="1:20">
       <c r="A85" s="5">
-        <v>11307</v>
+        <v>11303</v>
       </c>
       <c r="B85" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C85" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85" s="5">
         <v>1</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G85" s="5">
         <v>-1</v>
@@ -5648,13 +5659,13 @@
         <v>0</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="J85" s="5">
         <v>0</v>
       </c>
       <c r="K85" s="5">
-        <v>11308</v>
+        <v>11304</v>
       </c>
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
@@ -5666,15 +5677,15 @@
       <c r="S85" s="5"/>
       <c r="T85" s="5"/>
     </row>
-    <row r="86" ht="150" spans="1:20">
+    <row r="86" ht="138" spans="1:20">
       <c r="A86" s="5">
-        <v>11308</v>
+        <v>11304</v>
       </c>
       <c r="B86" s="5">
         <v>0</v>
       </c>
       <c r="C86" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D86" s="5">
         <v>1</v>
@@ -5689,19 +5700,17 @@
         <v>-1</v>
       </c>
       <c r="H86" s="5">
-        <v>0</v>
-      </c>
-      <c r="I86" s="4" t="s">
-        <v>143</v>
-      </c>
+        <v>-5</v>
+      </c>
+      <c r="I86" s="4"/>
       <c r="J86" s="5">
         <v>0</v>
       </c>
       <c r="K86" s="5">
-        <v>0</v>
+        <v>11305</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="M86" s="4"/>
       <c r="N86" s="4"/>
@@ -5712,21 +5721,21 @@
       <c r="S86" s="5"/>
       <c r="T86" s="5"/>
     </row>
-    <row r="87" ht="60" spans="1:20">
+    <row r="87" ht="207" spans="1:20">
       <c r="A87" s="5">
-        <v>2001</v>
+        <v>11305</v>
       </c>
       <c r="B87" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C87" s="5">
         <v>0</v>
       </c>
       <c r="D87" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>47</v>
@@ -5738,13 +5747,13 @@
         <v>0</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J87" s="5">
         <v>0</v>
       </c>
       <c r="K87" s="5">
-        <v>0</v>
+        <v>11306</v>
       </c>
       <c r="L87" s="4"/>
       <c r="M87" s="4"/>
@@ -5756,21 +5765,21 @@
       <c r="S87" s="5"/>
       <c r="T87" s="5"/>
     </row>
-    <row r="88" ht="60" spans="1:20">
+    <row r="88" ht="138" spans="1:20">
       <c r="A88" s="5">
-        <v>2101</v>
+        <v>11306</v>
       </c>
       <c r="B88" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C88" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>47</v>
@@ -5782,13 +5791,13 @@
         <v>0</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J88" s="5">
         <v>0</v>
       </c>
       <c r="K88" s="5">
-        <v>0</v>
+        <v>11307</v>
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
@@ -5800,21 +5809,21 @@
       <c r="S88" s="5"/>
       <c r="T88" s="5"/>
     </row>
-    <row r="89" spans="1:20">
+    <row r="89" ht="138" spans="1:20">
       <c r="A89" s="5">
-        <v>2201</v>
+        <v>11307</v>
       </c>
       <c r="B89" s="5">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C89" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>147</v>
+        <v>83</v>
       </c>
       <c r="F89" s="7" t="s">
         <v>47</v>
@@ -5826,13 +5835,13 @@
         <v>0</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J89" s="5">
         <v>0</v>
       </c>
       <c r="K89" s="5">
-        <v>0</v>
+        <v>11308</v>
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
@@ -5844,24 +5853,24 @@
       <c r="S89" s="5"/>
       <c r="T89" s="5"/>
     </row>
-    <row r="90" ht="90" spans="1:20">
+    <row r="90" ht="172" spans="1:20">
       <c r="A90" s="5">
-        <v>2301</v>
+        <v>11308</v>
       </c>
       <c r="B90" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C90" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D90" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G90" s="5">
         <v>-1</v>
@@ -5870,7 +5879,7 @@
         <v>0</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="J90" s="5">
         <v>0</v>
@@ -5878,7 +5887,9 @@
       <c r="K90" s="5">
         <v>0</v>
       </c>
-      <c r="L90" s="4"/>
+      <c r="L90" s="4" t="s">
+        <v>151</v>
+      </c>
       <c r="M90" s="4"/>
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
@@ -5888,12 +5899,12 @@
       <c r="S90" s="5"/>
       <c r="T90" s="5"/>
     </row>
-    <row r="91" ht="60" spans="1:20">
+    <row r="91" ht="69" spans="1:20">
       <c r="A91" s="5">
-        <v>11401</v>
+        <v>2001</v>
       </c>
       <c r="B91" s="5">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C91" s="5">
         <v>0</v>
@@ -5902,10 +5913,10 @@
         <v>0</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>100</v>
+        <v>85</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="G91" s="5">
         <v>-1</v>
@@ -5914,13 +5925,13 @@
         <v>0</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J91" s="5">
         <v>0</v>
       </c>
       <c r="K91" s="5">
-        <v>11402</v>
+        <v>0</v>
       </c>
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
@@ -5932,24 +5943,24 @@
       <c r="S91" s="5"/>
       <c r="T91" s="5"/>
     </row>
-    <row r="92" ht="90" spans="1:20">
+    <row r="92" ht="69" spans="1:20">
       <c r="A92" s="5">
-        <v>11402</v>
+        <v>2101</v>
       </c>
       <c r="B92" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C92" s="5">
         <v>0</v>
       </c>
       <c r="D92" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>43</v>
+        <v>153</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="G92" s="5">
         <v>-1</v>
@@ -5958,13 +5969,13 @@
         <v>0</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J92" s="5">
         <v>0</v>
       </c>
       <c r="K92" s="5">
-        <v>11403</v>
+        <v>0</v>
       </c>
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
@@ -5976,24 +5987,24 @@
       <c r="S92" s="5"/>
       <c r="T92" s="5"/>
     </row>
-    <row r="93" ht="60" spans="1:20">
+    <row r="93" ht="35" spans="1:20">
       <c r="A93" s="5">
-        <v>11403</v>
+        <v>2201</v>
       </c>
       <c r="B93" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C93" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D93" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>43</v>
+        <v>155</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="G93" s="5">
         <v>-1</v>
@@ -6002,7 +6013,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="J93" s="5">
         <v>0</v>
@@ -6010,9 +6021,7 @@
       <c r="K93" s="5">
         <v>0</v>
       </c>
-      <c r="L93" s="4" t="s">
-        <v>151</v>
-      </c>
+      <c r="L93" s="4"/>
       <c r="M93" s="4"/>
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
@@ -6022,23 +6031,23 @@
       <c r="S93" s="5"/>
       <c r="T93" s="5"/>
     </row>
-    <row r="94" ht="90" spans="1:20">
+    <row r="94" ht="104" spans="1:20">
       <c r="A94" s="5">
-        <v>11501</v>
+        <v>2301</v>
       </c>
       <c r="B94" s="5">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C94" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94" s="5">
         <v>0</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="F94" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F94" s="5" t="s">
         <v>47</v>
       </c>
       <c r="G94" s="5">
@@ -6048,13 +6057,13 @@
         <v>0</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>153</v>
+        <v>89</v>
       </c>
       <c r="J94" s="5">
         <v>0</v>
       </c>
       <c r="K94" s="5">
-        <v>11502</v>
+        <v>0</v>
       </c>
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
@@ -6066,24 +6075,24 @@
       <c r="S94" s="5"/>
       <c r="T94" s="5"/>
     </row>
-    <row r="95" ht="120" spans="1:20">
+    <row r="95" ht="69" spans="1:20">
       <c r="A95" s="5">
-        <v>11502</v>
+        <v>11401</v>
       </c>
       <c r="B95" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D95" s="5">
-        <v>1</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F95" s="8" t="s">
-        <v>59</v>
+        <v>0</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="G95" s="5">
         <v>-1</v>
@@ -6092,13 +6101,13 @@
         <v>0</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J95" s="5">
         <v>0</v>
       </c>
       <c r="K95" s="5">
-        <v>11503</v>
+        <v>11402</v>
       </c>
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
@@ -6110,24 +6119,24 @@
       <c r="S95" s="5"/>
       <c r="T95" s="5"/>
     </row>
-    <row r="96" ht="120" spans="1:20">
+    <row r="96" ht="104" spans="1:20">
       <c r="A96" s="5">
-        <v>11503</v>
+        <v>11402</v>
       </c>
       <c r="B96" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C96" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96" s="5">
         <v>1</v>
       </c>
-      <c r="E96" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>59</v>
+      <c r="E96" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G96" s="5">
         <v>-1</v>
@@ -6136,13 +6145,13 @@
         <v>0</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="J96" s="5">
         <v>0</v>
       </c>
       <c r="K96" s="5">
-        <v>11504</v>
+        <v>11403</v>
       </c>
       <c r="L96" s="4"/>
       <c r="M96" s="4"/>
@@ -6154,24 +6163,24 @@
       <c r="S96" s="5"/>
       <c r="T96" s="5"/>
     </row>
-    <row r="97" spans="1:20">
+    <row r="97" ht="69" spans="1:20">
       <c r="A97" s="5">
-        <v>11504</v>
+        <v>11403</v>
       </c>
       <c r="B97" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C97" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D97" s="5">
         <v>1</v>
       </c>
-      <c r="E97" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F97" s="8" t="s">
-        <v>59</v>
+      <c r="E97" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G97" s="5">
         <v>-1</v>
@@ -6180,15 +6189,17 @@
         <v>0</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>67</v>
+        <v>159</v>
       </c>
       <c r="J97" s="5">
         <v>0</v>
       </c>
       <c r="K97" s="5">
-        <v>11505</v>
-      </c>
-      <c r="L97" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="L97" s="4" t="s">
+        <v>159</v>
+      </c>
       <c r="M97" s="4"/>
       <c r="N97" s="4"/>
       <c r="O97" s="4"/>
@@ -6198,24 +6209,24 @@
       <c r="S97" s="5"/>
       <c r="T97" s="5"/>
     </row>
-    <row r="98" ht="60" spans="1:20">
+    <row r="98" ht="104" spans="1:20">
       <c r="A98" s="5">
-        <v>11505</v>
+        <v>11501</v>
       </c>
       <c r="B98" s="5">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C98" s="5">
         <v>1</v>
       </c>
       <c r="D98" s="5">
-        <v>1</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F98" s="8" t="s">
-        <v>59</v>
+        <v>0</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="G98" s="5">
         <v>-1</v>
@@ -6224,13 +6235,13 @@
         <v>0</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J98" s="5">
         <v>0</v>
       </c>
       <c r="K98" s="5">
-        <v>11506</v>
+        <v>11502</v>
       </c>
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
@@ -6242,9 +6253,9 @@
       <c r="S98" s="5"/>
       <c r="T98" s="5"/>
     </row>
-    <row r="99" spans="1:20">
+    <row r="99" ht="138" spans="1:20">
       <c r="A99" s="5">
-        <v>11506</v>
+        <v>11502</v>
       </c>
       <c r="B99" s="5">
         <v>2</v>
@@ -6268,13 +6279,13 @@
         <v>0</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="J99" s="5">
         <v>0</v>
       </c>
       <c r="K99" s="5">
-        <v>11507</v>
+        <v>11503</v>
       </c>
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
@@ -6286,9 +6297,9 @@
       <c r="S99" s="5"/>
       <c r="T99" s="5"/>
     </row>
-    <row r="100" ht="60" spans="1:20">
+    <row r="100" ht="138" spans="1:20">
       <c r="A100" s="5">
-        <v>11507</v>
+        <v>11503</v>
       </c>
       <c r="B100" s="5">
         <v>2</v>
@@ -6312,13 +6323,13 @@
         <v>0</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J100" s="5">
         <v>0</v>
       </c>
       <c r="K100" s="5">
-        <v>0</v>
+        <v>11504</v>
       </c>
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
@@ -6330,9 +6341,9 @@
       <c r="S100" s="5"/>
       <c r="T100" s="5"/>
     </row>
-    <row r="101" ht="150" spans="1:20">
+    <row r="101" ht="35" spans="1:20">
       <c r="A101" s="5">
-        <v>11601</v>
+        <v>11504</v>
       </c>
       <c r="B101" s="5">
         <v>2</v>
@@ -6341,7 +6352,7 @@
         <v>1</v>
       </c>
       <c r="D101" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" s="8" t="s">
         <v>58</v>
@@ -6356,13 +6367,13 @@
         <v>0</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>159</v>
+        <v>67</v>
       </c>
       <c r="J101" s="5">
         <v>0</v>
       </c>
       <c r="K101" s="5">
-        <v>11602</v>
+        <v>11505</v>
       </c>
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
@@ -6374,9 +6385,9 @@
       <c r="S101" s="5"/>
       <c r="T101" s="5"/>
     </row>
-    <row r="102" ht="90" spans="1:20">
+    <row r="102" ht="69" spans="1:20">
       <c r="A102" s="5">
-        <v>11602</v>
+        <v>11505</v>
       </c>
       <c r="B102" s="5">
         <v>2</v>
@@ -6400,13 +6411,13 @@
         <v>0</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J102" s="5">
         <v>0</v>
       </c>
       <c r="K102" s="5">
-        <v>11603</v>
+        <v>11506</v>
       </c>
       <c r="L102" s="4"/>
       <c r="M102" s="4"/>
@@ -6418,9 +6429,9 @@
       <c r="S102" s="5"/>
       <c r="T102" s="5"/>
     </row>
-    <row r="103" spans="1:20">
+    <row r="103" ht="35" spans="1:20">
       <c r="A103" s="5">
-        <v>11603</v>
+        <v>11506</v>
       </c>
       <c r="B103" s="5">
         <v>2</v>
@@ -6444,13 +6455,13 @@
         <v>0</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>67</v>
+        <v>165</v>
       </c>
       <c r="J103" s="5">
         <v>0</v>
       </c>
       <c r="K103" s="5">
-        <v>11604</v>
+        <v>11507</v>
       </c>
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
@@ -6462,9 +6473,9 @@
       <c r="S103" s="5"/>
       <c r="T103" s="5"/>
     </row>
-    <row r="104" ht="90" spans="1:20">
+    <row r="104" ht="69" spans="1:20">
       <c r="A104" s="5">
-        <v>11604</v>
+        <v>11507</v>
       </c>
       <c r="B104" s="5">
         <v>2</v>
@@ -6488,13 +6499,13 @@
         <v>0</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="J104" s="5">
         <v>0</v>
       </c>
       <c r="K104" s="5">
-        <v>11605</v>
+        <v>0</v>
       </c>
       <c r="L104" s="4"/>
       <c r="M104" s="4"/>
@@ -6506,9 +6517,9 @@
       <c r="S104" s="5"/>
       <c r="T104" s="5"/>
     </row>
-    <row r="105" spans="1:20">
+    <row r="105" ht="172" spans="1:20">
       <c r="A105" s="5">
-        <v>11605</v>
+        <v>11601</v>
       </c>
       <c r="B105" s="5">
         <v>2</v>
@@ -6517,7 +6528,7 @@
         <v>1</v>
       </c>
       <c r="D105" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" s="8" t="s">
         <v>58</v>
@@ -6532,13 +6543,13 @@
         <v>0</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>67</v>
+        <v>167</v>
       </c>
       <c r="J105" s="5">
         <v>0</v>
       </c>
       <c r="K105" s="5">
-        <v>11606</v>
+        <v>11602</v>
       </c>
       <c r="L105" s="4"/>
       <c r="M105" s="4"/>
@@ -6550,9 +6561,9 @@
       <c r="S105" s="5"/>
       <c r="T105" s="5"/>
     </row>
-    <row r="106" ht="90" spans="1:20">
+    <row r="106" ht="104" spans="1:20">
       <c r="A106" s="5">
-        <v>11606</v>
+        <v>11602</v>
       </c>
       <c r="B106" s="5">
         <v>2</v>
@@ -6576,13 +6587,13 @@
         <v>0</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="J106" s="5">
         <v>0</v>
       </c>
       <c r="K106" s="5">
-        <v>0</v>
+        <v>11603</v>
       </c>
       <c r="L106" s="4"/>
       <c r="M106" s="4"/>
@@ -6594,24 +6605,24 @@
       <c r="S106" s="5"/>
       <c r="T106" s="5"/>
     </row>
-    <row r="107" ht="90" spans="1:20">
+    <row r="107" ht="35" spans="1:20">
       <c r="A107" s="5">
-        <v>2401</v>
+        <v>11603</v>
       </c>
       <c r="B107" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C107" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107" s="5">
-        <v>0</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G107" s="5">
         <v>-1</v>
@@ -6620,13 +6631,13 @@
         <v>0</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="J107" s="5">
         <v>0</v>
       </c>
       <c r="K107" s="5">
-        <v>0</v>
+        <v>11604</v>
       </c>
       <c r="L107" s="4"/>
       <c r="M107" s="4"/>
@@ -6638,39 +6649,39 @@
       <c r="S107" s="5"/>
       <c r="T107" s="5"/>
     </row>
-    <row r="108" ht="90" spans="1:20">
+    <row r="108" ht="104" spans="1:20">
       <c r="A108" s="5">
-        <v>11701</v>
+        <v>11604</v>
       </c>
       <c r="B108" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C108" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D108" s="5">
-        <v>0</v>
-      </c>
-      <c r="E108" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="E108" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G108" s="5">
         <v>-1</v>
       </c>
       <c r="H108" s="5">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J108" s="5">
         <v>0</v>
       </c>
       <c r="K108" s="5">
-        <v>11702</v>
+        <v>11605</v>
       </c>
       <c r="L108" s="4"/>
       <c r="M108" s="4"/>
@@ -6682,24 +6693,24 @@
       <c r="S108" s="5"/>
       <c r="T108" s="5"/>
     </row>
-    <row r="109" spans="1:20">
+    <row r="109" ht="35" spans="1:20">
       <c r="A109" s="5">
-        <v>11702</v>
+        <v>11605</v>
       </c>
       <c r="B109" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C109" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D109" s="5">
         <v>1</v>
       </c>
-      <c r="E109" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F109" s="5" t="s">
-        <v>43</v>
+      <c r="E109" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G109" s="5">
         <v>-1</v>
@@ -6708,13 +6719,13 @@
         <v>0</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>165</v>
+        <v>67</v>
       </c>
       <c r="J109" s="5">
         <v>0</v>
       </c>
       <c r="K109" s="5">
-        <v>11703</v>
+        <v>11606</v>
       </c>
       <c r="L109" s="4"/>
       <c r="M109" s="4"/>
@@ -6726,24 +6737,24 @@
       <c r="S109" s="5"/>
       <c r="T109" s="5"/>
     </row>
-    <row r="110" ht="60" spans="1:20">
+    <row r="110" ht="104" spans="1:20">
       <c r="A110" s="5">
-        <v>11703</v>
+        <v>11606</v>
       </c>
       <c r="B110" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C110" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D110" s="5">
         <v>1</v>
       </c>
-      <c r="E110" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F110" s="5" t="s">
-        <v>43</v>
+      <c r="E110" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G110" s="5">
         <v>-1</v>
@@ -6752,7 +6763,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J110" s="5">
         <v>0</v>
@@ -6770,9 +6781,9 @@
       <c r="S110" s="5"/>
       <c r="T110" s="5"/>
     </row>
-    <row r="111" ht="60" spans="1:20">
+    <row r="111" ht="104" spans="1:20">
       <c r="A111" s="5">
-        <v>2501</v>
+        <v>2401</v>
       </c>
       <c r="B111" s="5">
         <v>0</v>
@@ -6796,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J111" s="5">
         <v>0</v>
@@ -6814,39 +6825,39 @@
       <c r="S111" s="5"/>
       <c r="T111" s="5"/>
     </row>
-    <row r="112" ht="60" spans="1:20">
+    <row r="112" ht="104" spans="1:20">
       <c r="A112" s="5">
-        <v>2601</v>
+        <v>11701</v>
       </c>
       <c r="B112" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C112" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D112" s="5">
         <v>0</v>
       </c>
-      <c r="E112" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F112" s="8" t="s">
-        <v>59</v>
+      <c r="E112" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G112" s="5">
         <v>-1</v>
       </c>
       <c r="H112" s="5">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="J112" s="5">
         <v>0</v>
       </c>
       <c r="K112" s="5">
-        <v>2602</v>
+        <v>11702</v>
       </c>
       <c r="L112" s="4"/>
       <c r="M112" s="4"/>
@@ -6858,12 +6869,12 @@
       <c r="S112" s="5"/>
       <c r="T112" s="5"/>
     </row>
-    <row r="113" ht="90" spans="1:20">
+    <row r="113" ht="35" spans="1:20">
       <c r="A113" s="5">
-        <v>2602</v>
+        <v>11702</v>
       </c>
       <c r="B113" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C113" s="5">
         <v>0</v>
@@ -6871,11 +6882,11 @@
       <c r="D113" s="5">
         <v>1</v>
       </c>
-      <c r="E113" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F113" s="8" t="s">
-        <v>59</v>
+      <c r="E113" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G113" s="5">
         <v>-1</v>
@@ -6884,13 +6895,13 @@
         <v>0</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J113" s="5">
         <v>0</v>
       </c>
       <c r="K113" s="5">
-        <v>0</v>
+        <v>11703</v>
       </c>
       <c r="L113" s="4"/>
       <c r="M113" s="4"/>
@@ -6902,18 +6913,18 @@
       <c r="S113" s="5"/>
       <c r="T113" s="5"/>
     </row>
-    <row r="114" ht="63" spans="1:20">
+    <row r="114" ht="69" spans="1:20">
       <c r="A114" s="5">
-        <v>11801</v>
+        <v>11703</v>
       </c>
       <c r="B114" s="5">
         <v>0</v>
       </c>
       <c r="C114" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D114" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114" s="5" t="s">
         <v>42</v>
@@ -6925,16 +6936,16 @@
         <v>-1</v>
       </c>
       <c r="H114" s="5">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I114" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J114" s="5">
         <v>0</v>
       </c>
       <c r="K114" s="5">
-        <v>11802</v>
+        <v>0</v>
       </c>
       <c r="L114" s="4"/>
       <c r="M114" s="4"/>
@@ -6946,18 +6957,18 @@
       <c r="S114" s="5"/>
       <c r="T114" s="5"/>
     </row>
-    <row r="115" ht="120" spans="1:20">
+    <row r="115" ht="69" spans="1:20">
       <c r="A115" s="5">
-        <v>11802</v>
+        <v>2501</v>
       </c>
       <c r="B115" s="5">
         <v>0</v>
       </c>
       <c r="C115" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D115" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E115" s="5" t="s">
         <v>42</v>
@@ -6969,16 +6980,16 @@
         <v>-1</v>
       </c>
       <c r="H115" s="5">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I115" s="4" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="J115" s="5">
         <v>0</v>
       </c>
       <c r="K115" s="5">
-        <v>11803</v>
+        <v>0</v>
       </c>
       <c r="L115" s="4"/>
       <c r="M115" s="4"/>
@@ -6990,39 +7001,39 @@
       <c r="S115" s="5"/>
       <c r="T115" s="5"/>
     </row>
-    <row r="116" ht="60" spans="1:20">
+    <row r="116" ht="69" spans="1:20">
       <c r="A116" s="5">
-        <v>11803</v>
+        <v>2601</v>
       </c>
       <c r="B116" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C116" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D116" s="5">
-        <v>1</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F116" s="5" t="s">
-        <v>43</v>
+        <v>0</v>
+      </c>
+      <c r="E116" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G116" s="5">
         <v>-1</v>
       </c>
       <c r="H116" s="5">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I116" s="4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="J116" s="5">
         <v>0</v>
       </c>
       <c r="K116" s="5">
-        <v>0</v>
+        <v>2602</v>
       </c>
       <c r="L116" s="4"/>
       <c r="M116" s="4"/>
@@ -7034,10 +7045,186 @@
       <c r="S116" s="5"/>
       <c r="T116" s="5"/>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="5"/>
-      <c r="B117" s="5"/>
-      <c r="C117" s="5"/>
+    <row r="117" ht="104" spans="1:20">
+      <c r="A117" s="5">
+        <v>2602</v>
+      </c>
+      <c r="B117" s="5">
+        <v>2</v>
+      </c>
+      <c r="C117" s="5">
+        <v>0</v>
+      </c>
+      <c r="D117" s="5">
+        <v>1</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G117" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H117" s="5">
+        <v>0</v>
+      </c>
+      <c r="I117" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="J117" s="5">
+        <v>0</v>
+      </c>
+      <c r="K117" s="5">
+        <v>0</v>
+      </c>
+      <c r="L117" s="4"/>
+      <c r="M117" s="4"/>
+      <c r="N117" s="4"/>
+      <c r="O117" s="4"/>
+      <c r="P117" s="4"/>
+      <c r="Q117" s="5"/>
+      <c r="R117" s="5"/>
+      <c r="S117" s="5"/>
+      <c r="T117" s="5"/>
+    </row>
+    <row r="118" ht="69" spans="1:20">
+      <c r="A118" s="5">
+        <v>11801</v>
+      </c>
+      <c r="B118" s="5">
+        <v>0</v>
+      </c>
+      <c r="C118" s="5">
+        <v>4</v>
+      </c>
+      <c r="D118" s="5">
+        <v>0</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G118" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H118" s="5">
+        <v>-10</v>
+      </c>
+      <c r="I118" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="J118" s="5">
+        <v>0</v>
+      </c>
+      <c r="K118" s="5">
+        <v>11802</v>
+      </c>
+      <c r="L118" s="4"/>
+      <c r="M118" s="4"/>
+      <c r="N118" s="4"/>
+      <c r="O118" s="4"/>
+      <c r="P118" s="4"/>
+      <c r="Q118" s="5"/>
+      <c r="R118" s="5"/>
+      <c r="S118" s="5"/>
+      <c r="T118" s="5"/>
+    </row>
+    <row r="119" ht="138" spans="1:20">
+      <c r="A119" s="5">
+        <v>11802</v>
+      </c>
+      <c r="B119" s="5">
+        <v>0</v>
+      </c>
+      <c r="C119" s="5">
+        <v>4</v>
+      </c>
+      <c r="D119" s="5">
+        <v>1</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G119" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H119" s="5">
+        <v>-10</v>
+      </c>
+      <c r="I119" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="J119" s="5">
+        <v>0</v>
+      </c>
+      <c r="K119" s="5">
+        <v>11803</v>
+      </c>
+      <c r="L119" s="4"/>
+      <c r="M119" s="4"/>
+      <c r="N119" s="4"/>
+      <c r="O119" s="4"/>
+      <c r="P119" s="4"/>
+      <c r="Q119" s="5"/>
+      <c r="R119" s="5"/>
+      <c r="S119" s="5"/>
+      <c r="T119" s="5"/>
+    </row>
+    <row r="120" ht="69" spans="1:20">
+      <c r="A120" s="5">
+        <v>11803</v>
+      </c>
+      <c r="B120" s="5">
+        <v>0</v>
+      </c>
+      <c r="C120" s="5">
+        <v>4</v>
+      </c>
+      <c r="D120" s="5">
+        <v>1</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G120" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H120" s="5">
+        <v>-10</v>
+      </c>
+      <c r="I120" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="J120" s="5">
+        <v>0</v>
+      </c>
+      <c r="K120" s="5">
+        <v>0</v>
+      </c>
+      <c r="L120" s="4"/>
+      <c r="M120" s="4"/>
+      <c r="N120" s="4"/>
+      <c r="O120" s="4"/>
+      <c r="P120" s="4"/>
+      <c r="Q120" s="5"/>
+      <c r="R120" s="5"/>
+      <c r="S120" s="5"/>
+      <c r="T120" s="5"/>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="5"/>
+      <c r="B121" s="5"/>
+      <c r="C121" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Excel/DialogDatas.xlsx
+++ b/Excel/DialogDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="14900"/>
+    <workbookView windowWidth="21000" windowHeight="12780"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="186">
   <si>
     <t>int</t>
   </si>
@@ -559,16 +559,31 @@
     <t>我家门口也有那种怪兽！去Mike家吧！</t>
   </si>
   <si>
-    <t>又是昨天一样的梦......得快点救下那个人！</t>
-  </si>
-  <si>
-    <t>刚刚真是吓死我了， 我手上怎么有伤痕？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这果然不是梦吗 </t>
+    <t>又是昨天一样的梦......</t>
+  </si>
+  <si>
+    <t>今天好像适应了这副身体，感觉可以大杀四方</t>
+  </si>
+  <si>
+    <t>等醒了可以和鲍勃炫耀一下今天的战果</t>
+  </si>
+  <si>
+    <t>今天必须击败场景中所有敌人才能够通关</t>
+  </si>
+  <si>
+    <t>迈克！！！不要！！！</t>
+  </si>
+  <si>
+    <t>刚刚那是什么声音， 我怎么好像听到了鲍勃的声音？</t>
+  </si>
+  <si>
+    <t>不对，我的头好痛，到底是怎么回事</t>
   </si>
   <si>
     <t>怪兽到底是哪里来的</t>
+  </si>
+  <si>
+    <t>迈克昏迷了过去</t>
   </si>
   <si>
     <t>这么晚了，还有谁会来呢</t>
@@ -808,13 +823,13 @@
     </font>
     <font>
       <sz val="24"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF333333"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="24"/>
-      <color rgb="FF333333"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1294,14 +1309,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1829,29 +1844,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T121"/>
-  <sheetFormatPr defaultColWidth="9.22115384615385" defaultRowHeight="34.4"/>
+  <dimension ref="A1:T126"/>
+  <sheetFormatPr defaultColWidth="9.22222222222222" defaultRowHeight="30.6"/>
   <cols>
     <col min="1" max="1" width="21" style="2" customWidth="1"/>
-    <col min="2" max="2" width="33.6634615384615" style="2" customWidth="1"/>
-    <col min="3" max="3" width="37.6634615384615" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25.4423076923077" style="2" customWidth="1"/>
-    <col min="5" max="5" width="26.1153846153846" style="2" customWidth="1"/>
-    <col min="6" max="6" width="50.8846153846154" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23.6634615384615" style="2" customWidth="1"/>
-    <col min="8" max="8" width="26.1153846153846" style="2" customWidth="1"/>
-    <col min="9" max="9" width="40.8365384615385" style="2" customWidth="1"/>
-    <col min="10" max="10" width="30.1153846153846" style="2" customWidth="1"/>
-    <col min="11" max="11" width="25.6634615384615" style="2" customWidth="1"/>
-    <col min="12" max="16" width="25.6634615384615" style="3" customWidth="1"/>
-    <col min="17" max="17" width="40.0673076923077" style="2" customWidth="1"/>
-    <col min="18" max="18" width="48.4807692307692" style="2" customWidth="1"/>
-    <col min="19" max="19" width="43.2692307692308" style="2" customWidth="1"/>
-    <col min="20" max="20" width="38.8557692307692" style="2" customWidth="1"/>
-    <col min="21" max="16384" width="9.22115384615385" style="2"/>
+    <col min="2" max="2" width="33.6666666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="37.6666666666667" style="2" customWidth="1"/>
+    <col min="4" max="4" width="25.4444444444444" style="2" customWidth="1"/>
+    <col min="5" max="5" width="26.1111111111111" style="2" customWidth="1"/>
+    <col min="6" max="6" width="50.8888888888889" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.6666666666667" style="2" customWidth="1"/>
+    <col min="8" max="8" width="26.1111111111111" style="2" customWidth="1"/>
+    <col min="9" max="9" width="40.8333333333333" style="2" customWidth="1"/>
+    <col min="10" max="10" width="30.1111111111111" style="2" customWidth="1"/>
+    <col min="11" max="11" width="25.6666666666667" style="2" customWidth="1"/>
+    <col min="12" max="16" width="25.6666666666667" style="3" customWidth="1"/>
+    <col min="17" max="17" width="40.0648148148148" style="2" customWidth="1"/>
+    <col min="18" max="18" width="48.4814814814815" style="2" customWidth="1"/>
+    <col min="19" max="19" width="43.2685185185185" style="2" customWidth="1"/>
+    <col min="20" max="20" width="38.8518518518519" style="2" customWidth="1"/>
+    <col min="21" max="16384" width="9.22222222222222" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" spans="1:20">
+    <row r="1" spans="1:20">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1975,7 +1990,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" ht="35" spans="1:20">
+    <row r="3" spans="1:20">
       <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
@@ -2037,7 +2052,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" ht="104" spans="1:20">
+    <row r="4" ht="90" spans="1:20">
       <c r="A4" s="5">
         <v>10001</v>
       </c>
@@ -2081,7 +2096,7 @@
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
     </row>
-    <row r="5" ht="104" spans="1:20">
+    <row r="5" ht="90" spans="1:20">
       <c r="A5" s="5">
         <v>10002</v>
       </c>
@@ -2125,7 +2140,7 @@
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
     </row>
-    <row r="6" ht="138" spans="1:20">
+    <row r="6" ht="120" spans="1:20">
       <c r="A6" s="5">
         <v>1001</v>
       </c>
@@ -2169,7 +2184,7 @@
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
     </row>
-    <row r="7" ht="104" spans="1:20">
+    <row r="7" ht="90" spans="1:20">
       <c r="A7" s="5">
         <v>1101</v>
       </c>
@@ -2213,7 +2228,7 @@
       <c r="S7" s="5"/>
       <c r="T7" s="5"/>
     </row>
-    <row r="8" ht="104" spans="1:20">
+    <row r="8" ht="90" spans="1:20">
       <c r="A8" s="5">
         <v>1201</v>
       </c>
@@ -2257,7 +2272,7 @@
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
     </row>
-    <row r="9" ht="138" spans="1:20">
+    <row r="9" ht="120" spans="1:20">
       <c r="A9" s="5">
         <v>1202</v>
       </c>
@@ -2301,7 +2316,7 @@
       <c r="S9" s="5"/>
       <c r="T9" s="5"/>
     </row>
-    <row r="10" ht="104" spans="1:20">
+    <row r="10" ht="90" spans="1:20">
       <c r="A10" s="5">
         <v>1203</v>
       </c>
@@ -2345,7 +2360,7 @@
       <c r="S10" s="5"/>
       <c r="T10" s="5"/>
     </row>
-    <row r="11" ht="138" spans="1:20">
+    <row r="11" ht="120" spans="1:20">
       <c r="A11" s="5">
         <v>10050</v>
       </c>
@@ -2391,7 +2406,7 @@
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
     </row>
-    <row r="12" ht="69" spans="1:20">
+    <row r="12" ht="60" spans="1:20">
       <c r="A12" s="5">
         <v>10101</v>
       </c>
@@ -2435,7 +2450,7 @@
       <c r="S12" s="5"/>
       <c r="T12" s="5"/>
     </row>
-    <row r="13" s="1" customFormat="1" ht="104" spans="1:20">
+    <row r="13" s="1" customFormat="1" ht="90" spans="1:20">
       <c r="A13" s="6">
         <v>10201</v>
       </c>
@@ -2460,7 +2475,7 @@
       <c r="H13" s="6">
         <v>0</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="7" t="s">
         <v>60</v>
       </c>
       <c r="J13" s="6">
@@ -2470,16 +2485,16 @@
         <v>10202</v>
       </c>
       <c r="L13" s="4"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
       <c r="Q13" s="6"/>
       <c r="R13" s="6"/>
       <c r="S13" s="6"/>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" ht="104" spans="1:20">
+    <row r="14" ht="90" spans="1:20">
       <c r="A14" s="5">
         <v>10202</v>
       </c>
@@ -2525,7 +2540,7 @@
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
     </row>
-    <row r="15" ht="69" spans="1:20">
+    <row r="15" ht="60" spans="1:20">
       <c r="A15" s="5">
         <v>10203</v>
       </c>
@@ -2569,7 +2584,7 @@
       <c r="S15" s="5"/>
       <c r="T15" s="5"/>
     </row>
-    <row r="16" ht="138" spans="1:20">
+    <row r="16" ht="120" spans="1:20">
       <c r="A16" s="5">
         <v>10204</v>
       </c>
@@ -2613,7 +2628,7 @@
       <c r="S16" s="5"/>
       <c r="T16" s="5"/>
     </row>
-    <row r="17" ht="138" spans="1:20">
+    <row r="17" ht="120" spans="1:20">
       <c r="A17" s="5">
         <v>10205</v>
       </c>
@@ -2657,7 +2672,7 @@
       <c r="S17" s="5"/>
       <c r="T17" s="5"/>
     </row>
-    <row r="18" s="1" customFormat="1" ht="104" spans="1:20">
+    <row r="18" s="1" customFormat="1" ht="90" spans="1:20">
       <c r="A18" s="5">
         <v>10206</v>
       </c>
@@ -2682,7 +2697,7 @@
       <c r="H18" s="6">
         <v>0</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="7" t="s">
         <v>66</v>
       </c>
       <c r="J18" s="6">
@@ -2692,16 +2707,16 @@
         <v>10207</v>
       </c>
       <c r="L18" s="4"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
       <c r="S18" s="6"/>
       <c r="T18" s="6"/>
     </row>
-    <row r="19" ht="35" spans="1:20">
+    <row r="19" spans="1:20">
       <c r="A19" s="5">
         <v>10207</v>
       </c>
@@ -2745,7 +2760,7 @@
       <c r="S19" s="5"/>
       <c r="T19" s="5"/>
     </row>
-    <row r="20" ht="35" spans="1:20">
+    <row r="20" spans="1:20">
       <c r="A20" s="5">
         <v>10208</v>
       </c>
@@ -2789,7 +2804,7 @@
       <c r="S20" s="5"/>
       <c r="T20" s="5"/>
     </row>
-    <row r="21" ht="69" spans="1:20">
+    <row r="21" ht="60" spans="1:20">
       <c r="A21" s="5">
         <v>1301</v>
       </c>
@@ -2833,7 +2848,7 @@
       <c r="S21" s="5"/>
       <c r="T21" s="5"/>
     </row>
-    <row r="22" ht="138" spans="1:20">
+    <row r="22" ht="120" spans="1:20">
       <c r="A22" s="5">
         <v>1302</v>
       </c>
@@ -2877,7 +2892,7 @@
       <c r="S22" s="5"/>
       <c r="T22" s="5"/>
     </row>
-    <row r="23" ht="69" spans="1:20">
+    <row r="23" ht="60" spans="1:20">
       <c r="A23" s="5">
         <v>1401</v>
       </c>
@@ -2921,7 +2936,7 @@
       <c r="S23" s="5"/>
       <c r="T23" s="5"/>
     </row>
-    <row r="24" ht="138" spans="1:20">
+    <row r="24" ht="120" spans="1:20">
       <c r="A24" s="5">
         <v>1402</v>
       </c>
@@ -2965,7 +2980,7 @@
       <c r="S24" s="5"/>
       <c r="T24" s="5"/>
     </row>
-    <row r="25" ht="104" spans="1:20">
+    <row r="25" ht="90" spans="1:20">
       <c r="A25" s="5">
         <v>1501</v>
       </c>
@@ -3009,7 +3024,7 @@
       <c r="S25" s="5"/>
       <c r="T25" s="5"/>
     </row>
-    <row r="26" ht="172" spans="1:20">
+    <row r="26" ht="150" spans="1:20">
       <c r="A26" s="5">
         <v>1502</v>
       </c>
@@ -3053,7 +3068,7 @@
       <c r="S26" s="5"/>
       <c r="T26" s="5"/>
     </row>
-    <row r="27" ht="104" spans="1:20">
+    <row r="27" ht="90" spans="1:20">
       <c r="A27" s="5">
         <v>1601</v>
       </c>
@@ -3097,7 +3112,7 @@
       <c r="S27" s="5"/>
       <c r="T27" s="5"/>
     </row>
-    <row r="28" ht="69" spans="1:20">
+    <row r="28" ht="60" spans="1:20">
       <c r="A28" s="5">
         <v>1701</v>
       </c>
@@ -3141,7 +3156,7 @@
       <c r="S28" s="5"/>
       <c r="T28" s="5"/>
     </row>
-    <row r="29" ht="69" spans="1:20">
+    <row r="29" ht="60" spans="1:20">
       <c r="A29" s="5">
         <v>10301</v>
       </c>
@@ -3185,7 +3200,7 @@
       <c r="S29" s="5"/>
       <c r="T29" s="5"/>
     </row>
-    <row r="30" ht="104" spans="1:20">
+    <row r="30" ht="90" spans="1:20">
       <c r="A30" s="5">
         <v>10401</v>
       </c>
@@ -3201,7 +3216,7 @@
       <c r="E30" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="8" t="s">
         <v>47</v>
       </c>
       <c r="G30" s="5">
@@ -3229,7 +3244,7 @@
       <c r="S30" s="5"/>
       <c r="T30" s="5"/>
     </row>
-    <row r="31" ht="104" spans="1:20">
+    <row r="31" ht="90" spans="1:20">
       <c r="A31" s="5">
         <v>10402</v>
       </c>
@@ -3245,7 +3260,7 @@
       <c r="E31" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="8" t="s">
         <v>47</v>
       </c>
       <c r="G31" s="5">
@@ -3273,7 +3288,7 @@
       <c r="S31" s="5"/>
       <c r="T31" s="5"/>
     </row>
-    <row r="32" ht="138" spans="1:20">
+    <row r="32" ht="120" spans="1:20">
       <c r="A32" s="5">
         <v>10404</v>
       </c>
@@ -3289,7 +3304,7 @@
       <c r="E32" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="8" t="s">
         <v>47</v>
       </c>
       <c r="G32" s="5">
@@ -3317,7 +3332,7 @@
       <c r="S32" s="5"/>
       <c r="T32" s="5"/>
     </row>
-    <row r="33" ht="35" spans="1:20">
+    <row r="33" spans="1:20">
       <c r="A33" s="5">
         <v>10403</v>
       </c>
@@ -3333,7 +3348,7 @@
       <c r="E33" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="8" t="s">
         <v>47</v>
       </c>
       <c r="G33" s="5">
@@ -3361,7 +3376,7 @@
       <c r="S33" s="5"/>
       <c r="T33" s="5"/>
     </row>
-    <row r="34" ht="104" spans="1:20">
+    <row r="34" ht="90" spans="1:20">
       <c r="A34" s="5">
         <v>10501</v>
       </c>
@@ -3405,7 +3420,7 @@
       <c r="S34" s="5"/>
       <c r="T34" s="5"/>
     </row>
-    <row r="35" ht="104" spans="1:20">
+    <row r="35" ht="90" spans="1:20">
       <c r="A35" s="5">
         <v>10502</v>
       </c>
@@ -3449,7 +3464,7 @@
       <c r="S35" s="5"/>
       <c r="T35" s="5"/>
     </row>
-    <row r="36" s="1" customFormat="1" ht="138" spans="1:20">
+    <row r="36" s="1" customFormat="1" ht="120" spans="1:20">
       <c r="A36" s="5">
         <v>10503</v>
       </c>
@@ -3495,7 +3510,7 @@
       <c r="S36" s="5"/>
       <c r="T36" s="5"/>
     </row>
-    <row r="37" s="1" customFormat="1" ht="172" spans="1:20">
+    <row r="37" s="1" customFormat="1" ht="150" spans="1:20">
       <c r="A37" s="6">
         <v>10550</v>
       </c>
@@ -3532,16 +3547,16 @@
       <c r="L37" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
-      <c r="P37" s="9"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="7"/>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
       <c r="Q37" s="6"/>
       <c r="R37" s="6"/>
       <c r="S37" s="6"/>
       <c r="T37" s="6"/>
     </row>
-    <row r="38" s="1" customFormat="1" ht="172" spans="1:20">
+    <row r="38" s="1" customFormat="1" ht="150" spans="1:20">
       <c r="A38" s="6">
         <v>1801</v>
       </c>
@@ -3566,7 +3581,7 @@
       <c r="H38" s="6">
         <v>0</v>
       </c>
-      <c r="I38" s="9" t="s">
+      <c r="I38" s="7" t="s">
         <v>93</v>
       </c>
       <c r="J38" s="6">
@@ -3576,10 +3591,10 @@
         <v>1802</v>
       </c>
       <c r="L38" s="4"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
-      <c r="P38" s="9"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
+      <c r="P38" s="7"/>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
       <c r="S38" s="6"/>
@@ -3620,16 +3635,16 @@
         <v>1803</v>
       </c>
       <c r="L39" s="4"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="9"/>
+      <c r="M39" s="7"/>
+      <c r="N39" s="7"/>
+      <c r="O39" s="7"/>
+      <c r="P39" s="7"/>
       <c r="Q39" s="6"/>
       <c r="R39" s="6"/>
       <c r="S39" s="6"/>
       <c r="T39" s="6"/>
     </row>
-    <row r="40" customFormat="1" ht="69" spans="1:20">
+    <row r="40" customFormat="1" ht="60" spans="1:20">
       <c r="A40" s="5">
         <v>1803</v>
       </c>
@@ -3679,7 +3694,7 @@
       <c r="S40" s="5"/>
       <c r="T40" s="5"/>
     </row>
-    <row r="41" ht="69" spans="1:20">
+    <row r="41" ht="60" spans="1:20">
       <c r="A41" s="5">
         <v>10601</v>
       </c>
@@ -3723,7 +3738,7 @@
       <c r="S41" s="5"/>
       <c r="T41" s="5"/>
     </row>
-    <row r="42" ht="35" spans="1:20">
+    <row r="42" spans="1:20">
       <c r="A42" s="5">
         <v>10602</v>
       </c>
@@ -3767,7 +3782,7 @@
       <c r="S42" s="5"/>
       <c r="T42" s="5"/>
     </row>
-    <row r="43" ht="69" spans="1:20">
+    <row r="43" ht="60" spans="1:20">
       <c r="A43" s="5">
         <v>10603</v>
       </c>
@@ -3811,7 +3826,7 @@
       <c r="S43" s="5"/>
       <c r="T43" s="5"/>
     </row>
-    <row r="44" ht="69" spans="1:20">
+    <row r="44" ht="60" spans="1:20">
       <c r="A44" s="5">
         <v>10604</v>
       </c>
@@ -3855,7 +3870,7 @@
       <c r="S44" s="5"/>
       <c r="T44" s="5"/>
     </row>
-    <row r="45" ht="35" spans="1:20">
+    <row r="45" spans="1:20">
       <c r="A45" s="5">
         <v>10701</v>
       </c>
@@ -3899,7 +3914,7 @@
       <c r="S45" s="5"/>
       <c r="T45" s="5"/>
     </row>
-    <row r="46" ht="69" spans="1:20">
+    <row r="46" ht="60" spans="1:20">
       <c r="A46" s="5">
         <v>10702</v>
       </c>
@@ -3943,7 +3958,7 @@
       <c r="S46" s="5"/>
       <c r="T46" s="5"/>
     </row>
-    <row r="47" ht="138" spans="1:20">
+    <row r="47" ht="120" spans="1:20">
       <c r="A47" s="5">
         <v>10703</v>
       </c>
@@ -3987,7 +4002,7 @@
       <c r="S47" s="5"/>
       <c r="T47" s="5"/>
     </row>
-    <row r="48" ht="207" spans="1:20">
+    <row r="48" ht="180" spans="1:20">
       <c r="A48" s="5">
         <v>10704</v>
       </c>
@@ -4033,7 +4048,7 @@
       <c r="S48" s="5"/>
       <c r="T48" s="5"/>
     </row>
-    <row r="49" ht="172" spans="1:20">
+    <row r="49" ht="150" spans="1:20">
       <c r="A49" s="5">
         <v>10705</v>
       </c>
@@ -4079,7 +4094,7 @@
       <c r="S49" s="5"/>
       <c r="T49" s="5"/>
     </row>
-    <row r="50" ht="138" spans="1:20">
+    <row r="50" ht="120" spans="1:20">
       <c r="A50" s="5">
         <v>10706</v>
       </c>
@@ -4125,7 +4140,7 @@
       <c r="S50" s="5"/>
       <c r="T50" s="5"/>
     </row>
-    <row r="51" ht="241" spans="1:20">
+    <row r="51" ht="210" spans="1:20">
       <c r="A51" s="5">
         <v>10707</v>
       </c>
@@ -4171,7 +4186,7 @@
       <c r="S51" s="5"/>
       <c r="T51" s="5"/>
     </row>
-    <row r="52" ht="138" spans="1:20">
+    <row r="52" ht="120" spans="1:20">
       <c r="A52" s="5">
         <v>10708</v>
       </c>
@@ -4217,7 +4232,7 @@
       <c r="S52" s="5"/>
       <c r="T52" s="5"/>
     </row>
-    <row r="53" ht="69" spans="1:20">
+    <row r="53" ht="60" spans="1:20">
       <c r="A53" s="5">
         <v>10801</v>
       </c>
@@ -4261,7 +4276,7 @@
       <c r="S53" s="5"/>
       <c r="T53" s="5"/>
     </row>
-    <row r="54" ht="138" spans="1:20">
+    <row r="54" ht="120" spans="1:20">
       <c r="A54" s="5">
         <v>10802</v>
       </c>
@@ -4305,7 +4320,7 @@
       <c r="S54" s="5"/>
       <c r="T54" s="5"/>
     </row>
-    <row r="55" ht="69" spans="1:20">
+    <row r="55" ht="63" spans="1:20">
       <c r="A55" s="5">
         <v>10803</v>
       </c>
@@ -4349,7 +4364,7 @@
       <c r="S55" s="5"/>
       <c r="T55" s="5"/>
     </row>
-    <row r="56" ht="69" spans="1:20">
+    <row r="56" ht="60" spans="1:20">
       <c r="A56" s="5">
         <v>10804</v>
       </c>
@@ -4393,7 +4408,7 @@
       <c r="S56" s="5"/>
       <c r="T56" s="5"/>
     </row>
-    <row r="57" ht="104" spans="1:20">
+    <row r="57" ht="90" spans="1:20">
       <c r="A57" s="5">
         <v>10901</v>
       </c>
@@ -4437,7 +4452,7 @@
       <c r="S57" s="5"/>
       <c r="T57" s="5"/>
     </row>
-    <row r="58" ht="104" spans="1:20">
+    <row r="58" ht="90" spans="1:20">
       <c r="A58" s="5">
         <v>10902</v>
       </c>
@@ -4481,7 +4496,7 @@
       <c r="S58" s="5"/>
       <c r="T58" s="5"/>
     </row>
-    <row r="59" ht="104" spans="1:20">
+    <row r="59" ht="90" spans="1:20">
       <c r="A59" s="5">
         <v>10903</v>
       </c>
@@ -4525,7 +4540,7 @@
       <c r="S59" s="5"/>
       <c r="T59" s="5"/>
     </row>
-    <row r="60" ht="69" spans="1:20">
+    <row r="60" ht="60" spans="1:20">
       <c r="A60" s="5">
         <v>10904</v>
       </c>
@@ -4569,7 +4584,7 @@
       <c r="S60" s="5"/>
       <c r="T60" s="5"/>
     </row>
-    <row r="61" ht="138" spans="1:20">
+    <row r="61" ht="120" spans="1:20">
       <c r="A61" s="5">
         <v>10905</v>
       </c>
@@ -4613,7 +4628,7 @@
       <c r="S61" s="5"/>
       <c r="T61" s="5"/>
     </row>
-    <row r="62" ht="138" spans="1:20">
+    <row r="62" ht="120" spans="1:20">
       <c r="A62" s="5">
         <v>10906</v>
       </c>
@@ -4657,7 +4672,7 @@
       <c r="S62" s="5"/>
       <c r="T62" s="5"/>
     </row>
-    <row r="63" ht="69" spans="1:20">
+    <row r="63" ht="60" spans="1:20">
       <c r="A63" s="5">
         <v>10907</v>
       </c>
@@ -4670,10 +4685,10 @@
       <c r="D63" s="5">
         <v>1</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="E63" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F63" s="8" t="s">
+      <c r="F63" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G63" s="5">
@@ -4701,7 +4716,7 @@
       <c r="S63" s="5"/>
       <c r="T63" s="5"/>
     </row>
-    <row r="64" ht="69" spans="1:20">
+    <row r="64" ht="60" spans="1:20">
       <c r="A64" s="5">
         <v>10908</v>
       </c>
@@ -4745,7 +4760,7 @@
       <c r="S64" s="5"/>
       <c r="T64" s="5"/>
     </row>
-    <row r="65" ht="104" spans="1:20">
+    <row r="65" ht="90" spans="1:20">
       <c r="A65" s="5">
         <v>10909</v>
       </c>
@@ -4789,7 +4804,7 @@
       <c r="S65" s="5"/>
       <c r="T65" s="5"/>
     </row>
-    <row r="66" ht="104" spans="1:20">
+    <row r="66" ht="90" spans="1:20">
       <c r="A66" s="5">
         <v>10910</v>
       </c>
@@ -4802,10 +4817,10 @@
       <c r="D66" s="5">
         <v>1</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E66" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F66" s="8" t="s">
+      <c r="F66" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G66" s="5">
@@ -4833,7 +4848,7 @@
       <c r="S66" s="5"/>
       <c r="T66" s="5"/>
     </row>
-    <row r="67" ht="69" spans="1:20">
+    <row r="67" ht="60" spans="1:20">
       <c r="A67" s="5">
         <v>10911</v>
       </c>
@@ -4877,7 +4892,7 @@
       <c r="S67" s="5"/>
       <c r="T67" s="5"/>
     </row>
-    <row r="68" ht="104" spans="1:20">
+    <row r="68" ht="90" spans="1:20">
       <c r="A68" s="5">
         <v>10912</v>
       </c>
@@ -4923,7 +4938,7 @@
       <c r="S68" s="5"/>
       <c r="T68" s="5"/>
     </row>
-    <row r="69" ht="104" spans="1:20">
+    <row r="69" ht="90" spans="1:20">
       <c r="A69" s="5">
         <v>10950</v>
       </c>
@@ -4969,7 +4984,7 @@
       <c r="S69" s="5"/>
       <c r="T69" s="5"/>
     </row>
-    <row r="70" ht="104" spans="1:20">
+    <row r="70" ht="90" spans="1:20">
       <c r="A70" s="5">
         <v>11001</v>
       </c>
@@ -5013,7 +5028,7 @@
       <c r="S70" s="5"/>
       <c r="T70" s="5"/>
     </row>
-    <row r="71" ht="35" spans="1:20">
+    <row r="71" spans="1:20">
       <c r="A71" s="5">
         <v>11002</v>
       </c>
@@ -5057,7 +5072,7 @@
       <c r="S71" s="5"/>
       <c r="T71" s="5"/>
     </row>
-    <row r="72" ht="104" spans="1:20">
+    <row r="72" ht="90" spans="1:20">
       <c r="A72" s="5">
         <v>11101</v>
       </c>
@@ -5101,7 +5116,7 @@
       <c r="S72" s="5"/>
       <c r="T72" s="5"/>
     </row>
-    <row r="73" ht="69" spans="1:20">
+    <row r="73" ht="60" spans="1:20">
       <c r="A73" s="5">
         <v>11102</v>
       </c>
@@ -5114,10 +5129,10 @@
       <c r="D73" s="5">
         <v>1</v>
       </c>
-      <c r="E73" s="8" t="s">
+      <c r="E73" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F73" s="8" t="s">
+      <c r="F73" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G73" s="5">
@@ -5145,7 +5160,7 @@
       <c r="S73" s="5"/>
       <c r="T73" s="5"/>
     </row>
-    <row r="74" ht="172" spans="1:20">
+    <row r="74" ht="150" spans="1:20">
       <c r="A74" s="5">
         <v>11103</v>
       </c>
@@ -5189,7 +5204,7 @@
       <c r="S74" s="5"/>
       <c r="T74" s="5"/>
     </row>
-    <row r="75" ht="172" spans="1:20">
+    <row r="75" ht="150" spans="1:20">
       <c r="A75" s="5">
         <v>11150</v>
       </c>
@@ -5235,7 +5250,7 @@
       <c r="S75" s="5"/>
       <c r="T75" s="5"/>
     </row>
-    <row r="76" ht="104" spans="1:20">
+    <row r="76" ht="90" spans="1:20">
       <c r="A76" s="5">
         <v>1901</v>
       </c>
@@ -5279,7 +5294,7 @@
       <c r="S76" s="5"/>
       <c r="T76" s="5"/>
     </row>
-    <row r="77" ht="138" spans="1:20">
+    <row r="77" ht="120" spans="1:20">
       <c r="A77" s="5">
         <v>1902</v>
       </c>
@@ -5323,7 +5338,7 @@
       <c r="S77" s="5"/>
       <c r="T77" s="5"/>
     </row>
-    <row r="78" ht="104" spans="1:20">
+    <row r="78" ht="90" spans="1:20">
       <c r="A78" s="5">
         <v>11201</v>
       </c>
@@ -5336,10 +5351,10 @@
       <c r="D78" s="5">
         <v>0</v>
       </c>
-      <c r="E78" s="8" t="s">
+      <c r="E78" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F78" s="8" t="s">
+      <c r="F78" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G78" s="5">
@@ -5367,7 +5382,7 @@
       <c r="S78" s="5"/>
       <c r="T78" s="5"/>
     </row>
-    <row r="79" ht="69" spans="1:20">
+    <row r="79" ht="60" spans="1:20">
       <c r="A79" s="5">
         <v>11202</v>
       </c>
@@ -5411,7 +5426,7 @@
       <c r="S79" s="5"/>
       <c r="T79" s="5"/>
     </row>
-    <row r="80" ht="207" spans="1:20">
+    <row r="80" ht="180" spans="1:20">
       <c r="A80" s="5">
         <v>11203</v>
       </c>
@@ -5455,7 +5470,7 @@
       <c r="S80" s="5"/>
       <c r="T80" s="5"/>
     </row>
-    <row r="81" ht="104" spans="1:20">
+    <row r="81" ht="90" spans="1:20">
       <c r="A81" s="5">
         <v>11204</v>
       </c>
@@ -5499,7 +5514,7 @@
       <c r="S81" s="5"/>
       <c r="T81" s="5"/>
     </row>
-    <row r="82" ht="104" spans="1:20">
+    <row r="82" ht="90" spans="1:20">
       <c r="A82" s="5">
         <v>11205</v>
       </c>
@@ -5545,7 +5560,7 @@
       <c r="S82" s="5"/>
       <c r="T82" s="5"/>
     </row>
-    <row r="83" ht="69" spans="1:20">
+    <row r="83" ht="60" spans="1:20">
       <c r="A83" s="5">
         <v>11301</v>
       </c>
@@ -5589,7 +5604,7 @@
       <c r="S83" s="5"/>
       <c r="T83" s="5"/>
     </row>
-    <row r="84" ht="104" spans="1:20">
+    <row r="84" ht="90" spans="1:20">
       <c r="A84" s="5">
         <v>11302</v>
       </c>
@@ -5605,7 +5620,7 @@
       <c r="E84" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F84" s="7" t="s">
+      <c r="F84" s="8" t="s">
         <v>47</v>
       </c>
       <c r="G84" s="5">
@@ -5633,7 +5648,7 @@
       <c r="S84" s="5"/>
       <c r="T84" s="5"/>
     </row>
-    <row r="85" ht="69" spans="1:20">
+    <row r="85" spans="1:20">
       <c r="A85" s="5">
         <v>11303</v>
       </c>
@@ -5677,7 +5692,7 @@
       <c r="S85" s="5"/>
       <c r="T85" s="5"/>
     </row>
-    <row r="86" ht="138" spans="1:20">
+    <row r="86" ht="120" spans="1:20">
       <c r="A86" s="5">
         <v>11304</v>
       </c>
@@ -5721,7 +5736,7 @@
       <c r="S86" s="5"/>
       <c r="T86" s="5"/>
     </row>
-    <row r="87" ht="207" spans="1:20">
+    <row r="87" ht="180" spans="1:20">
       <c r="A87" s="5">
         <v>11305</v>
       </c>
@@ -5737,7 +5752,7 @@
       <c r="E87" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F87" s="7" t="s">
+      <c r="F87" s="8" t="s">
         <v>47</v>
       </c>
       <c r="G87" s="5">
@@ -5765,7 +5780,7 @@
       <c r="S87" s="5"/>
       <c r="T87" s="5"/>
     </row>
-    <row r="88" ht="138" spans="1:20">
+    <row r="88" ht="120" spans="1:20">
       <c r="A88" s="5">
         <v>11306</v>
       </c>
@@ -5781,7 +5796,7 @@
       <c r="E88" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F88" s="7" t="s">
+      <c r="F88" s="8" t="s">
         <v>47</v>
       </c>
       <c r="G88" s="5">
@@ -5809,7 +5824,7 @@
       <c r="S88" s="5"/>
       <c r="T88" s="5"/>
     </row>
-    <row r="89" ht="138" spans="1:20">
+    <row r="89" ht="120" spans="1:20">
       <c r="A89" s="5">
         <v>11307</v>
       </c>
@@ -5825,7 +5840,7 @@
       <c r="E89" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F89" s="7" t="s">
+      <c r="F89" s="8" t="s">
         <v>47</v>
       </c>
       <c r="G89" s="5">
@@ -5853,7 +5868,7 @@
       <c r="S89" s="5"/>
       <c r="T89" s="5"/>
     </row>
-    <row r="90" ht="172" spans="1:20">
+    <row r="90" ht="150" spans="1:20">
       <c r="A90" s="5">
         <v>11308</v>
       </c>
@@ -5899,7 +5914,7 @@
       <c r="S90" s="5"/>
       <c r="T90" s="5"/>
     </row>
-    <row r="91" ht="69" spans="1:20">
+    <row r="91" ht="60" spans="1:20">
       <c r="A91" s="5">
         <v>2001</v>
       </c>
@@ -5915,7 +5930,7 @@
       <c r="E91" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F91" s="7" t="s">
+      <c r="F91" s="8" t="s">
         <v>47</v>
       </c>
       <c r="G91" s="5">
@@ -5943,7 +5958,7 @@
       <c r="S91" s="5"/>
       <c r="T91" s="5"/>
     </row>
-    <row r="92" ht="69" spans="1:20">
+    <row r="92" ht="60" spans="1:20">
       <c r="A92" s="5">
         <v>2101</v>
       </c>
@@ -5959,7 +5974,7 @@
       <c r="E92" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F92" s="7" t="s">
+      <c r="F92" s="8" t="s">
         <v>47</v>
       </c>
       <c r="G92" s="5">
@@ -5987,7 +6002,7 @@
       <c r="S92" s="5"/>
       <c r="T92" s="5"/>
     </row>
-    <row r="93" ht="35" spans="1:20">
+    <row r="93" spans="1:20">
       <c r="A93" s="5">
         <v>2201</v>
       </c>
@@ -6003,7 +6018,7 @@
       <c r="E93" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="F93" s="7" t="s">
+      <c r="F93" s="8" t="s">
         <v>47</v>
       </c>
       <c r="G93" s="5">
@@ -6031,7 +6046,7 @@
       <c r="S93" s="5"/>
       <c r="T93" s="5"/>
     </row>
-    <row r="94" ht="104" spans="1:20">
+    <row r="94" ht="90" spans="1:20">
       <c r="A94" s="5">
         <v>2301</v>
       </c>
@@ -6075,7 +6090,7 @@
       <c r="S94" s="5"/>
       <c r="T94" s="5"/>
     </row>
-    <row r="95" ht="69" spans="1:20">
+    <row r="95" ht="60" spans="1:20">
       <c r="A95" s="5">
         <v>11401</v>
       </c>
@@ -6119,7 +6134,7 @@
       <c r="S95" s="5"/>
       <c r="T95" s="5"/>
     </row>
-    <row r="96" ht="104" spans="1:20">
+    <row r="96" ht="90" spans="1:20">
       <c r="A96" s="5">
         <v>11402</v>
       </c>
@@ -6163,7 +6178,7 @@
       <c r="S96" s="5"/>
       <c r="T96" s="5"/>
     </row>
-    <row r="97" ht="69" spans="1:20">
+    <row r="97" ht="60" spans="1:20">
       <c r="A97" s="5">
         <v>11403</v>
       </c>
@@ -6209,7 +6224,7 @@
       <c r="S97" s="5"/>
       <c r="T97" s="5"/>
     </row>
-    <row r="98" ht="104" spans="1:20">
+    <row r="98" ht="90" spans="1:20">
       <c r="A98" s="5">
         <v>11501</v>
       </c>
@@ -6225,7 +6240,7 @@
       <c r="E98" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="F98" s="7" t="s">
+      <c r="F98" s="8" t="s">
         <v>47</v>
       </c>
       <c r="G98" s="5">
@@ -6253,7 +6268,7 @@
       <c r="S98" s="5"/>
       <c r="T98" s="5"/>
     </row>
-    <row r="99" ht="138" spans="1:20">
+    <row r="99" ht="120" spans="1:20">
       <c r="A99" s="5">
         <v>11502</v>
       </c>
@@ -6266,10 +6281,10 @@
       <c r="D99" s="5">
         <v>1</v>
       </c>
-      <c r="E99" s="8" t="s">
+      <c r="E99" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F99" s="8" t="s">
+      <c r="F99" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G99" s="5">
@@ -6297,7 +6312,7 @@
       <c r="S99" s="5"/>
       <c r="T99" s="5"/>
     </row>
-    <row r="100" ht="138" spans="1:20">
+    <row r="100" ht="120" spans="1:20">
       <c r="A100" s="5">
         <v>11503</v>
       </c>
@@ -6310,10 +6325,10 @@
       <c r="D100" s="5">
         <v>1</v>
       </c>
-      <c r="E100" s="8" t="s">
+      <c r="E100" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F100" s="8" t="s">
+      <c r="F100" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G100" s="5">
@@ -6341,7 +6356,7 @@
       <c r="S100" s="5"/>
       <c r="T100" s="5"/>
     </row>
-    <row r="101" ht="35" spans="1:20">
+    <row r="101" spans="1:20">
       <c r="A101" s="5">
         <v>11504</v>
       </c>
@@ -6354,10 +6369,10 @@
       <c r="D101" s="5">
         <v>1</v>
       </c>
-      <c r="E101" s="8" t="s">
+      <c r="E101" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F101" s="8" t="s">
+      <c r="F101" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G101" s="5">
@@ -6385,7 +6400,7 @@
       <c r="S101" s="5"/>
       <c r="T101" s="5"/>
     </row>
-    <row r="102" ht="69" spans="1:20">
+    <row r="102" ht="60" spans="1:20">
       <c r="A102" s="5">
         <v>11505</v>
       </c>
@@ -6398,10 +6413,10 @@
       <c r="D102" s="5">
         <v>1</v>
       </c>
-      <c r="E102" s="8" t="s">
+      <c r="E102" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F102" s="8" t="s">
+      <c r="F102" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G102" s="5">
@@ -6429,7 +6444,7 @@
       <c r="S102" s="5"/>
       <c r="T102" s="5"/>
     </row>
-    <row r="103" ht="35" spans="1:20">
+    <row r="103" spans="1:20">
       <c r="A103" s="5">
         <v>11506</v>
       </c>
@@ -6442,10 +6457,10 @@
       <c r="D103" s="5">
         <v>1</v>
       </c>
-      <c r="E103" s="8" t="s">
+      <c r="E103" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F103" s="8" t="s">
+      <c r="F103" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G103" s="5">
@@ -6473,7 +6488,7 @@
       <c r="S103" s="5"/>
       <c r="T103" s="5"/>
     </row>
-    <row r="104" ht="69" spans="1:20">
+    <row r="104" ht="60" spans="1:20">
       <c r="A104" s="5">
         <v>11507</v>
       </c>
@@ -6486,10 +6501,10 @@
       <c r="D104" s="5">
         <v>1</v>
       </c>
-      <c r="E104" s="8" t="s">
+      <c r="E104" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F104" s="8" t="s">
+      <c r="F104" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G104" s="5">
@@ -6517,7 +6532,7 @@
       <c r="S104" s="5"/>
       <c r="T104" s="5"/>
     </row>
-    <row r="105" ht="172" spans="1:20">
+    <row r="105" ht="150" spans="1:20">
       <c r="A105" s="5">
         <v>11601</v>
       </c>
@@ -6530,10 +6545,10 @@
       <c r="D105" s="5">
         <v>0</v>
       </c>
-      <c r="E105" s="8" t="s">
+      <c r="E105" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F105" s="8" t="s">
+      <c r="F105" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G105" s="5">
@@ -6561,7 +6576,7 @@
       <c r="S105" s="5"/>
       <c r="T105" s="5"/>
     </row>
-    <row r="106" ht="104" spans="1:20">
+    <row r="106" ht="90" spans="1:20">
       <c r="A106" s="5">
         <v>11602</v>
       </c>
@@ -6574,10 +6589,10 @@
       <c r="D106" s="5">
         <v>1</v>
       </c>
-      <c r="E106" s="8" t="s">
+      <c r="E106" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F106" s="8" t="s">
+      <c r="F106" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G106" s="5">
@@ -6605,7 +6620,7 @@
       <c r="S106" s="5"/>
       <c r="T106" s="5"/>
     </row>
-    <row r="107" ht="35" spans="1:20">
+    <row r="107" spans="1:20">
       <c r="A107" s="5">
         <v>11603</v>
       </c>
@@ -6618,10 +6633,10 @@
       <c r="D107" s="5">
         <v>1</v>
       </c>
-      <c r="E107" s="8" t="s">
+      <c r="E107" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F107" s="8" t="s">
+      <c r="F107" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G107" s="5">
@@ -6649,7 +6664,7 @@
       <c r="S107" s="5"/>
       <c r="T107" s="5"/>
     </row>
-    <row r="108" ht="104" spans="1:20">
+    <row r="108" ht="90" spans="1:20">
       <c r="A108" s="5">
         <v>11604</v>
       </c>
@@ -6662,10 +6677,10 @@
       <c r="D108" s="5">
         <v>1</v>
       </c>
-      <c r="E108" s="8" t="s">
+      <c r="E108" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F108" s="8" t="s">
+      <c r="F108" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G108" s="5">
@@ -6693,7 +6708,7 @@
       <c r="S108" s="5"/>
       <c r="T108" s="5"/>
     </row>
-    <row r="109" ht="35" spans="1:20">
+    <row r="109" spans="1:20">
       <c r="A109" s="5">
         <v>11605</v>
       </c>
@@ -6706,10 +6721,10 @@
       <c r="D109" s="5">
         <v>1</v>
       </c>
-      <c r="E109" s="8" t="s">
+      <c r="E109" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F109" s="8" t="s">
+      <c r="F109" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G109" s="5">
@@ -6737,7 +6752,7 @@
       <c r="S109" s="5"/>
       <c r="T109" s="5"/>
     </row>
-    <row r="110" ht="104" spans="1:20">
+    <row r="110" ht="90" spans="1:20">
       <c r="A110" s="5">
         <v>11606</v>
       </c>
@@ -6750,10 +6765,10 @@
       <c r="D110" s="5">
         <v>1</v>
       </c>
-      <c r="E110" s="8" t="s">
+      <c r="E110" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F110" s="8" t="s">
+      <c r="F110" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G110" s="5">
@@ -6781,7 +6796,7 @@
       <c r="S110" s="5"/>
       <c r="T110" s="5"/>
     </row>
-    <row r="111" ht="104" spans="1:20">
+    <row r="111" ht="60" spans="1:20">
       <c r="A111" s="5">
         <v>2401</v>
       </c>
@@ -6813,7 +6828,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="5">
-        <v>0</v>
+        <v>2402</v>
       </c>
       <c r="L111" s="4"/>
       <c r="M111" s="4"/>
@@ -6825,15 +6840,15 @@
       <c r="S111" s="5"/>
       <c r="T111" s="5"/>
     </row>
-    <row r="112" ht="104" spans="1:20">
+    <row r="112" ht="90" spans="1:20">
       <c r="A112" s="5">
-        <v>11701</v>
+        <v>2402</v>
       </c>
       <c r="B112" s="5">
         <v>0</v>
       </c>
       <c r="C112" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D112" s="5">
         <v>0</v>
@@ -6848,7 +6863,7 @@
         <v>-1</v>
       </c>
       <c r="H112" s="5">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I112" s="4" t="s">
         <v>172</v>
@@ -6857,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="5">
-        <v>11702</v>
+        <v>2403</v>
       </c>
       <c r="L112" s="4"/>
       <c r="M112" s="4"/>
@@ -6869,9 +6884,9 @@
       <c r="S112" s="5"/>
       <c r="T112" s="5"/>
     </row>
-    <row r="113" ht="35" spans="1:20">
+    <row r="113" ht="90" spans="1:20">
       <c r="A113" s="5">
-        <v>11702</v>
+        <v>2403</v>
       </c>
       <c r="B113" s="5">
         <v>0</v>
@@ -6880,7 +6895,7 @@
         <v>0</v>
       </c>
       <c r="D113" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>42</v>
@@ -6901,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="5">
-        <v>11703</v>
+        <v>2404</v>
       </c>
       <c r="L113" s="4"/>
       <c r="M113" s="4"/>
@@ -6913,18 +6928,18 @@
       <c r="S113" s="5"/>
       <c r="T113" s="5"/>
     </row>
-    <row r="114" ht="69" spans="1:20">
+    <row r="114" ht="120" spans="1:20">
       <c r="A114" s="5">
-        <v>11703</v>
+        <v>2404</v>
       </c>
       <c r="B114" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C114" s="5">
         <v>0</v>
       </c>
       <c r="D114" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" s="5" t="s">
         <v>42</v>
@@ -6947,7 +6962,9 @@
       <c r="K114" s="5">
         <v>0</v>
       </c>
-      <c r="L114" s="4"/>
+      <c r="L114" s="4" t="s">
+        <v>174</v>
+      </c>
       <c r="M114" s="4"/>
       <c r="N114" s="4"/>
       <c r="O114" s="4"/>
@@ -6957,12 +6974,12 @@
       <c r="S114" s="5"/>
       <c r="T114" s="5"/>
     </row>
-    <row r="115" ht="69" spans="1:20">
+    <row r="115" ht="60" spans="1:20">
       <c r="A115" s="5">
         <v>2501</v>
       </c>
       <c r="B115" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C115" s="5">
         <v>0</v>
@@ -6970,11 +6987,11 @@
       <c r="D115" s="5">
         <v>0</v>
       </c>
-      <c r="E115" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F115" s="5" t="s">
-        <v>43</v>
+      <c r="E115" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F115" s="9" t="s">
+        <v>59</v>
       </c>
       <c r="G115" s="5">
         <v>-1</v>
@@ -7001,12 +7018,12 @@
       <c r="S115" s="5"/>
       <c r="T115" s="5"/>
     </row>
-    <row r="116" ht="69" spans="1:20">
+    <row r="116" ht="90" spans="1:20">
       <c r="A116" s="5">
-        <v>2601</v>
+        <v>11701</v>
       </c>
       <c r="B116" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C116" s="5">
         <v>0</v>
@@ -7014,11 +7031,11 @@
       <c r="D116" s="5">
         <v>0</v>
       </c>
-      <c r="E116" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F116" s="8" t="s">
-        <v>59</v>
+      <c r="E116" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G116" s="5">
         <v>-1</v>
@@ -7033,7 +7050,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="5">
-        <v>2602</v>
+        <v>11702</v>
       </c>
       <c r="L116" s="4"/>
       <c r="M116" s="4"/>
@@ -7045,12 +7062,12 @@
       <c r="S116" s="5"/>
       <c r="T116" s="5"/>
     </row>
-    <row r="117" ht="104" spans="1:20">
+    <row r="117" ht="90" spans="1:20">
       <c r="A117" s="5">
-        <v>2602</v>
+        <v>11702</v>
       </c>
       <c r="B117" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C117" s="5">
         <v>0</v>
@@ -7058,11 +7075,11 @@
       <c r="D117" s="5">
         <v>1</v>
       </c>
-      <c r="E117" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F117" s="8" t="s">
-        <v>59</v>
+      <c r="E117" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G117" s="5">
         <v>-1</v>
@@ -7077,7 +7094,7 @@
         <v>0</v>
       </c>
       <c r="K117" s="5">
-        <v>0</v>
+        <v>11703</v>
       </c>
       <c r="L117" s="4"/>
       <c r="M117" s="4"/>
@@ -7089,18 +7106,18 @@
       <c r="S117" s="5"/>
       <c r="T117" s="5"/>
     </row>
-    <row r="118" ht="69" spans="1:20">
+    <row r="118" ht="60" spans="1:20">
       <c r="A118" s="5">
-        <v>11801</v>
+        <v>11703</v>
       </c>
       <c r="B118" s="5">
         <v>0</v>
       </c>
       <c r="C118" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D118" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>42</v>
@@ -7112,7 +7129,7 @@
         <v>-1</v>
       </c>
       <c r="H118" s="5">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I118" s="4" t="s">
         <v>178</v>
@@ -7121,7 +7138,7 @@
         <v>0</v>
       </c>
       <c r="K118" s="5">
-        <v>11802</v>
+        <v>11704</v>
       </c>
       <c r="L118" s="4"/>
       <c r="M118" s="4"/>
@@ -7133,15 +7150,15 @@
       <c r="S118" s="5"/>
       <c r="T118" s="5"/>
     </row>
-    <row r="119" ht="138" spans="1:20">
+    <row r="119" spans="1:20">
       <c r="A119" s="5">
-        <v>11802</v>
+        <v>11704</v>
       </c>
       <c r="B119" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C119" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D119" s="5">
         <v>1</v>
@@ -7156,7 +7173,7 @@
         <v>-1</v>
       </c>
       <c r="H119" s="5">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I119" s="4" t="s">
         <v>179</v>
@@ -7165,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K119" s="5">
-        <v>11803</v>
+        <v>0</v>
       </c>
       <c r="L119" s="4"/>
       <c r="M119" s="4"/>
@@ -7177,18 +7194,18 @@
       <c r="S119" s="5"/>
       <c r="T119" s="5"/>
     </row>
-    <row r="120" ht="69" spans="1:20">
+    <row r="120" ht="60" spans="1:20">
       <c r="A120" s="5">
-        <v>11803</v>
+        <v>2501</v>
       </c>
       <c r="B120" s="5">
         <v>0</v>
       </c>
       <c r="C120" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D120" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E120" s="5" t="s">
         <v>42</v>
@@ -7200,7 +7217,7 @@
         <v>-1</v>
       </c>
       <c r="H120" s="5">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I120" s="4" t="s">
         <v>180</v>
@@ -7221,10 +7238,230 @@
       <c r="S120" s="5"/>
       <c r="T120" s="5"/>
     </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="5"/>
-      <c r="B121" s="5"/>
-      <c r="C121" s="5"/>
+    <row r="121" ht="60" spans="1:20">
+      <c r="A121" s="5">
+        <v>2601</v>
+      </c>
+      <c r="B121" s="5">
+        <v>2</v>
+      </c>
+      <c r="C121" s="5">
+        <v>0</v>
+      </c>
+      <c r="D121" s="5">
+        <v>0</v>
+      </c>
+      <c r="E121" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F121" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G121" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H121" s="5">
+        <v>0</v>
+      </c>
+      <c r="I121" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="J121" s="5">
+        <v>0</v>
+      </c>
+      <c r="K121" s="5">
+        <v>2602</v>
+      </c>
+      <c r="L121" s="4"/>
+      <c r="M121" s="4"/>
+      <c r="N121" s="4"/>
+      <c r="O121" s="4"/>
+      <c r="P121" s="4"/>
+      <c r="Q121" s="5"/>
+      <c r="R121" s="5"/>
+      <c r="S121" s="5"/>
+      <c r="T121" s="5"/>
+    </row>
+    <row r="122" ht="90" spans="1:20">
+      <c r="A122" s="5">
+        <v>2602</v>
+      </c>
+      <c r="B122" s="5">
+        <v>2</v>
+      </c>
+      <c r="C122" s="5">
+        <v>0</v>
+      </c>
+      <c r="D122" s="5">
+        <v>1</v>
+      </c>
+      <c r="E122" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F122" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G122" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H122" s="5">
+        <v>0</v>
+      </c>
+      <c r="I122" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="J122" s="5">
+        <v>0</v>
+      </c>
+      <c r="K122" s="5">
+        <v>0</v>
+      </c>
+      <c r="L122" s="4"/>
+      <c r="M122" s="4"/>
+      <c r="N122" s="4"/>
+      <c r="O122" s="4"/>
+      <c r="P122" s="4"/>
+      <c r="Q122" s="5"/>
+      <c r="R122" s="5"/>
+      <c r="S122" s="5"/>
+      <c r="T122" s="5"/>
+    </row>
+    <row r="123" ht="63" spans="1:20">
+      <c r="A123" s="5">
+        <v>11801</v>
+      </c>
+      <c r="B123" s="5">
+        <v>0</v>
+      </c>
+      <c r="C123" s="5">
+        <v>0</v>
+      </c>
+      <c r="D123" s="5">
+        <v>0</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G123" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H123" s="5">
+        <v>0</v>
+      </c>
+      <c r="I123" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="J123" s="5">
+        <v>0</v>
+      </c>
+      <c r="K123" s="5">
+        <v>11802</v>
+      </c>
+      <c r="L123" s="4"/>
+      <c r="M123" s="4"/>
+      <c r="N123" s="4"/>
+      <c r="O123" s="4"/>
+      <c r="P123" s="4"/>
+      <c r="Q123" s="5"/>
+      <c r="R123" s="5"/>
+      <c r="S123" s="5"/>
+      <c r="T123" s="5"/>
+    </row>
+    <row r="124" ht="120" spans="1:20">
+      <c r="A124" s="5">
+        <v>11802</v>
+      </c>
+      <c r="B124" s="5">
+        <v>0</v>
+      </c>
+      <c r="C124" s="5">
+        <v>0</v>
+      </c>
+      <c r="D124" s="5">
+        <v>1</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G124" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H124" s="5">
+        <v>0</v>
+      </c>
+      <c r="I124" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="J124" s="5">
+        <v>0</v>
+      </c>
+      <c r="K124" s="5">
+        <v>11803</v>
+      </c>
+      <c r="L124" s="4"/>
+      <c r="M124" s="4"/>
+      <c r="N124" s="4"/>
+      <c r="O124" s="4"/>
+      <c r="P124" s="4"/>
+      <c r="Q124" s="5"/>
+      <c r="R124" s="5"/>
+      <c r="S124" s="5"/>
+      <c r="T124" s="5"/>
+    </row>
+    <row r="125" ht="60" spans="1:20">
+      <c r="A125" s="5">
+        <v>11803</v>
+      </c>
+      <c r="B125" s="5">
+        <v>0</v>
+      </c>
+      <c r="C125" s="5">
+        <v>0</v>
+      </c>
+      <c r="D125" s="5">
+        <v>1</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G125" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H125" s="5">
+        <v>0</v>
+      </c>
+      <c r="I125" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="J125" s="5">
+        <v>0</v>
+      </c>
+      <c r="K125" s="5">
+        <v>0</v>
+      </c>
+      <c r="L125" s="4"/>
+      <c r="M125" s="4"/>
+      <c r="N125" s="4"/>
+      <c r="O125" s="4"/>
+      <c r="P125" s="4"/>
+      <c r="Q125" s="5"/>
+      <c r="R125" s="5"/>
+      <c r="S125" s="5"/>
+      <c r="T125" s="5"/>
+    </row>
+    <row r="126" spans="1:20">
+      <c r="A126" s="5"/>
+      <c r="B126" s="5"/>
+      <c r="C126" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Excel/DialogDatas.xlsx
+++ b/Excel/DialogDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="12780"/>
+    <workbookView windowHeight="15060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1845,28 +1845,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:T126"/>
-  <sheetFormatPr defaultColWidth="9.22222222222222" defaultRowHeight="30.6"/>
+  <sheetFormatPr defaultColWidth="9.22115384615385" defaultRowHeight="34.4"/>
   <cols>
     <col min="1" max="1" width="21" style="2" customWidth="1"/>
-    <col min="2" max="2" width="33.6666666666667" style="2" customWidth="1"/>
-    <col min="3" max="3" width="37.6666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25.4444444444444" style="2" customWidth="1"/>
-    <col min="5" max="5" width="26.1111111111111" style="2" customWidth="1"/>
-    <col min="6" max="6" width="50.8888888888889" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23.6666666666667" style="2" customWidth="1"/>
-    <col min="8" max="8" width="26.1111111111111" style="2" customWidth="1"/>
-    <col min="9" max="9" width="40.8333333333333" style="2" customWidth="1"/>
-    <col min="10" max="10" width="30.1111111111111" style="2" customWidth="1"/>
-    <col min="11" max="11" width="25.6666666666667" style="2" customWidth="1"/>
-    <col min="12" max="16" width="25.6666666666667" style="3" customWidth="1"/>
-    <col min="17" max="17" width="40.0648148148148" style="2" customWidth="1"/>
-    <col min="18" max="18" width="48.4814814814815" style="2" customWidth="1"/>
-    <col min="19" max="19" width="43.2685185185185" style="2" customWidth="1"/>
-    <col min="20" max="20" width="38.8518518518519" style="2" customWidth="1"/>
-    <col min="21" max="16384" width="9.22222222222222" style="2"/>
+    <col min="2" max="2" width="33.6634615384615" style="2" customWidth="1"/>
+    <col min="3" max="3" width="37.6634615384615" style="2" customWidth="1"/>
+    <col min="4" max="4" width="25.4423076923077" style="2" customWidth="1"/>
+    <col min="5" max="5" width="26.1153846153846" style="2" customWidth="1"/>
+    <col min="6" max="6" width="50.8846153846154" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.6634615384615" style="2" customWidth="1"/>
+    <col min="8" max="8" width="26.1153846153846" style="2" customWidth="1"/>
+    <col min="9" max="9" width="40.8365384615385" style="2" customWidth="1"/>
+    <col min="10" max="10" width="30.1153846153846" style="2" customWidth="1"/>
+    <col min="11" max="11" width="25.6634615384615" style="2" customWidth="1"/>
+    <col min="12" max="16" width="25.6634615384615" style="3" customWidth="1"/>
+    <col min="17" max="17" width="40.0673076923077" style="2" customWidth="1"/>
+    <col min="18" max="18" width="48.4807692307692" style="2" customWidth="1"/>
+    <col min="19" max="19" width="43.2692307692308" style="2" customWidth="1"/>
+    <col min="20" max="20" width="38.8557692307692" style="2" customWidth="1"/>
+    <col min="21" max="16384" width="9.22115384615385" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" ht="35" spans="1:20">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1990,7 +1990,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" ht="35" spans="1:20">
       <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" ht="90" spans="1:20">
+    <row r="4" ht="104" spans="1:20">
       <c r="A4" s="5">
         <v>10001</v>
       </c>
@@ -2096,7 +2096,7 @@
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
     </row>
-    <row r="5" ht="90" spans="1:20">
+    <row r="5" ht="104" spans="1:20">
       <c r="A5" s="5">
         <v>10002</v>
       </c>
@@ -2140,7 +2140,7 @@
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
     </row>
-    <row r="6" ht="120" spans="1:20">
+    <row r="6" ht="138" spans="1:20">
       <c r="A6" s="5">
         <v>1001</v>
       </c>
@@ -2184,7 +2184,7 @@
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
     </row>
-    <row r="7" ht="90" spans="1:20">
+    <row r="7" ht="104" spans="1:20">
       <c r="A7" s="5">
         <v>1101</v>
       </c>
@@ -2228,7 +2228,7 @@
       <c r="S7" s="5"/>
       <c r="T7" s="5"/>
     </row>
-    <row r="8" ht="90" spans="1:20">
+    <row r="8" ht="104" spans="1:20">
       <c r="A8" s="5">
         <v>1201</v>
       </c>
@@ -2272,7 +2272,7 @@
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
     </row>
-    <row r="9" ht="120" spans="1:20">
+    <row r="9" ht="138" spans="1:20">
       <c r="A9" s="5">
         <v>1202</v>
       </c>
@@ -2316,7 +2316,7 @@
       <c r="S9" s="5"/>
       <c r="T9" s="5"/>
     </row>
-    <row r="10" ht="90" spans="1:20">
+    <row r="10" ht="104" spans="1:20">
       <c r="A10" s="5">
         <v>1203</v>
       </c>
@@ -2360,7 +2360,7 @@
       <c r="S10" s="5"/>
       <c r="T10" s="5"/>
     </row>
-    <row r="11" ht="120" spans="1:20">
+    <row r="11" ht="138" spans="1:20">
       <c r="A11" s="5">
         <v>10050</v>
       </c>
@@ -2406,7 +2406,7 @@
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
     </row>
-    <row r="12" ht="60" spans="1:20">
+    <row r="12" ht="69" spans="1:20">
       <c r="A12" s="5">
         <v>10101</v>
       </c>
@@ -2450,7 +2450,7 @@
       <c r="S12" s="5"/>
       <c r="T12" s="5"/>
     </row>
-    <row r="13" s="1" customFormat="1" ht="90" spans="1:20">
+    <row r="13" s="1" customFormat="1" ht="104" spans="1:20">
       <c r="A13" s="6">
         <v>10201</v>
       </c>
@@ -2494,7 +2494,7 @@
       <c r="S13" s="6"/>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" ht="90" spans="1:20">
+    <row r="14" ht="104" spans="1:20">
       <c r="A14" s="5">
         <v>10202</v>
       </c>
@@ -2540,7 +2540,7 @@
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
     </row>
-    <row r="15" ht="60" spans="1:20">
+    <row r="15" ht="69" spans="1:20">
       <c r="A15" s="5">
         <v>10203</v>
       </c>
@@ -2584,7 +2584,7 @@
       <c r="S15" s="5"/>
       <c r="T15" s="5"/>
     </row>
-    <row r="16" ht="120" spans="1:20">
+    <row r="16" ht="138" spans="1:20">
       <c r="A16" s="5">
         <v>10204</v>
       </c>
@@ -2628,7 +2628,7 @@
       <c r="S16" s="5"/>
       <c r="T16" s="5"/>
     </row>
-    <row r="17" ht="120" spans="1:20">
+    <row r="17" ht="138" spans="1:20">
       <c r="A17" s="5">
         <v>10205</v>
       </c>
@@ -2672,7 +2672,7 @@
       <c r="S17" s="5"/>
       <c r="T17" s="5"/>
     </row>
-    <row r="18" s="1" customFormat="1" ht="90" spans="1:20">
+    <row r="18" s="1" customFormat="1" ht="104" spans="1:20">
       <c r="A18" s="5">
         <v>10206</v>
       </c>
@@ -2716,7 +2716,7 @@
       <c r="S18" s="6"/>
       <c r="T18" s="6"/>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" ht="35" spans="1:20">
       <c r="A19" s="5">
         <v>10207</v>
       </c>
@@ -2760,7 +2760,7 @@
       <c r="S19" s="5"/>
       <c r="T19" s="5"/>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" ht="35" spans="1:20">
       <c r="A20" s="5">
         <v>10208</v>
       </c>
@@ -2804,7 +2804,7 @@
       <c r="S20" s="5"/>
       <c r="T20" s="5"/>
     </row>
-    <row r="21" ht="60" spans="1:20">
+    <row r="21" ht="69" spans="1:20">
       <c r="A21" s="5">
         <v>1301</v>
       </c>
@@ -2848,7 +2848,7 @@
       <c r="S21" s="5"/>
       <c r="T21" s="5"/>
     </row>
-    <row r="22" ht="120" spans="1:20">
+    <row r="22" ht="138" spans="1:20">
       <c r="A22" s="5">
         <v>1302</v>
       </c>
@@ -2892,7 +2892,7 @@
       <c r="S22" s="5"/>
       <c r="T22" s="5"/>
     </row>
-    <row r="23" ht="60" spans="1:20">
+    <row r="23" ht="69" spans="1:20">
       <c r="A23" s="5">
         <v>1401</v>
       </c>
@@ -2936,7 +2936,7 @@
       <c r="S23" s="5"/>
       <c r="T23" s="5"/>
     </row>
-    <row r="24" ht="120" spans="1:20">
+    <row r="24" ht="138" spans="1:20">
       <c r="A24" s="5">
         <v>1402</v>
       </c>
@@ -2980,7 +2980,7 @@
       <c r="S24" s="5"/>
       <c r="T24" s="5"/>
     </row>
-    <row r="25" ht="90" spans="1:20">
+    <row r="25" ht="104" spans="1:20">
       <c r="A25" s="5">
         <v>1501</v>
       </c>
@@ -3024,7 +3024,7 @@
       <c r="S25" s="5"/>
       <c r="T25" s="5"/>
     </row>
-    <row r="26" ht="150" spans="1:20">
+    <row r="26" ht="172" spans="1:20">
       <c r="A26" s="5">
         <v>1502</v>
       </c>
@@ -3068,7 +3068,7 @@
       <c r="S26" s="5"/>
       <c r="T26" s="5"/>
     </row>
-    <row r="27" ht="90" spans="1:20">
+    <row r="27" ht="104" spans="1:20">
       <c r="A27" s="5">
         <v>1601</v>
       </c>
@@ -3112,7 +3112,7 @@
       <c r="S27" s="5"/>
       <c r="T27" s="5"/>
     </row>
-    <row r="28" ht="60" spans="1:20">
+    <row r="28" ht="69" spans="1:20">
       <c r="A28" s="5">
         <v>1701</v>
       </c>
@@ -3156,7 +3156,7 @@
       <c r="S28" s="5"/>
       <c r="T28" s="5"/>
     </row>
-    <row r="29" ht="60" spans="1:20">
+    <row r="29" ht="69" spans="1:20">
       <c r="A29" s="5">
         <v>10301</v>
       </c>
@@ -3200,7 +3200,7 @@
       <c r="S29" s="5"/>
       <c r="T29" s="5"/>
     </row>
-    <row r="30" ht="90" spans="1:20">
+    <row r="30" ht="104" spans="1:20">
       <c r="A30" s="5">
         <v>10401</v>
       </c>
@@ -3244,7 +3244,7 @@
       <c r="S30" s="5"/>
       <c r="T30" s="5"/>
     </row>
-    <row r="31" ht="90" spans="1:20">
+    <row r="31" ht="104" spans="1:20">
       <c r="A31" s="5">
         <v>10402</v>
       </c>
@@ -3288,7 +3288,7 @@
       <c r="S31" s="5"/>
       <c r="T31" s="5"/>
     </row>
-    <row r="32" ht="120" spans="1:20">
+    <row r="32" ht="138" spans="1:20">
       <c r="A32" s="5">
         <v>10404</v>
       </c>
@@ -3332,7 +3332,7 @@
       <c r="S32" s="5"/>
       <c r="T32" s="5"/>
     </row>
-    <row r="33" spans="1:20">
+    <row r="33" ht="35" spans="1:20">
       <c r="A33" s="5">
         <v>10403</v>
       </c>
@@ -3376,7 +3376,7 @@
       <c r="S33" s="5"/>
       <c r="T33" s="5"/>
     </row>
-    <row r="34" ht="90" spans="1:20">
+    <row r="34" ht="104" spans="1:20">
       <c r="A34" s="5">
         <v>10501</v>
       </c>
@@ -3420,7 +3420,7 @@
       <c r="S34" s="5"/>
       <c r="T34" s="5"/>
     </row>
-    <row r="35" ht="90" spans="1:20">
+    <row r="35" ht="104" spans="1:20">
       <c r="A35" s="5">
         <v>10502</v>
       </c>
@@ -3464,7 +3464,7 @@
       <c r="S35" s="5"/>
       <c r="T35" s="5"/>
     </row>
-    <row r="36" s="1" customFormat="1" ht="120" spans="1:20">
+    <row r="36" s="1" customFormat="1" ht="138" spans="1:20">
       <c r="A36" s="5">
         <v>10503</v>
       </c>
@@ -3510,7 +3510,7 @@
       <c r="S36" s="5"/>
       <c r="T36" s="5"/>
     </row>
-    <row r="37" s="1" customFormat="1" ht="150" spans="1:20">
+    <row r="37" s="1" customFormat="1" ht="172" spans="1:20">
       <c r="A37" s="6">
         <v>10550</v>
       </c>
@@ -3556,7 +3556,7 @@
       <c r="S37" s="6"/>
       <c r="T37" s="6"/>
     </row>
-    <row r="38" s="1" customFormat="1" ht="150" spans="1:20">
+    <row r="38" s="1" customFormat="1" ht="172" spans="1:20">
       <c r="A38" s="6">
         <v>1801</v>
       </c>
@@ -3644,7 +3644,7 @@
       <c r="S39" s="6"/>
       <c r="T39" s="6"/>
     </row>
-    <row r="40" customFormat="1" ht="60" spans="1:20">
+    <row r="40" customFormat="1" ht="69" spans="1:20">
       <c r="A40" s="5">
         <v>1803</v>
       </c>
@@ -3694,7 +3694,7 @@
       <c r="S40" s="5"/>
       <c r="T40" s="5"/>
     </row>
-    <row r="41" ht="60" spans="1:20">
+    <row r="41" ht="69" spans="1:20">
       <c r="A41" s="5">
         <v>10601</v>
       </c>
@@ -3738,7 +3738,7 @@
       <c r="S41" s="5"/>
       <c r="T41" s="5"/>
     </row>
-    <row r="42" spans="1:20">
+    <row r="42" ht="35" spans="1:20">
       <c r="A42" s="5">
         <v>10602</v>
       </c>
@@ -3782,7 +3782,7 @@
       <c r="S42" s="5"/>
       <c r="T42" s="5"/>
     </row>
-    <row r="43" ht="60" spans="1:20">
+    <row r="43" ht="69" spans="1:20">
       <c r="A43" s="5">
         <v>10603</v>
       </c>
@@ -3826,7 +3826,7 @@
       <c r="S43" s="5"/>
       <c r="T43" s="5"/>
     </row>
-    <row r="44" ht="60" spans="1:20">
+    <row r="44" ht="69" spans="1:20">
       <c r="A44" s="5">
         <v>10604</v>
       </c>
@@ -3870,7 +3870,7 @@
       <c r="S44" s="5"/>
       <c r="T44" s="5"/>
     </row>
-    <row r="45" spans="1:20">
+    <row r="45" ht="35" spans="1:20">
       <c r="A45" s="5">
         <v>10701</v>
       </c>
@@ -3914,7 +3914,7 @@
       <c r="S45" s="5"/>
       <c r="T45" s="5"/>
     </row>
-    <row r="46" ht="60" spans="1:20">
+    <row r="46" ht="69" spans="1:20">
       <c r="A46" s="5">
         <v>10702</v>
       </c>
@@ -3958,7 +3958,7 @@
       <c r="S46" s="5"/>
       <c r="T46" s="5"/>
     </row>
-    <row r="47" ht="120" spans="1:20">
+    <row r="47" ht="138" spans="1:20">
       <c r="A47" s="5">
         <v>10703</v>
       </c>
@@ -4002,7 +4002,7 @@
       <c r="S47" s="5"/>
       <c r="T47" s="5"/>
     </row>
-    <row r="48" ht="180" spans="1:20">
+    <row r="48" ht="207" spans="1:20">
       <c r="A48" s="5">
         <v>10704</v>
       </c>
@@ -4048,7 +4048,7 @@
       <c r="S48" s="5"/>
       <c r="T48" s="5"/>
     </row>
-    <row r="49" ht="150" spans="1:20">
+    <row r="49" ht="172" spans="1:20">
       <c r="A49" s="5">
         <v>10705</v>
       </c>
@@ -4094,7 +4094,7 @@
       <c r="S49" s="5"/>
       <c r="T49" s="5"/>
     </row>
-    <row r="50" ht="120" spans="1:20">
+    <row r="50" ht="138" spans="1:20">
       <c r="A50" s="5">
         <v>10706</v>
       </c>
@@ -4140,7 +4140,7 @@
       <c r="S50" s="5"/>
       <c r="T50" s="5"/>
     </row>
-    <row r="51" ht="210" spans="1:20">
+    <row r="51" ht="241" spans="1:20">
       <c r="A51" s="5">
         <v>10707</v>
       </c>
@@ -4186,7 +4186,7 @@
       <c r="S51" s="5"/>
       <c r="T51" s="5"/>
     </row>
-    <row r="52" ht="120" spans="1:20">
+    <row r="52" ht="138" spans="1:20">
       <c r="A52" s="5">
         <v>10708</v>
       </c>
@@ -4232,7 +4232,7 @@
       <c r="S52" s="5"/>
       <c r="T52" s="5"/>
     </row>
-    <row r="53" ht="60" spans="1:20">
+    <row r="53" ht="69" spans="1:20">
       <c r="A53" s="5">
         <v>10801</v>
       </c>
@@ -4276,7 +4276,7 @@
       <c r="S53" s="5"/>
       <c r="T53" s="5"/>
     </row>
-    <row r="54" ht="120" spans="1:20">
+    <row r="54" ht="138" spans="1:20">
       <c r="A54" s="5">
         <v>10802</v>
       </c>
@@ -4320,7 +4320,7 @@
       <c r="S54" s="5"/>
       <c r="T54" s="5"/>
     </row>
-    <row r="55" ht="63" spans="1:20">
+    <row r="55" ht="69" spans="1:20">
       <c r="A55" s="5">
         <v>10803</v>
       </c>
@@ -4364,7 +4364,7 @@
       <c r="S55" s="5"/>
       <c r="T55" s="5"/>
     </row>
-    <row r="56" ht="60" spans="1:20">
+    <row r="56" ht="69" spans="1:20">
       <c r="A56" s="5">
         <v>10804</v>
       </c>
@@ -4408,7 +4408,7 @@
       <c r="S56" s="5"/>
       <c r="T56" s="5"/>
     </row>
-    <row r="57" ht="90" spans="1:20">
+    <row r="57" ht="104" spans="1:20">
       <c r="A57" s="5">
         <v>10901</v>
       </c>
@@ -4452,7 +4452,7 @@
       <c r="S57" s="5"/>
       <c r="T57" s="5"/>
     </row>
-    <row r="58" ht="90" spans="1:20">
+    <row r="58" ht="104" spans="1:20">
       <c r="A58" s="5">
         <v>10902</v>
       </c>
@@ -4496,7 +4496,7 @@
       <c r="S58" s="5"/>
       <c r="T58" s="5"/>
     </row>
-    <row r="59" ht="90" spans="1:20">
+    <row r="59" ht="104" spans="1:20">
       <c r="A59" s="5">
         <v>10903</v>
       </c>
@@ -4540,7 +4540,7 @@
       <c r="S59" s="5"/>
       <c r="T59" s="5"/>
     </row>
-    <row r="60" ht="60" spans="1:20">
+    <row r="60" ht="69" spans="1:20">
       <c r="A60" s="5">
         <v>10904</v>
       </c>
@@ -4584,7 +4584,7 @@
       <c r="S60" s="5"/>
       <c r="T60" s="5"/>
     </row>
-    <row r="61" ht="120" spans="1:20">
+    <row r="61" ht="138" spans="1:20">
       <c r="A61" s="5">
         <v>10905</v>
       </c>
@@ -4628,7 +4628,7 @@
       <c r="S61" s="5"/>
       <c r="T61" s="5"/>
     </row>
-    <row r="62" ht="120" spans="1:20">
+    <row r="62" ht="138" spans="1:20">
       <c r="A62" s="5">
         <v>10906</v>
       </c>
@@ -4672,7 +4672,7 @@
       <c r="S62" s="5"/>
       <c r="T62" s="5"/>
     </row>
-    <row r="63" ht="60" spans="1:20">
+    <row r="63" ht="69" spans="1:20">
       <c r="A63" s="5">
         <v>10907</v>
       </c>
@@ -4716,7 +4716,7 @@
       <c r="S63" s="5"/>
       <c r="T63" s="5"/>
     </row>
-    <row r="64" ht="60" spans="1:20">
+    <row r="64" ht="69" spans="1:20">
       <c r="A64" s="5">
         <v>10908</v>
       </c>
@@ -4760,7 +4760,7 @@
       <c r="S64" s="5"/>
       <c r="T64" s="5"/>
     </row>
-    <row r="65" ht="90" spans="1:20">
+    <row r="65" ht="104" spans="1:20">
       <c r="A65" s="5">
         <v>10909</v>
       </c>
@@ -4804,7 +4804,7 @@
       <c r="S65" s="5"/>
       <c r="T65" s="5"/>
     </row>
-    <row r="66" ht="90" spans="1:20">
+    <row r="66" ht="104" spans="1:20">
       <c r="A66" s="5">
         <v>10910</v>
       </c>
@@ -4848,7 +4848,7 @@
       <c r="S66" s="5"/>
       <c r="T66" s="5"/>
     </row>
-    <row r="67" ht="60" spans="1:20">
+    <row r="67" ht="69" spans="1:20">
       <c r="A67" s="5">
         <v>10911</v>
       </c>
@@ -4892,7 +4892,7 @@
       <c r="S67" s="5"/>
       <c r="T67" s="5"/>
     </row>
-    <row r="68" ht="90" spans="1:20">
+    <row r="68" ht="104" spans="1:20">
       <c r="A68" s="5">
         <v>10912</v>
       </c>
@@ -4938,7 +4938,7 @@
       <c r="S68" s="5"/>
       <c r="T68" s="5"/>
     </row>
-    <row r="69" ht="90" spans="1:20">
+    <row r="69" ht="104" spans="1:20">
       <c r="A69" s="5">
         <v>10950</v>
       </c>
@@ -4984,7 +4984,7 @@
       <c r="S69" s="5"/>
       <c r="T69" s="5"/>
     </row>
-    <row r="70" ht="90" spans="1:20">
+    <row r="70" ht="104" spans="1:20">
       <c r="A70" s="5">
         <v>11001</v>
       </c>
@@ -5028,7 +5028,7 @@
       <c r="S70" s="5"/>
       <c r="T70" s="5"/>
     </row>
-    <row r="71" spans="1:20">
+    <row r="71" ht="35" spans="1:20">
       <c r="A71" s="5">
         <v>11002</v>
       </c>
@@ -5072,7 +5072,7 @@
       <c r="S71" s="5"/>
       <c r="T71" s="5"/>
     </row>
-    <row r="72" ht="90" spans="1:20">
+    <row r="72" ht="104" spans="1:20">
       <c r="A72" s="5">
         <v>11101</v>
       </c>
@@ -5116,7 +5116,7 @@
       <c r="S72" s="5"/>
       <c r="T72" s="5"/>
     </row>
-    <row r="73" ht="60" spans="1:20">
+    <row r="73" ht="69" spans="1:20">
       <c r="A73" s="5">
         <v>11102</v>
       </c>
@@ -5160,7 +5160,7 @@
       <c r="S73" s="5"/>
       <c r="T73" s="5"/>
     </row>
-    <row r="74" ht="150" spans="1:20">
+    <row r="74" ht="172" spans="1:20">
       <c r="A74" s="5">
         <v>11103</v>
       </c>
@@ -5204,7 +5204,7 @@
       <c r="S74" s="5"/>
       <c r="T74" s="5"/>
     </row>
-    <row r="75" ht="150" spans="1:20">
+    <row r="75" ht="172" spans="1:20">
       <c r="A75" s="5">
         <v>11150</v>
       </c>
@@ -5250,7 +5250,7 @@
       <c r="S75" s="5"/>
       <c r="T75" s="5"/>
     </row>
-    <row r="76" ht="90" spans="1:20">
+    <row r="76" ht="104" spans="1:20">
       <c r="A76" s="5">
         <v>1901</v>
       </c>
@@ -5294,7 +5294,7 @@
       <c r="S76" s="5"/>
       <c r="T76" s="5"/>
     </row>
-    <row r="77" ht="120" spans="1:20">
+    <row r="77" ht="138" spans="1:20">
       <c r="A77" s="5">
         <v>1902</v>
       </c>
@@ -5338,7 +5338,7 @@
       <c r="S77" s="5"/>
       <c r="T77" s="5"/>
     </row>
-    <row r="78" ht="90" spans="1:20">
+    <row r="78" ht="104" spans="1:20">
       <c r="A78" s="5">
         <v>11201</v>
       </c>
@@ -5382,7 +5382,7 @@
       <c r="S78" s="5"/>
       <c r="T78" s="5"/>
     </row>
-    <row r="79" ht="60" spans="1:20">
+    <row r="79" ht="69" spans="1:20">
       <c r="A79" s="5">
         <v>11202</v>
       </c>
@@ -5426,7 +5426,7 @@
       <c r="S79" s="5"/>
       <c r="T79" s="5"/>
     </row>
-    <row r="80" ht="180" spans="1:20">
+    <row r="80" ht="207" spans="1:20">
       <c r="A80" s="5">
         <v>11203</v>
       </c>
@@ -5470,7 +5470,7 @@
       <c r="S80" s="5"/>
       <c r="T80" s="5"/>
     </row>
-    <row r="81" ht="90" spans="1:20">
+    <row r="81" ht="104" spans="1:20">
       <c r="A81" s="5">
         <v>11204</v>
       </c>
@@ -5514,7 +5514,7 @@
       <c r="S81" s="5"/>
       <c r="T81" s="5"/>
     </row>
-    <row r="82" ht="90" spans="1:20">
+    <row r="82" ht="104" spans="1:20">
       <c r="A82" s="5">
         <v>11205</v>
       </c>
@@ -5560,7 +5560,7 @@
       <c r="S82" s="5"/>
       <c r="T82" s="5"/>
     </row>
-    <row r="83" ht="60" spans="1:20">
+    <row r="83" ht="69" spans="1:20">
       <c r="A83" s="5">
         <v>11301</v>
       </c>
@@ -5604,7 +5604,7 @@
       <c r="S83" s="5"/>
       <c r="T83" s="5"/>
     </row>
-    <row r="84" ht="90" spans="1:20">
+    <row r="84" ht="104" spans="1:20">
       <c r="A84" s="5">
         <v>11302</v>
       </c>
@@ -5648,7 +5648,7 @@
       <c r="S84" s="5"/>
       <c r="T84" s="5"/>
     </row>
-    <row r="85" spans="1:20">
+    <row r="85" ht="69" spans="1:20">
       <c r="A85" s="5">
         <v>11303</v>
       </c>
@@ -5692,7 +5692,7 @@
       <c r="S85" s="5"/>
       <c r="T85" s="5"/>
     </row>
-    <row r="86" ht="120" spans="1:20">
+    <row r="86" ht="138" spans="1:20">
       <c r="A86" s="5">
         <v>11304</v>
       </c>
@@ -5736,7 +5736,7 @@
       <c r="S86" s="5"/>
       <c r="T86" s="5"/>
     </row>
-    <row r="87" ht="180" spans="1:20">
+    <row r="87" ht="207" spans="1:20">
       <c r="A87" s="5">
         <v>11305</v>
       </c>
@@ -5780,7 +5780,7 @@
       <c r="S87" s="5"/>
       <c r="T87" s="5"/>
     </row>
-    <row r="88" ht="120" spans="1:20">
+    <row r="88" ht="138" spans="1:20">
       <c r="A88" s="5">
         <v>11306</v>
       </c>
@@ -5824,7 +5824,7 @@
       <c r="S88" s="5"/>
       <c r="T88" s="5"/>
     </row>
-    <row r="89" ht="120" spans="1:20">
+    <row r="89" ht="138" spans="1:20">
       <c r="A89" s="5">
         <v>11307</v>
       </c>
@@ -5868,7 +5868,7 @@
       <c r="S89" s="5"/>
       <c r="T89" s="5"/>
     </row>
-    <row r="90" ht="150" spans="1:20">
+    <row r="90" ht="172" spans="1:20">
       <c r="A90" s="5">
         <v>11308</v>
       </c>
@@ -5914,7 +5914,7 @@
       <c r="S90" s="5"/>
       <c r="T90" s="5"/>
     </row>
-    <row r="91" ht="60" spans="1:20">
+    <row r="91" ht="69" spans="1:20">
       <c r="A91" s="5">
         <v>2001</v>
       </c>
@@ -5958,7 +5958,7 @@
       <c r="S91" s="5"/>
       <c r="T91" s="5"/>
     </row>
-    <row r="92" ht="60" spans="1:20">
+    <row r="92" ht="69" spans="1:20">
       <c r="A92" s="5">
         <v>2101</v>
       </c>
@@ -6002,7 +6002,7 @@
       <c r="S92" s="5"/>
       <c r="T92" s="5"/>
     </row>
-    <row r="93" spans="1:20">
+    <row r="93" ht="35" spans="1:20">
       <c r="A93" s="5">
         <v>2201</v>
       </c>
@@ -6046,7 +6046,7 @@
       <c r="S93" s="5"/>
       <c r="T93" s="5"/>
     </row>
-    <row r="94" ht="90" spans="1:20">
+    <row r="94" ht="104" spans="1:20">
       <c r="A94" s="5">
         <v>2301</v>
       </c>
@@ -6090,7 +6090,7 @@
       <c r="S94" s="5"/>
       <c r="T94" s="5"/>
     </row>
-    <row r="95" ht="60" spans="1:20">
+    <row r="95" ht="69" spans="1:20">
       <c r="A95" s="5">
         <v>11401</v>
       </c>
@@ -6134,7 +6134,7 @@
       <c r="S95" s="5"/>
       <c r="T95" s="5"/>
     </row>
-    <row r="96" ht="90" spans="1:20">
+    <row r="96" ht="104" spans="1:20">
       <c r="A96" s="5">
         <v>11402</v>
       </c>
@@ -6178,7 +6178,7 @@
       <c r="S96" s="5"/>
       <c r="T96" s="5"/>
     </row>
-    <row r="97" ht="60" spans="1:20">
+    <row r="97" ht="69" spans="1:20">
       <c r="A97" s="5">
         <v>11403</v>
       </c>
@@ -6224,7 +6224,7 @@
       <c r="S97" s="5"/>
       <c r="T97" s="5"/>
     </row>
-    <row r="98" ht="90" spans="1:20">
+    <row r="98" ht="104" spans="1:20">
       <c r="A98" s="5">
         <v>11501</v>
       </c>
@@ -6268,7 +6268,7 @@
       <c r="S98" s="5"/>
       <c r="T98" s="5"/>
     </row>
-    <row r="99" ht="120" spans="1:20">
+    <row r="99" ht="138" spans="1:20">
       <c r="A99" s="5">
         <v>11502</v>
       </c>
@@ -6312,7 +6312,7 @@
       <c r="S99" s="5"/>
       <c r="T99" s="5"/>
     </row>
-    <row r="100" ht="120" spans="1:20">
+    <row r="100" ht="138" spans="1:20">
       <c r="A100" s="5">
         <v>11503</v>
       </c>
@@ -6356,7 +6356,7 @@
       <c r="S100" s="5"/>
       <c r="T100" s="5"/>
     </row>
-    <row r="101" spans="1:20">
+    <row r="101" ht="35" spans="1:20">
       <c r="A101" s="5">
         <v>11504</v>
       </c>
@@ -6400,7 +6400,7 @@
       <c r="S101" s="5"/>
       <c r="T101" s="5"/>
     </row>
-    <row r="102" ht="60" spans="1:20">
+    <row r="102" ht="69" spans="1:20">
       <c r="A102" s="5">
         <v>11505</v>
       </c>
@@ -6444,7 +6444,7 @@
       <c r="S102" s="5"/>
       <c r="T102" s="5"/>
     </row>
-    <row r="103" spans="1:20">
+    <row r="103" ht="35" spans="1:20">
       <c r="A103" s="5">
         <v>11506</v>
       </c>
@@ -6488,7 +6488,7 @@
       <c r="S103" s="5"/>
       <c r="T103" s="5"/>
     </row>
-    <row r="104" ht="60" spans="1:20">
+    <row r="104" ht="69" spans="1:20">
       <c r="A104" s="5">
         <v>11507</v>
       </c>
@@ -6532,7 +6532,7 @@
       <c r="S104" s="5"/>
       <c r="T104" s="5"/>
     </row>
-    <row r="105" ht="150" spans="1:20">
+    <row r="105" ht="172" spans="1:20">
       <c r="A105" s="5">
         <v>11601</v>
       </c>
@@ -6576,7 +6576,7 @@
       <c r="S105" s="5"/>
       <c r="T105" s="5"/>
     </row>
-    <row r="106" ht="90" spans="1:20">
+    <row r="106" ht="104" spans="1:20">
       <c r="A106" s="5">
         <v>11602</v>
       </c>
@@ -6620,7 +6620,7 @@
       <c r="S106" s="5"/>
       <c r="T106" s="5"/>
     </row>
-    <row r="107" spans="1:20">
+    <row r="107" ht="35" spans="1:20">
       <c r="A107" s="5">
         <v>11603</v>
       </c>
@@ -6664,7 +6664,7 @@
       <c r="S107" s="5"/>
       <c r="T107" s="5"/>
     </row>
-    <row r="108" ht="90" spans="1:20">
+    <row r="108" ht="104" spans="1:20">
       <c r="A108" s="5">
         <v>11604</v>
       </c>
@@ -6708,7 +6708,7 @@
       <c r="S108" s="5"/>
       <c r="T108" s="5"/>
     </row>
-    <row r="109" spans="1:20">
+    <row r="109" ht="35" spans="1:20">
       <c r="A109" s="5">
         <v>11605</v>
       </c>
@@ -6752,7 +6752,7 @@
       <c r="S109" s="5"/>
       <c r="T109" s="5"/>
     </row>
-    <row r="110" ht="90" spans="1:20">
+    <row r="110" ht="104" spans="1:20">
       <c r="A110" s="5">
         <v>11606</v>
       </c>
@@ -6796,7 +6796,7 @@
       <c r="S110" s="5"/>
       <c r="T110" s="5"/>
     </row>
-    <row r="111" ht="60" spans="1:20">
+    <row r="111" ht="69" spans="1:20">
       <c r="A111" s="5">
         <v>2401</v>
       </c>
@@ -6840,7 +6840,7 @@
       <c r="S111" s="5"/>
       <c r="T111" s="5"/>
     </row>
-    <row r="112" ht="90" spans="1:20">
+    <row r="112" ht="104" spans="1:20">
       <c r="A112" s="5">
         <v>2402</v>
       </c>
@@ -6884,7 +6884,7 @@
       <c r="S112" s="5"/>
       <c r="T112" s="5"/>
     </row>
-    <row r="113" ht="90" spans="1:20">
+    <row r="113" ht="104" spans="1:20">
       <c r="A113" s="5">
         <v>2403</v>
       </c>
@@ -6928,7 +6928,7 @@
       <c r="S113" s="5"/>
       <c r="T113" s="5"/>
     </row>
-    <row r="114" ht="120" spans="1:20">
+    <row r="114" ht="138" spans="1:20">
       <c r="A114" s="5">
         <v>2404</v>
       </c>
@@ -6974,9 +6974,9 @@
       <c r="S114" s="5"/>
       <c r="T114" s="5"/>
     </row>
-    <row r="115" ht="60" spans="1:20">
+    <row r="115" ht="69" spans="1:20">
       <c r="A115" s="5">
-        <v>2501</v>
+        <v>2551</v>
       </c>
       <c r="B115" s="5">
         <v>2</v>
@@ -7018,7 +7018,7 @@
       <c r="S115" s="5"/>
       <c r="T115" s="5"/>
     </row>
-    <row r="116" ht="90" spans="1:20">
+    <row r="116" ht="104" spans="1:20">
       <c r="A116" s="5">
         <v>11701</v>
       </c>
@@ -7062,7 +7062,7 @@
       <c r="S116" s="5"/>
       <c r="T116" s="5"/>
     </row>
-    <row r="117" ht="90" spans="1:20">
+    <row r="117" ht="104" spans="1:20">
       <c r="A117" s="5">
         <v>11702</v>
       </c>
@@ -7106,7 +7106,7 @@
       <c r="S117" s="5"/>
       <c r="T117" s="5"/>
     </row>
-    <row r="118" ht="60" spans="1:20">
+    <row r="118" ht="69" spans="1:20">
       <c r="A118" s="5">
         <v>11703</v>
       </c>
@@ -7150,7 +7150,7 @@
       <c r="S118" s="5"/>
       <c r="T118" s="5"/>
     </row>
-    <row r="119" spans="1:20">
+    <row r="119" ht="35" spans="1:20">
       <c r="A119" s="5">
         <v>11704</v>
       </c>
@@ -7194,7 +7194,7 @@
       <c r="S119" s="5"/>
       <c r="T119" s="5"/>
     </row>
-    <row r="120" ht="60" spans="1:20">
+    <row r="120" ht="69" spans="1:20">
       <c r="A120" s="5">
         <v>2501</v>
       </c>
@@ -7238,7 +7238,7 @@
       <c r="S120" s="5"/>
       <c r="T120" s="5"/>
     </row>
-    <row r="121" ht="60" spans="1:20">
+    <row r="121" ht="69" spans="1:20">
       <c r="A121" s="5">
         <v>2601</v>
       </c>
@@ -7282,7 +7282,7 @@
       <c r="S121" s="5"/>
       <c r="T121" s="5"/>
     </row>
-    <row r="122" ht="90" spans="1:20">
+    <row r="122" ht="104" spans="1:20">
       <c r="A122" s="5">
         <v>2602</v>
       </c>
@@ -7326,7 +7326,7 @@
       <c r="S122" s="5"/>
       <c r="T122" s="5"/>
     </row>
-    <row r="123" ht="63" spans="1:20">
+    <row r="123" ht="69" spans="1:20">
       <c r="A123" s="5">
         <v>11801</v>
       </c>
@@ -7370,7 +7370,7 @@
       <c r="S123" s="5"/>
       <c r="T123" s="5"/>
     </row>
-    <row r="124" ht="120" spans="1:20">
+    <row r="124" ht="138" spans="1:20">
       <c r="A124" s="5">
         <v>11802</v>
       </c>
@@ -7414,7 +7414,7 @@
       <c r="S124" s="5"/>
       <c r="T124" s="5"/>
     </row>
-    <row r="125" ht="60" spans="1:20">
+    <row r="125" ht="69" spans="1:20">
       <c r="A125" s="5">
         <v>11803</v>
       </c>

--- a/Excel/DialogDatas.xlsx
+++ b/Excel/DialogDatas.xlsx
@@ -38,13 +38,13 @@
     <t>对话数据的id</t>
   </si>
   <si>
-    <t>对话主体的类型：0代表主角，1代表Mom，2代表Bob，3代表God，4代表TV，5代表相框，6代表桌子，7代表猫，8代表狗，9代表炸鸡店，10代表糖果店，11代表花店，12代表路人甲，13代表路人乙，14代表路人丙，15代表路人丁，16代表David‘Mom</t>
-  </si>
-  <si>
-    <t>对话的类型：0代表Normal，1代表Task，2代表Item，3代表Choose，4代表Effect，5代表Info</t>
-  </si>
-  <si>
-    <t>对话的触发时机，0代表isStart,1代表isSpeaking，2代表isEnd，isEnd暂时没用</t>
+    <t>对话主体的类型：0代表主角,1代表Mom,2代表Bob,3代表God,4代表TV,5代表相框,6代表桌子,7代表猫,8代表狗,9代表炸鸡店,10代表糖果店,11代表花店,12代表路人甲,13代表路人乙,14代表路人丙,15代表路人丁,16代表David‘Mom</t>
+  </si>
+  <si>
+    <t>对话的类型：0代表Normal,1代表Task,2代表Item,3代表Choose,4代表Effect,5代表Info</t>
+  </si>
+  <si>
+    <t>对话的触发时机,0代表isStart,1代表isSpeaking,2代表isEnd,isEnd暂时没用</t>
   </si>
   <si>
     <t>对话主体的名字</t>
@@ -53,46 +53,46 @@
     <t>对话主体的头像资源位置</t>
   </si>
   <si>
-    <t>如果是获得道具的对话，需要写出道具的id，默认没有道具，值为-1</t>
-  </si>
-  <si>
-    <t>如果是状态变化的对话，需要写出变化值，默认值为0</t>
+    <t>如果是获得道具的对话,需要写出道具的id,默认没有道具,值为-1</t>
+  </si>
+  <si>
+    <t>如果是状态变化的对话,需要写出变化值,默认值为0</t>
   </si>
   <si>
     <t>对话的文本数据</t>
   </si>
   <si>
-    <t>对话的父节点，写出父节点的id即可，暂时没用，没有就填0</t>
-  </si>
-  <si>
-    <t>对话的子节点，写出子节点的id即可</t>
-  </si>
-  <si>
-    <t>如果需要弹出提示面板，提示面板显示出的信息，如果不需要不需要填写内容</t>
-  </si>
-  <si>
-    <t>对话节点的选项一，没有不填，有填对应的内容</t>
-  </si>
-  <si>
-    <t>对话节点的选项二，没有不填，有填对应的内容</t>
-  </si>
-  <si>
-    <t>对话节点的选项三，没有不填，有填对应的内容</t>
-  </si>
-  <si>
-    <t>对话节点的选项四，没有不填，有填对应的内容</t>
-  </si>
-  <si>
-    <t>选择选项一对应的下一段对话（两种设计，这里对应的是RoleDialogData）的id,如果填0，选择后没有任何效果，直接关闭</t>
-  </si>
-  <si>
-    <t>选择选项二对应的下一段对话（两种设计，这里对应的是RoleDialogData）的id，,如果填0，选择后没有任何效果，直接关闭</t>
-  </si>
-  <si>
-    <t>选择选项三对应的下一段对话（两种设计，这里对应的是RoleDialogData）的id,如果填0，选择后没有任何效果，直接关闭</t>
-  </si>
-  <si>
-    <t>选择选项四对应的下一段对话（两种设计，这里对应的是RoleDialogData）的id,如果填0，选择后没有任何效果，直接关闭</t>
+    <t>对话的父节点,写出父节点的id即可,暂时没用,没有就填0</t>
+  </si>
+  <si>
+    <t>对话的子节点,写出子节点的id即可</t>
+  </si>
+  <si>
+    <t>如果需要弹出提示面板,提示面板显示出的信息,如果不需要不需要填写内容</t>
+  </si>
+  <si>
+    <t>对话节点的选项一,没有不填,有填对应的内容</t>
+  </si>
+  <si>
+    <t>对话节点的选项二,没有不填,有填对应的内容</t>
+  </si>
+  <si>
+    <t>对话节点的选项三,没有不填,有填对应的内容</t>
+  </si>
+  <si>
+    <t>对话节点的选项四,没有不填,有填对应的内容</t>
+  </si>
+  <si>
+    <t>选择选项一对应的下一段对话（两种设计,这里对应的是RoleDialogData）的id,如果填0,选择后没有任何效果,直接关闭</t>
+  </si>
+  <si>
+    <t>选择选项二对应的下一段对话（两种设计,这里对应的是RoleDialogData）的id,,如果填0,选择后没有任何效果,直接关闭</t>
+  </si>
+  <si>
+    <t>选择选项三对应的下一段对话（两种设计,这里对应的是RoleDialogData）的id,如果填0,选择后没有任何效果,直接关闭</t>
+  </si>
+  <si>
+    <t>选择选项四对应的下一段对话（两种设计,这里对应的是RoleDialogData）的id,如果填0,选择后没有任何效果,直接关闭</t>
   </si>
   <si>
     <t>id</t>
@@ -161,10 +161,10 @@
     <t>Sprites/MainRole</t>
   </si>
   <si>
-    <t>又做梦了，怎么最近老是梦到奇怪的场景</t>
-  </si>
-  <si>
-    <t xml:space="preserve">别管了，出去走走吧，今天还约了bob来家里玩 </t>
+    <t>又做梦了,怎么最近老是梦到奇怪的场景</t>
+  </si>
+  <si>
+    <t xml:space="preserve">别管了,出去走走吧,今天还约了bob来家里玩 </t>
   </si>
   <si>
     <t>相框</t>
@@ -173,34 +173,34 @@
     <t>Sprites/God</t>
   </si>
   <si>
-    <t>这是一张全家福。不过爸爸最近出差了，不知道什么时候回来。</t>
+    <t>这是一张全家福.不过爸爸最近出差了,不知道什么时候回来.</t>
   </si>
   <si>
     <t>桌子</t>
   </si>
   <si>
-    <t>吃饭的地方。有时除了饭还想吃点别的。</t>
+    <t>吃饭的地方.有时除了饭还想吃点别的.</t>
   </si>
   <si>
     <t>电视</t>
   </si>
   <si>
-    <t>近日，镇上隔壁老王失踪多日后确认遇害。</t>
-  </si>
-  <si>
-    <t>据透露，有人上山时打猎时在的山中发现他的残缺的遗体......</t>
-  </si>
-  <si>
-    <t>感觉收到惊吓，San值减少了20</t>
+    <t>近日,镇上隔壁老王失踪多日后确认遇害.</t>
+  </si>
+  <si>
+    <t>据透露,有人上山时打猎时在的山中发现他的残缺的遗体......</t>
+  </si>
+  <si>
+    <t>感觉收到惊吓,San值减少了20</t>
   </si>
   <si>
     <t>上帝</t>
   </si>
   <si>
-    <t>家里好像还有事情没有处理，四处逛逛吧</t>
-  </si>
-  <si>
-    <t>bob来了，我去开门吧</t>
+    <t>家里好像还有事情没有处理,四处逛逛吧</t>
+  </si>
+  <si>
+    <t>bob来了,我去开门吧</t>
   </si>
   <si>
     <t>鲍勃</t>
@@ -209,49 +209,49 @@
     <t>Sprites/Bob</t>
   </si>
   <si>
-    <t>嘿bro，看我在家里翻出一个水晶徽章，送给你</t>
-  </si>
-  <si>
-    <t>徽章中镶嵌着水晶，在阳光下很耀眼，似乎很珍贵</t>
+    <t>嘿bro,看我在家里翻出一个水晶徽章,送给你</t>
+  </si>
+  <si>
+    <t>徽章中镶嵌着水晶,在阳光下很耀眼,似乎很珍贵</t>
   </si>
   <si>
     <t>获得了Bob赠送的一个徽章</t>
   </si>
   <si>
-    <t>谢谢你，很好看，我很喜欢。</t>
-  </si>
-  <si>
-    <t>因为徽章的原因，觉得很开心，San值增加5</t>
-  </si>
-  <si>
-    <t>对了，你听说了隔壁老王的事吗？太可怕了，他住的就离我们家不远。</t>
-  </si>
-  <si>
-    <t>我听家里人说了...他们还让我不要多问。</t>
+    <t>谢谢你,很好看,我很喜欢.</t>
+  </si>
+  <si>
+    <t>因为徽章的原因,觉得很开心,San值增加5</t>
+  </si>
+  <si>
+    <t>对了,你听说了隔壁老王的事吗?太可怕了,他住的就离我们家不远.</t>
+  </si>
+  <si>
+    <t>我听家里人说了...他们还让我不要多问.</t>
   </si>
   <si>
     <t>......</t>
   </si>
   <si>
-    <t>一起走走吧。</t>
+    <t>一起走走吧.</t>
   </si>
   <si>
     <t>猫</t>
   </si>
   <si>
-    <t>猫抬头看了你一眼，并伸了个懒腰</t>
-  </si>
-  <si>
-    <t>和小猫互动感觉很开心，San值增加了5</t>
+    <t>猫抬头看了你一眼,并伸了个懒腰</t>
+  </si>
+  <si>
+    <t>和小猫互动感觉很开心,San值增加了5</t>
   </si>
   <si>
     <t>狗</t>
   </si>
   <si>
-    <t>继续继续，狗子更喜欢你</t>
-  </si>
-  <si>
-    <t>和小狗互动感觉很开心，San值增加了5</t>
+    <t>继续继续,狗子更喜欢你</t>
+  </si>
+  <si>
+    <t>和小狗互动感觉很开心,San值增加了5</t>
   </si>
   <si>
     <t>炸鸡店</t>
@@ -260,19 +260,19 @@
     <t>好心的老板给了两位小朋友一人一个炸鸡腿</t>
   </si>
   <si>
-    <t>因为老板赠送的鸡腿感觉很高兴，San值增加了5</t>
+    <t>因为老板赠送的鸡腿感觉很高兴,San值增加了5</t>
   </si>
   <si>
     <t>糖果店</t>
   </si>
   <si>
-    <t>小时候最爱吃的糖果。不对现在就是小时候啊喂</t>
+    <t>小时候最爱吃的糖果.不对现在就是小时候啊喂</t>
   </si>
   <si>
     <t>花店</t>
   </si>
   <si>
-    <t>买束花吧，或许接下来会有用</t>
+    <t>买束花吧,或许接下来会有用</t>
   </si>
   <si>
     <t>好像是隔壁老王家在举行葬礼</t>
@@ -281,37 +281,37 @@
     <t>路人甲</t>
   </si>
   <si>
-    <t>上周我还跟老王聊天呢。哎。他说他睡得不太好。</t>
+    <t>上周我还跟老王聊天呢.哎.他说他睡得不太好.</t>
   </si>
   <si>
     <t>路人乙</t>
   </si>
   <si>
-    <t>我最近也睡得不好，醒来总是很疲惫。</t>
-  </si>
-  <si>
-    <t>奇怪的是，醒来鞋子上有湿泥土的痕迹。但最近只有晚上下雨啊</t>
+    <t>我最近也睡得不好,醒来总是很疲惫.</t>
+  </si>
+  <si>
+    <t>奇怪的是,醒来鞋子上有湿泥土的痕迹.但最近只有晚上下雨啊</t>
   </si>
   <si>
     <t>旁白</t>
   </si>
   <si>
-    <t>快傍晚了，心底有一股力量在说你们该回家了</t>
-  </si>
-  <si>
-    <t>我总觉得有些不对，bob你明天再来我家吧</t>
-  </si>
-  <si>
-    <t>尽快回家吧，在外面玩的太晚不是什么好事</t>
-  </si>
-  <si>
-    <t>家里已经没有事情可以处理了，在院子四处逛逛吧</t>
-  </si>
-  <si>
-    <t>想想今天所看到的。奇怪的梦，遇害的隔壁老王，带血的牙齿，异常的毛发......</t>
-  </si>
-  <si>
-    <t>你认为这是因为？</t>
+    <t>快傍晚了,心底有一股力量在说你们该回家了</t>
+  </si>
+  <si>
+    <t>我总觉得有些不对,bob你明天再来我家吧</t>
+  </si>
+  <si>
+    <t>尽快回家吧,在外面玩的太晚不是什么好事</t>
+  </si>
+  <si>
+    <t>家里已经没有事情可以处理了,在院子四处逛逛吧</t>
+  </si>
+  <si>
+    <t>想想今天所看到的.奇怪的梦,遇害的隔壁老王,带血的牙齿,异常的毛发......</t>
+  </si>
+  <si>
+    <t>你认为这是因为?</t>
   </si>
   <si>
     <t>外星人打过来了</t>
@@ -332,25 +332,25 @@
     <t>Sprites/Mom</t>
   </si>
   <si>
-    <t>宝贝，喝了牛奶快睡觉吧。</t>
+    <t>宝贝,喝了牛奶快睡觉吧.</t>
   </si>
   <si>
     <t>我有点不想喝</t>
   </si>
   <si>
-    <t>不喝的话晚上会有怪兽来抓你噢。</t>
-  </si>
-  <si>
-    <t>我才不怕呢，有怪兽我会打败它的。</t>
-  </si>
-  <si>
-    <t>这是怎么回事？</t>
+    <t>不喝的话晚上会有怪兽来抓你噢.</t>
+  </si>
+  <si>
+    <t>我才不怕呢,有怪兽我会打败它的.</t>
+  </si>
+  <si>
+    <t>这是怎么回事?</t>
   </si>
   <si>
     <t>我为什么会变成这幅模样</t>
   </si>
   <si>
-    <t>等等，我感觉身体变得很轻盈，感觉跑的速度更快了，一跳可以跳的很高</t>
+    <t>等等,我感觉身体变得很轻盈,感觉跑的速度更快了,一跳可以跳的很高</t>
   </si>
   <si>
     <t>按下&lt;color=yellow&gt;A&lt;/color&gt;和&lt;color=yellow&gt;D&lt;/color&gt;键进行左右移动</t>
@@ -359,10 +359,10 @@
     <t>按下A和D键进行左右移动</t>
   </si>
   <si>
-    <t>按下&lt;color=yellow&gt;Space&lt;/color&gt;键进行跳跃，连续按下可以进行二连跳</t>
-  </si>
-  <si>
-    <t>按下Space键进行跳跃，连续按下可以进行而连跳</t>
+    <t>按下&lt;color=yellow&gt;Space&lt;/color&gt;键进行跳跃,连续按下可以进行二连跳</t>
+  </si>
+  <si>
+    <t>按下Space键进行跳跃,连续按下可以进行而连跳</t>
   </si>
   <si>
     <t>在平台上可以通过&lt;color=yellow&gt;S+Space&lt;/color&gt;进行下平台</t>
@@ -371,138 +371,121 @@
     <t>在平台上可以通过S+Space进行下平台</t>
   </si>
   <si>
-    <t>按下&lt;color=yellow&gt;J&lt;/color&gt;键可以进行普通攻击1，按下&lt;color=yellow&gt;K&lt;/color&gt;键可以进行普通攻击2</t>
-  </si>
-  <si>
-    <t>按下J键可以进行普通攻击1，按下K键可以进行普通攻击2</t>
-  </si>
-  <si>
-    <t>你已经熟悉了全部操作，尝试通过这里吧</t>
-  </si>
-  <si>
-    <t>这太奇怪了，我居然又做了这种梦</t>
-  </si>
-  <si>
-    <t>对梦里的事情感到后怕，San值减少10</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <color rgb="FF000000"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>等下bob来，必须得和他说一下</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <color rgb="FF333333"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>嘿bob我跟你说，我这两天都梦见我在打怪兽。</t>
-  </si>
-  <si>
-    <t>我特别厉害，一刀一个打倒了很多怪兽，还救了路人</t>
+    <t>按下&lt;color=yellow&gt;J&lt;/color&gt;键可以进行普通攻击1,按下&lt;color=yellow&gt;K&lt;/color&gt;键可以进行普通攻击2</t>
+  </si>
+  <si>
+    <t>按下J键可以进行普通攻击1,按下K键可以进行普通攻击2</t>
+  </si>
+  <si>
+    <t>你已经熟悉了全部操作,尝试通过这里吧</t>
+  </si>
+  <si>
+    <t>这太奇怪了,我居然又做了这种梦</t>
+  </si>
+  <si>
+    <t>对梦里的事情感到后怕,San值减少10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">等下bob来,必须得和他说一下 </t>
+  </si>
+  <si>
+    <t>嘿bob我跟你说,我这两天都梦见我在打怪兽.</t>
+  </si>
+  <si>
+    <t>我特别厉害,一刀一个打倒了很多怪兽,还救了路人</t>
   </si>
   <si>
     <t>我今天早上起来好像都有点腰酸背痛呢</t>
   </si>
   <si>
-    <t>但我觉得这有些奇怪。</t>
-  </si>
-  <si>
-    <t>我才不信呢，如果我打怪兽肯定比你厉害 。我家可还有圣剑！</t>
-  </si>
-  <si>
-    <t>那可不一定！但是说不定今晚你也能梦到，我们一起打怪兽</t>
+    <t>但我觉得这有些奇怪.</t>
+  </si>
+  <si>
+    <t>我才不信呢,如果我打怪兽肯定比你厉害 .我家可还有圣剑！</t>
+  </si>
+  <si>
+    <t>那可不一定！但是说不定今晚你也能梦到,我们一起打怪兽</t>
   </si>
   <si>
     <t>可是我从来没做过梦</t>
   </si>
   <si>
-    <t>怎么会呢？我就经常做梦</t>
-  </si>
-  <si>
-    <t>别说这些了，进去坐坐，我们喝牛奶吧</t>
-  </si>
-  <si>
-    <t>好啊。不过那种东西你天天喝还没喝腻吗</t>
-  </si>
-  <si>
-    <t>没办法，我妈让我喝，说长得高</t>
+    <t>怎么会呢?我就经常做梦</t>
+  </si>
+  <si>
+    <t>别说这些了,进去坐坐,我们喝牛奶吧</t>
+  </si>
+  <si>
+    <t>好啊.不过那种东西你天天喝还没喝腻吗</t>
+  </si>
+  <si>
+    <t>没办法,我妈让我喝,说长得高</t>
   </si>
   <si>
     <t>去客厅的桌子上喝牛奶吧</t>
   </si>
   <si>
-    <t>你们不可以白天喝牛奶噢。乖，去外边玩吧</t>
-  </si>
-  <si>
-    <t>为什么妈妈不让我们现在喝牛奶呢？好奇怪</t>
-  </si>
-  <si>
-    <t>要不给小猫喝一下？</t>
-  </si>
-  <si>
-    <t>感觉到很奇怪，san值减少5，去拿给小猫喝一口吧</t>
-  </si>
-  <si>
-    <t>妈妈不允许喝牛奶，这是为什么呢？去院子探索一番吧</t>
-  </si>
-  <si>
-    <t>猫喝了牛奶很快呼呼大睡了，你心里觉得更奇怪了</t>
-  </si>
-  <si>
-    <t>对小猫的行为感到很奇怪，san值减5</t>
-  </si>
-  <si>
-    <t>小猫真是吃饱了就睡觉了。我们把它的铃铛取下来吧</t>
+    <t>你们不可以白天喝牛奶噢.乖,去外边玩吧</t>
+  </si>
+  <si>
+    <t>为什么妈妈不让我们现在喝牛奶呢?好奇怪</t>
+  </si>
+  <si>
+    <t>要不给小猫喝一下?</t>
+  </si>
+  <si>
+    <t>感觉到很奇怪,san值减少5,去拿给小猫喝一口吧</t>
+  </si>
+  <si>
+    <t>妈妈不允许喝牛奶,这是为什么呢?去院子探索一番吧</t>
+  </si>
+  <si>
+    <t>猫喝了牛奶很快呼呼大睡了,你心里觉得更奇怪了</t>
+  </si>
+  <si>
+    <t>对小猫的行为感到很奇怪,san值减5</t>
+  </si>
+  <si>
+    <t>小猫真是吃饱了就睡觉了.我们把它的铃铛取下来吧</t>
   </si>
   <si>
     <t>你上前取下了小猫戴着的铃铛</t>
   </si>
   <si>
-    <t>获得一个铃铛，虽然看起来有些旧，但是收着吧，可能后面会有用</t>
-  </si>
-  <si>
-    <t>不应该是这样的，我们得去问问其他人</t>
-  </si>
-  <si>
-    <t>四处走走，打听一下消息吧</t>
-  </si>
-  <si>
-    <t>叔叔，想问你会在白天喝牛奶吗</t>
-  </si>
-  <si>
-    <t>会。但我指的牛奶跟你说的不是同一种吧。</t>
+    <t>获得一个铃铛,虽然看起来有些旧,但是收着吧,可能后面会有用</t>
+  </si>
+  <si>
+    <t>不应该是这样的,我们得去问问其他人</t>
+  </si>
+  <si>
+    <t>四处走走,打听一下消息吧</t>
+  </si>
+  <si>
+    <t>叔叔,想问你会在白天喝牛奶吗</t>
+  </si>
+  <si>
+    <t>会.但我指的牛奶跟你说的不是同一种吧.</t>
   </si>
   <si>
     <t>......为什么这么说</t>
   </si>
   <si>
-    <t>对他说的话感到奇怪，san值减少5点</t>
-  </si>
-  <si>
-    <t>是你家大人不让你们喝吗？我只能告诉你，我的父母从小也是这么告诉我的，父母的父母那辈也是如此。</t>
-  </si>
-  <si>
-    <t>说不定只有我们镇上，父母会跟孩子说睡前不喝牛奶会有怪兽来抓你呢。</t>
-  </si>
-  <si>
-    <t>你长大就知道了。有些事情就是这样传承下来的。不需要知道为什么。</t>
-  </si>
-  <si>
-    <t>对他的话感到很疑惑，四处逛逛收集更多信息吧</t>
-  </si>
-  <si>
-    <t>我爱睡觉皮肤好好，啦啦啦</t>
+    <t>对他说的话感到奇怪,san值减少5点</t>
+  </si>
+  <si>
+    <t>是你家大人不让你们喝吗?我只能告诉你,我的父母从小也是这么告诉我的,父母的父母那辈也是如此.</t>
+  </si>
+  <si>
+    <t>说不定只有我们镇上,父母会跟孩子说睡前不喝牛奶会有怪兽来抓你呢.</t>
+  </si>
+  <si>
+    <t>你长大就知道了.有些事情就是这样传承下来的.不需要知道为什么.</t>
+  </si>
+  <si>
+    <t>对他的话感到很疑惑,四处逛逛收集更多信息吧</t>
+  </si>
+  <si>
+    <t>我爱睡觉皮肤好好,啦啦啦</t>
   </si>
   <si>
     <t>路人丙</t>
@@ -517,10 +500,10 @@
     <t>最近晚上不安全啊</t>
   </si>
   <si>
-    <t>宝贝，喝牛奶长高高，喝了快睡觉吧</t>
-  </si>
-  <si>
-    <t>你感到牛奶也很奇怪，但心底有股冲动还是想喝下去</t>
+    <t>宝贝,喝牛奶长高高,喝了快睡觉吧</t>
+  </si>
+  <si>
+    <t>你感到牛奶也很奇怪,但心底有股冲动还是想喝下去</t>
   </si>
   <si>
     <t>你最终选择喝下了牛奶</t>
@@ -529,16 +512,16 @@
     <t>鲍勃的妈妈</t>
   </si>
   <si>
-    <t>bob！把作业写了之后把这个喝了，你怎么又在玩玩具！</t>
-  </si>
-  <si>
-    <t>这是圣剑啦！作业我早就写完了，还有，我不想喝这个了，我都喝腻了</t>
-  </si>
-  <si>
-    <t>这个牛奶的味道让我恶心。（拿过杯子）（也许我可以偷偷把它倒掉）</t>
-  </si>
-  <si>
-    <t>奇怪，今天怎么有点睡不着？</t>
+    <t>bob！把作业写了之后把这个喝了,你怎么又在玩玩具！</t>
+  </si>
+  <si>
+    <t>这是圣剑啦！作业我早就写完了,还有,我不想喝这个了,我都喝腻了</t>
+  </si>
+  <si>
+    <t>这个牛奶的味道让我恶心.（拿过杯子）（也许我可以偷偷把它倒掉）</t>
+  </si>
+  <si>
+    <t>奇怪,今天怎么有点睡不着?</t>
   </si>
   <si>
     <t>（外面月光明亮）</t>
@@ -547,10 +530,10 @@
     <t>带上圣剑出去走走吧</t>
   </si>
   <si>
-    <t>还从来没有在这时候出过门呢，路上怎么一个人都没有。我有点害怕了，也许我该回去了</t>
-  </si>
-  <si>
-    <t>那里有个人！等等，那些是什么啊！</t>
+    <t>还从来没有在这时候出过门呢,路上怎么一个人都没有.我有点害怕了,也许我该回去了</t>
+  </si>
+  <si>
+    <t>那里有个人！等等,那些是什么啊！</t>
   </si>
   <si>
     <t>啊！那些怪物吃了他！我要快点回家！</t>
@@ -562,7 +545,7 @@
     <t>又是昨天一样的梦......</t>
   </si>
   <si>
-    <t>今天好像适应了这副身体，感觉可以大杀四方</t>
+    <t>今天好像适应了这副身体,感觉可以大杀四方</t>
   </si>
   <si>
     <t>等醒了可以和鲍勃炫耀一下今天的战果</t>
@@ -574,10 +557,10 @@
     <t>迈克！！！不要！！！</t>
   </si>
   <si>
-    <t>刚刚那是什么声音， 我怎么好像听到了鲍勃的声音？</t>
-  </si>
-  <si>
-    <t>不对，我的头好痛，到底是怎么回事</t>
+    <t>刚刚那是什么声音, 我怎么好像听到了鲍勃的声音?</t>
+  </si>
+  <si>
+    <t>不对,我的头好痛,到底是怎么回事</t>
   </si>
   <si>
     <t>怪兽到底是哪里来的</t>
@@ -586,36 +569,19 @@
     <t>迈克昏迷了过去</t>
   </si>
   <si>
-    <t>这么晚了，还有谁会来呢</t>
-  </si>
-  <si>
-    <t>救命啊 , mike快开门，</t>
+    <t>这么晚了,还有谁会来呢</t>
+  </si>
+  <si>
+    <t>救命啊 , mike快开门,</t>
   </si>
   <si>
     <t>你都不知道我在外面看到了什么恐怖的东西</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <color rgb="FF000000"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我闻到一股香甜的味道。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">我感觉身体在被撕裂，正在慢慢变大，牙齿也在变长...... </t>
+    <t xml:space="preserve">我闻到一股香甜的味道. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">我感觉身体在被撕裂,正在慢慢变大,牙齿也在变长...... </t>
   </si>
   <si>
     <t>我难以抑制的向前扑了过去</t>
@@ -631,7 +597,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -820,18 +786,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="24"/>
-      <color rgb="FF333333"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="24"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2184,7 +2138,7 @@
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
     </row>
-    <row r="7" ht="104" spans="1:20">
+    <row r="7" ht="69" spans="1:20">
       <c r="A7" s="5">
         <v>1101</v>
       </c>
@@ -3244,7 +3198,7 @@
       <c r="S30" s="5"/>
       <c r="T30" s="5"/>
     </row>
-    <row r="31" ht="104" spans="1:20">
+    <row r="31" ht="69" spans="1:20">
       <c r="A31" s="5">
         <v>10402</v>
       </c>
@@ -4760,7 +4714,7 @@
       <c r="S64" s="5"/>
       <c r="T64" s="5"/>
     </row>
-    <row r="65" ht="104" spans="1:20">
+    <row r="65" ht="69" spans="1:20">
       <c r="A65" s="5">
         <v>10909</v>
       </c>
@@ -5116,7 +5070,7 @@
       <c r="S72" s="5"/>
       <c r="T72" s="5"/>
     </row>
-    <row r="73" ht="69" spans="1:20">
+    <row r="73" ht="35" spans="1:20">
       <c r="A73" s="5">
         <v>11102</v>
       </c>
@@ -5470,7 +5424,7 @@
       <c r="S80" s="5"/>
       <c r="T80" s="5"/>
     </row>
-    <row r="81" ht="104" spans="1:20">
+    <row r="81" ht="69" spans="1:20">
       <c r="A81" s="5">
         <v>11204</v>
       </c>
@@ -6576,7 +6530,7 @@
       <c r="S105" s="5"/>
       <c r="T105" s="5"/>
     </row>
-    <row r="106" ht="104" spans="1:20">
+    <row r="106" ht="69" spans="1:20">
       <c r="A106" s="5">
         <v>11602</v>
       </c>
@@ -7062,7 +7016,7 @@
       <c r="S116" s="5"/>
       <c r="T116" s="5"/>
     </row>
-    <row r="117" ht="104" spans="1:20">
+    <row r="117" ht="69" spans="1:20">
       <c r="A117" s="5">
         <v>11702</v>
       </c>
